--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,108 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Hobro</t>
+  </si>
+  <si>
+    <t>Al Riyadh SC</t>
+  </si>
+  <si>
+    <t>Al-Hazm (KSA)</t>
+  </si>
+  <si>
+    <t>AL Arabi (Qat)</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Al-Quadisiya (KSA)</t>
+  </si>
+  <si>
+    <t>Al Faisaly ( KSA )</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Esbjerg</t>
+  </si>
+  <si>
+    <t>AaB</t>
+  </si>
+  <si>
+    <t>Al Nassr</t>
+  </si>
+  <si>
+    <t>Al Draih</t>
+  </si>
+  <si>
+    <t>AL Shamal</t>
+  </si>
+  <si>
+    <t>Aarhus Fremad</t>
+  </si>
+  <si>
+    <t>Al-Ittihad</t>
+  </si>
+  <si>
+    <t>NEOM Sports Club</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>2026-08-19 00:05:49</t>
   </si>
 </sst>
 </file>
@@ -585,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +930,2426 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2">
+        <v>1.96</v>
+      </c>
+      <c r="G2">
+        <v>2.1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>5.7</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3.25</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.16</v>
+      </c>
+      <c r="N2">
+        <v>2.24</v>
+      </c>
+      <c r="O2">
+        <v>1.69</v>
+      </c>
+      <c r="P2">
+        <v>1.41</v>
+      </c>
+      <c r="Q2">
+        <v>3.1</v>
+      </c>
+      <c r="R2">
+        <v>1.16</v>
+      </c>
+      <c r="S2">
+        <v>6.8</v>
+      </c>
+      <c r="T2">
+        <v>2.52</v>
+      </c>
+      <c r="U2">
+        <v>1.56</v>
+      </c>
+      <c r="V2">
+        <v>1.21</v>
+      </c>
+      <c r="W2">
+        <v>1.9</v>
+      </c>
+      <c r="X2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y2">
+        <v>13.5</v>
+      </c>
+      <c r="Z2">
+        <v>46</v>
+      </c>
+      <c r="AA2">
+        <v>220</v>
+      </c>
+      <c r="AB2">
+        <v>6.6</v>
+      </c>
+      <c r="AC2">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>29</v>
+      </c>
+      <c r="AE2">
+        <v>150</v>
+      </c>
+      <c r="AF2">
+        <v>12</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>40</v>
+      </c>
+      <c r="AI2">
+        <v>190</v>
+      </c>
+      <c r="AJ2">
+        <v>30</v>
+      </c>
+      <c r="AK2">
+        <v>40</v>
+      </c>
+      <c r="AL2">
+        <v>100</v>
+      </c>
+      <c r="AM2">
+        <v>410</v>
+      </c>
+      <c r="AN2">
+        <v>38</v>
+      </c>
+      <c r="AO2">
+        <v>320</v>
+      </c>
+      <c r="AP2">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>5</v>
+      </c>
+      <c r="AS2">
+        <v>5.5</v>
+      </c>
+      <c r="AT2">
+        <v>4.5</v>
+      </c>
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
+        <v>18.5</v>
+      </c>
+      <c r="AW2">
+        <v>5.4</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>11</v>
+      </c>
+      <c r="AZ2">
+        <v>4.9</v>
+      </c>
+      <c r="BA2">
+        <v>5.4</v>
+      </c>
+      <c r="BB2">
+        <v>18.5</v>
+      </c>
+      <c r="BC2">
+        <v>4.9</v>
+      </c>
+      <c r="BD2">
+        <v>5.3</v>
+      </c>
+      <c r="BE2">
+        <v>5.5</v>
+      </c>
+      <c r="BF2">
+        <v>4.9</v>
+      </c>
+      <c r="BG2">
+        <v>5.5</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.65</v>
+      </c>
+      <c r="BJ2">
+        <v>18.5</v>
+      </c>
+      <c r="BK2">
+        <v>1.51</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.65</v>
+      </c>
+      <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>3</v>
+      </c>
+      <c r="BP2">
+        <v>24</v>
+      </c>
+      <c r="BQ2">
+        <v>1.54</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.61</v>
+      </c>
+      <c r="BT2">
+        <v>12.5</v>
+      </c>
+      <c r="BU2">
+        <v>1.46</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.62</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.65</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.61</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3">
+        <v>1.67</v>
+      </c>
+      <c r="G3">
+        <v>1.81</v>
+      </c>
+      <c r="H3">
+        <v>4.3</v>
+      </c>
+      <c r="I3">
+        <v>5.2</v>
+      </c>
+      <c r="J3">
+        <v>4.2</v>
+      </c>
+      <c r="K3">
+        <v>5.1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>2.58</v>
+      </c>
+      <c r="Q3">
+        <v>1.46</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4">
+        <v>2.76</v>
+      </c>
+      <c r="G4">
+        <v>3.1</v>
+      </c>
+      <c r="H4">
+        <v>2.44</v>
+      </c>
+      <c r="I4">
+        <v>2.68</v>
+      </c>
+      <c r="J4">
+        <v>3.55</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.96</v>
+      </c>
+      <c r="Q4">
+        <v>1.61</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5">
+        <v>9.6</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>1.27</v>
+      </c>
+      <c r="I5">
+        <v>1.35</v>
+      </c>
+      <c r="J5">
+        <v>6.4</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>3.3</v>
+      </c>
+      <c r="Q5">
+        <v>1.34</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6">
+        <v>1.16</v>
+      </c>
+      <c r="G6">
+        <v>600</v>
+      </c>
+      <c r="H6">
+        <v>1.16</v>
+      </c>
+      <c r="I6">
+        <v>870</v>
+      </c>
+      <c r="J6">
+        <v>1.17</v>
+      </c>
+      <c r="K6">
+        <v>950</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7">
+        <v>2.76</v>
+      </c>
+      <c r="G7">
+        <v>3.35</v>
+      </c>
+      <c r="H7">
+        <v>2.28</v>
+      </c>
+      <c r="I7">
+        <v>2.66</v>
+      </c>
+      <c r="J7">
+        <v>3.7</v>
+      </c>
+      <c r="K7">
+        <v>5.1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>2.38</v>
+      </c>
+      <c r="Q7">
+        <v>1.53</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8">
+        <v>1.64</v>
+      </c>
+      <c r="G8">
+        <v>1.78</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>6.8</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>4.7</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2.04</v>
+      </c>
+      <c r="Q8">
+        <v>1.57</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>1.76</v>
+      </c>
+      <c r="G9">
+        <v>1.94</v>
+      </c>
+      <c r="H9">
+        <v>3.75</v>
+      </c>
+      <c r="I9">
+        <v>870</v>
+      </c>
+      <c r="J9">
+        <v>4.3</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>2.74</v>
+      </c>
+      <c r="Q9">
+        <v>1.4</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10">
+        <v>4.3</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>1.72</v>
+      </c>
+      <c r="I10">
+        <v>1.85</v>
+      </c>
+      <c r="J10">
+        <v>4.2</v>
+      </c>
+      <c r="K10">
+        <v>4.7</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.22</v>
+      </c>
+      <c r="Q10">
+        <v>1.48</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11">
+        <v>2.14</v>
+      </c>
+      <c r="G11">
+        <v>2.18</v>
+      </c>
+      <c r="H11">
+        <v>3.85</v>
+      </c>
+      <c r="I11">
+        <v>3.95</v>
+      </c>
+      <c r="J11">
+        <v>3.55</v>
+      </c>
+      <c r="K11">
+        <v>3.65</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.08</v>
+      </c>
+      <c r="N11">
+        <v>3.6</v>
+      </c>
+      <c r="O11">
+        <v>1.36</v>
+      </c>
+      <c r="P11">
+        <v>1.89</v>
+      </c>
+      <c r="Q11">
+        <v>2.06</v>
+      </c>
+      <c r="R11">
+        <v>1.34</v>
+      </c>
+      <c r="S11">
+        <v>3.8</v>
+      </c>
+      <c r="T11">
+        <v>1.86</v>
+      </c>
+      <c r="U11">
+        <v>2.1</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>13.5</v>
+      </c>
+      <c r="Y11">
+        <v>13.5</v>
+      </c>
+      <c r="Z11">
+        <v>28</v>
+      </c>
+      <c r="AA11">
+        <v>85</v>
+      </c>
+      <c r="AB11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC11">
+        <v>7.8</v>
+      </c>
+      <c r="AD11">
+        <v>16</v>
+      </c>
+      <c r="AE11">
+        <v>55</v>
+      </c>
+      <c r="AF11">
+        <v>13</v>
+      </c>
+      <c r="AG11">
+        <v>11</v>
+      </c>
+      <c r="AH11">
+        <v>20</v>
+      </c>
+      <c r="AI11">
+        <v>60</v>
+      </c>
+      <c r="AJ11">
+        <v>26</v>
+      </c>
+      <c r="AK11">
+        <v>24</v>
+      </c>
+      <c r="AL11">
+        <v>42</v>
+      </c>
+      <c r="AM11">
+        <v>130</v>
+      </c>
+      <c r="AN11">
+        <v>17.5</v>
+      </c>
+      <c r="AO11">
+        <v>60</v>
+      </c>
+      <c r="AP11">
+        <v>12</v>
+      </c>
+      <c r="AQ11">
+        <v>12</v>
+      </c>
+      <c r="AR11">
+        <v>18</v>
+      </c>
+      <c r="AS11">
+        <v>34</v>
+      </c>
+      <c r="AT11">
+        <v>8.4</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>14</v>
+      </c>
+      <c r="AW11">
+        <v>38</v>
+      </c>
+      <c r="AX11">
+        <v>11.5</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>17</v>
+      </c>
+      <c r="BA11">
+        <v>30</v>
+      </c>
+      <c r="BB11">
+        <v>21</v>
+      </c>
+      <c r="BC11">
+        <v>20</v>
+      </c>
+      <c r="BD11">
+        <v>32</v>
+      </c>
+      <c r="BE11">
+        <v>40</v>
+      </c>
+      <c r="BF11">
+        <v>16</v>
+      </c>
+      <c r="BG11">
+        <v>42</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -355,7 +355,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-19 00:05:49</t>
+    <t>2026-08-19 02:15:14</t>
   </si>
 </sst>
 </file>
@@ -949,22 +949,22 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -973,13 +973,13 @@
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q2">
         <v>3.1</v>
@@ -988,25 +988,25 @@
         <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T2">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V2">
         <v>1.21</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
         <v>46</v>
@@ -1021,7 +1021,7 @@
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE2">
         <v>150</v>
@@ -1039,10 +1039,10 @@
         <v>190</v>
       </c>
       <c r="AJ2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL2">
         <v>100</v>
@@ -1051,25 +1051,25 @@
         <v>410</v>
       </c>
       <c r="AN2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AP2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT2">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1078,37 +1078,37 @@
         <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AY2">
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BA2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB2">
         <v>18.5</v>
       </c>
       <c r="BC2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1191,7 +1191,7 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G3">
         <v>1.81</v>
@@ -1200,7 +1200,7 @@
         <v>4.3</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
         <v>4.2</v>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1433,22 +1433,22 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H4">
         <v>2.44</v>
       </c>
       <c r="I4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J4">
         <v>3.55</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>3.3</v>
       </c>
       <c r="Q5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1917,19 +1917,19 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G6">
         <v>600</v>
       </c>
       <c r="H6">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2404,16 +2404,16 @@
         <v>1.64</v>
       </c>
       <c r="G8">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
         <v>4.7</v>
@@ -2431,10 +2431,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>2.06</v>
       </c>
       <c r="R11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
         <v>3.8</v>
@@ -3190,7 +3190,7 @@
         <v>28</v>
       </c>
       <c r="AA11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB11">
         <v>9.199999999999999</v>
@@ -3205,7 +3205,7 @@
         <v>55</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3232,7 +3232,7 @@
         <v>17.5</v>
       </c>
       <c r="AO11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11">
         <v>12</v>
@@ -3256,7 +3256,7 @@
         <v>14</v>
       </c>
       <c r="AW11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AX11">
         <v>11.5</v>
@@ -3286,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="BG11">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BH11">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -355,7 +355,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-19 02:15:14</t>
+    <t>2026-08-19 04:24:07</t>
   </si>
 </sst>
 </file>
@@ -967,13 +967,13 @@
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
         <v>1.7</v>
@@ -1048,7 +1048,7 @@
         <v>100</v>
       </c>
       <c r="AM2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AN2">
         <v>36</v>
@@ -1111,64 +1111,64 @@
         <v>5.9</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="BI2">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>1.51</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="BQ2">
-        <v>1.54</v>
+        <v>9</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.61</v>
+        <v>13.5</v>
       </c>
       <c r="BT2">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.62</v>
+        <v>15</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.65</v>
+        <v>16</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.61</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
         <v>113</v>
@@ -1194,7 +1194,7 @@
         <v>1.7</v>
       </c>
       <c r="G3">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H3">
         <v>4.3</v>
@@ -1463,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q4">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2159,22 +2159,22 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G7">
         <v>3.35</v>
       </c>
       <c r="H7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I7">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q7">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2649,16 +2649,16 @@
         <v>1.94</v>
       </c>
       <c r="H9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2673,10 +2673,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q9">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2888,19 +2888,19 @@
         <v>4.3</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="I10">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>3.85</v>
       </c>
       <c r="I11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J11">
         <v>3.55</v>
@@ -3154,7 +3154,7 @@
         <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
         <v>1.89</v>
@@ -3163,7 +3163,7 @@
         <v>2.06</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S11">
         <v>3.8</v>
@@ -3205,7 +3205,7 @@
         <v>55</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3217,7 +3217,7 @@
         <v>60</v>
       </c>
       <c r="AJ11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK11">
         <v>24</v>
@@ -3256,7 +3256,7 @@
         <v>14</v>
       </c>
       <c r="AW11">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AX11">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -355,7 +355,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-19 04:24:07</t>
+    <t>2026-08-19 06:33:35</t>
   </si>
 </sst>
 </file>
@@ -2162,19 +2162,19 @@
         <v>2.78</v>
       </c>
       <c r="G7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H7">
         <v>2.3</v>
       </c>
       <c r="I7">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="J7">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         <v>2.48</v>
       </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>2.78</v>
       </c>
       <c r="Q9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         <v>4</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3130,7 +3130,7 @@
         <v>2.14</v>
       </c>
       <c r="G11">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H11">
         <v>3.85</v>
@@ -3163,7 +3163,7 @@
         <v>2.06</v>
       </c>
       <c r="R11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
         <v>3.8</v>
@@ -3205,7 +3205,7 @@
         <v>55</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="121">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
+    <t>Japanese J League</t>
+  </si>
+  <si>
     <t>Danish 1st Division</t>
   </si>
   <si>
@@ -277,6 +280,12 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -298,6 +307,12 @@
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Kashiwa</t>
+  </si>
+  <si>
+    <t>FC Tokyo</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
@@ -328,6 +343,12 @@
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Nagasaki</t>
+  </si>
+  <si>
+    <t>Jef Utd Chiba</t>
+  </si>
+  <si>
     <t>Esbjerg</t>
   </si>
   <si>
@@ -355,7 +376,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-19 06:33:35</t>
+    <t>2026-08-19 08:43:11</t>
   </si>
 </sst>
 </file>
@@ -687,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -937,19 +958,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G2">
         <v>2.08</v>
@@ -967,7 +988,7 @@
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
         <v>1.16</v>
@@ -976,13 +997,13 @@
         <v>2.3</v>
       </c>
       <c r="O2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P2">
         <v>1.42</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
         <v>1.16</v>
@@ -1156,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>15</v>
+        <v>2.12</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1171,7 +1192,7 @@
         <v>14</v>
       </c>
       <c r="CB2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1179,232 +1200,232 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="G3">
+        <v>1.73</v>
+      </c>
+      <c r="H3">
+        <v>5.6</v>
+      </c>
+      <c r="I3">
+        <v>6.4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>4.6</v>
+      </c>
+      <c r="L3">
+        <v>1.29</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>3.85</v>
+      </c>
+      <c r="O3">
+        <v>1.27</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
         <v>1.83</v>
       </c>
-      <c r="H3">
-        <v>4.3</v>
-      </c>
-      <c r="I3">
-        <v>4.9</v>
-      </c>
-      <c r="J3">
-        <v>4.2</v>
-      </c>
-      <c r="K3">
-        <v>5.1</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>2.66</v>
-      </c>
-      <c r="Q3">
-        <v>1.48</v>
-      </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1413,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1421,232 +1442,232 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F4">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="G4">
-        <v>3.05</v>
+        <v>1.6</v>
       </c>
       <c r="H4">
-        <v>2.44</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>2.66</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P4">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="Q4">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1655,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1663,34 +1684,34 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F5">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>1.83</v>
       </c>
       <c r="H5">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="I5">
-        <v>1.35</v>
+        <v>4.9</v>
       </c>
       <c r="J5">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1705,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="Q5">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1897,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1905,34 +1926,34 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F6">
-        <v>1.22</v>
+        <v>2.8</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H6">
-        <v>1.22</v>
+        <v>2.44</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="J6">
-        <v>1.23</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1947,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2139,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2147,52 +2168,52 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>2.78</v>
+        <v>9.6</v>
       </c>
       <c r="G7">
+        <v>13.5</v>
+      </c>
+      <c r="H7">
+        <v>1.28</v>
+      </c>
+      <c r="I7">
+        <v>1.34</v>
+      </c>
+      <c r="J7">
+        <v>6.6</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>3.3</v>
       </c>
-      <c r="H7">
-        <v>2.3</v>
-      </c>
-      <c r="I7">
-        <v>2.6</v>
-      </c>
-      <c r="J7">
-        <v>3.85</v>
-      </c>
-      <c r="K7">
-        <v>4.4</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>2.48</v>
-      </c>
       <c r="Q7">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2381,42 +2402,42 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="G8">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>5.2</v>
+        <v>1.26</v>
       </c>
       <c r="I8">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>1.27</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2431,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2623,42 +2644,42 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>1.76</v>
+        <v>2.78</v>
       </c>
       <c r="G9">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="H9">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2673,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q9">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2865,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2873,34 +2894,34 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F10">
-        <v>4.3</v>
+        <v>1.64</v>
       </c>
       <c r="G10">
-        <v>4.9</v>
+        <v>1.75</v>
       </c>
       <c r="H10">
-        <v>1.75</v>
+        <v>5.2</v>
       </c>
       <c r="I10">
-        <v>1.87</v>
+        <v>5.9</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2915,10 +2936,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q10">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3107,249 +3128,733 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11">
+        <v>1.76</v>
+      </c>
+      <c r="G11">
+        <v>1.94</v>
+      </c>
+      <c r="H11">
+        <v>3.8</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>4.2</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.78</v>
+      </c>
+      <c r="Q11">
+        <v>1.45</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12">
+        <v>4.3</v>
+      </c>
+      <c r="G12">
+        <v>4.9</v>
+      </c>
+      <c r="H12">
+        <v>1.75</v>
+      </c>
+      <c r="I12">
+        <v>1.87</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <v>4.5</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.4</v>
+      </c>
+      <c r="Q12">
+        <v>1.61</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
         <v>85</v>
       </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11">
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13">
         <v>2.14</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>2.16</v>
       </c>
-      <c r="H11">
+      <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I11">
+      <c r="I13">
         <v>3.9</v>
       </c>
-      <c r="J11">
+      <c r="J13">
         <v>3.55</v>
       </c>
-      <c r="K11">
+      <c r="K13">
         <v>3.65</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>1.08</v>
       </c>
-      <c r="N11">
-        <v>3.6</v>
-      </c>
-      <c r="O11">
+      <c r="N13">
+        <v>3.65</v>
+      </c>
+      <c r="O13">
         <v>1.35</v>
       </c>
-      <c r="P11">
+      <c r="P13">
         <v>1.89</v>
       </c>
-      <c r="Q11">
+      <c r="Q13">
         <v>2.06</v>
       </c>
-      <c r="R11">
+      <c r="R13">
         <v>1.33</v>
       </c>
-      <c r="S11">
+      <c r="S13">
         <v>3.8</v>
       </c>
-      <c r="T11">
+      <c r="T13">
         <v>1.86</v>
       </c>
-      <c r="U11">
+      <c r="U13">
         <v>2.1</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>13.5</v>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <v>13.5</v>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <v>28</v>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <v>80</v>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <v>7.8</v>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <v>16</v>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <v>55</v>
       </c>
-      <c r="AF11">
-        <v>12.5</v>
-      </c>
-      <c r="AG11">
+      <c r="AF13">
+        <v>13</v>
+      </c>
+      <c r="AG13">
         <v>11</v>
       </c>
-      <c r="AH11">
+      <c r="AH13">
         <v>20</v>
       </c>
-      <c r="AI11">
+      <c r="AI13">
         <v>60</v>
       </c>
-      <c r="AJ11">
+      <c r="AJ13">
         <v>27</v>
       </c>
-      <c r="AK11">
+      <c r="AK13">
         <v>24</v>
       </c>
-      <c r="AL11">
+      <c r="AL13">
         <v>42</v>
       </c>
-      <c r="AM11">
+      <c r="AM13">
         <v>130</v>
       </c>
-      <c r="AN11">
+      <c r="AN13">
         <v>17.5</v>
       </c>
-      <c r="AO11">
+      <c r="AO13">
         <v>55</v>
       </c>
-      <c r="AP11">
+      <c r="AP13">
         <v>12</v>
       </c>
-      <c r="AQ11">
+      <c r="AQ13">
         <v>12</v>
       </c>
-      <c r="AR11">
+      <c r="AR13">
         <v>18</v>
       </c>
-      <c r="AS11">
+      <c r="AS13">
         <v>34</v>
       </c>
-      <c r="AT11">
+      <c r="AT13">
         <v>8.4</v>
       </c>
-      <c r="AU11">
-        <v>7</v>
-      </c>
-      <c r="AV11">
+      <c r="AU13">
+        <v>7.2</v>
+      </c>
+      <c r="AV13">
         <v>14</v>
       </c>
-      <c r="AW11">
+      <c r="AW13">
         <v>40</v>
       </c>
-      <c r="AX11">
+      <c r="AX13">
         <v>11.5</v>
       </c>
-      <c r="AY11">
+      <c r="AY13">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ11">
+      <c r="AZ13">
         <v>17</v>
       </c>
-      <c r="BA11">
+      <c r="BA13">
         <v>30</v>
       </c>
-      <c r="BB11">
+      <c r="BB13">
         <v>21</v>
       </c>
-      <c r="BC11">
+      <c r="BC13">
         <v>20</v>
       </c>
-      <c r="BD11">
+      <c r="BD13">
         <v>32</v>
       </c>
-      <c r="BE11">
+      <c r="BE13">
         <v>40</v>
       </c>
-      <c r="BF11">
-        <v>16</v>
-      </c>
-      <c r="BG11">
+      <c r="BF13">
+        <v>15.5</v>
+      </c>
+      <c r="BG13">
         <v>28</v>
       </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
         <v>1.04</v>
       </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
         <v>1.04</v>
       </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
         <v>1.04</v>
       </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
         <v>1.04</v>
       </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
         <v>1.04</v>
       </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
         <v>1.04</v>
       </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
         <v>1.04</v>
       </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
         <v>1.04</v>
       </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
         <v>1.04</v>
       </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
         <v>1.04</v>
       </c>
-      <c r="CB11" t="s">
-        <v>113</v>
+      <c r="CB13" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -376,7 +376,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-19 08:43:11</t>
+    <t>2026-08-19 10:51:58</t>
   </si>
 </sst>
 </file>
@@ -970,28 +970,28 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
         <v>2.3</v>
@@ -1000,7 +1000,7 @@
         <v>1.69</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
@@ -1012,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="T2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
         <v>1.57</v>
@@ -1021,13 +1021,13 @@
         <v>1.21</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X2">
         <v>8</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
         <v>46</v>
@@ -1036,10 +1036,10 @@
         <v>220</v>
       </c>
       <c r="AB2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
         <v>28</v>
@@ -1048,10 +1048,10 @@
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
         <v>40</v>
@@ -1060,13 +1060,13 @@
         <v>190</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM2">
         <v>400</v>
@@ -1078,58 +1078,58 @@
         <v>310</v>
       </c>
       <c r="AP2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT2">
         <v>5.1</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX2">
+        <v>8.6</v>
+      </c>
+      <c r="AY2">
         <v>9</v>
       </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
       <c r="AZ2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB2">
         <v>18.5</v>
       </c>
       <c r="BC2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH2">
         <v>2.48</v>
@@ -1460,7 +1460,7 @@
         <v>1.6</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>8.4</v>
@@ -1484,19 +1484,19 @@
         <v>1.3</v>
       </c>
       <c r="P4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U4">
         <v>1.86</v>
@@ -1505,7 +1505,7 @@
         <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1562,52 +1562,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -2180,16 +2180,16 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>1.28</v>
       </c>
       <c r="I7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="J7">
         <v>6.6</v>
@@ -2210,10 +2210,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2422,13 +2422,13 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="G8">
         <v>1000</v>
       </c>
       <c r="H8">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="I8">
         <v>1000</v>
@@ -2667,7 +2667,7 @@
         <v>2.78</v>
       </c>
       <c r="G9">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
         <v>2.3</v>
@@ -2679,7 +2679,7 @@
         <v>3.85</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3151,19 +3151,19 @@
         <v>1.76</v>
       </c>
       <c r="G11">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J11">
         <v>4.2</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q12">
         <v>1.61</v>
@@ -3710,7 +3710,7 @@
         <v>55</v>
       </c>
       <c r="AF13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG13">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="159">
   <si>
     <t>League</t>
   </si>
@@ -262,15 +262,36 @@
     <t>Japanese J League</t>
   </si>
   <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>UAE Arabian Gulf League</t>
+  </si>
+  <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Slovenian Premier League</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
     <t>Danish 1st Division</t>
   </si>
   <si>
-    <t>Saudi Professional League</t>
-  </si>
-  <si>
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>French Ligue 1</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -286,6 +307,18 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -295,12 +328,21 @@
     <t>16:30:00</t>
   </si>
   <si>
+    <t>16:35:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
     <t>18:00:00</t>
   </si>
   <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -313,30 +355,66 @@
     <t>FC Tokyo</t>
   </si>
   <si>
+    <t>Alashkert</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Al-Ittihad Kalba</t>
+  </si>
+  <si>
+    <t>FC Ararat Yerevan</t>
+  </si>
+  <si>
+    <t>FK Auda</t>
+  </si>
+  <si>
+    <t>Liepajas Metalurgs</t>
+  </si>
+  <si>
+    <t>Paks</t>
+  </si>
+  <si>
+    <t>NK Aluminij</t>
+  </si>
+  <si>
+    <t>Al Riyadh SC</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
     <t>Hobro</t>
   </si>
   <si>
-    <t>Al Riyadh SC</t>
-  </si>
-  <si>
     <t>Al-Hazm (KSA)</t>
   </si>
   <si>
     <t>AL Arabi (Qat)</t>
   </si>
   <si>
+    <t>Al Nasr (UAE)</t>
+  </si>
+  <si>
     <t>Fredericia</t>
   </si>
   <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
     <t>Al-Quadisiya (KSA)</t>
   </si>
   <si>
     <t>Al Faisaly ( KSA )</t>
   </si>
   <si>
+    <t>Olimpija</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
     <t>Betis</t>
   </si>
   <si>
@@ -349,34 +427,70 @@
     <t>Jef Utd Chiba</t>
   </si>
   <si>
+    <t>FC Gandzasar</t>
+  </si>
+  <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
+    <t>Al Wasl</t>
+  </si>
+  <si>
+    <t>FC Pyunik</t>
+  </si>
+  <si>
+    <t>FK Tukums 2000</t>
+  </si>
+  <si>
+    <t>SC Grobina</t>
+  </si>
+  <si>
+    <t>Ujpest</t>
+  </si>
+  <si>
+    <t>NK Brinje Grosuplje</t>
+  </si>
+  <si>
+    <t>Al Nassr</t>
+  </si>
+  <si>
     <t>Esbjerg</t>
   </si>
   <si>
     <t>AaB</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Al Draih</t>
   </si>
   <si>
     <t>AL Shamal</t>
   </si>
   <si>
+    <t>Al Wahda (Abu Dhabi)</t>
+  </si>
+  <si>
     <t>Aarhus Fremad</t>
   </si>
   <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
     <t>Al-Ittihad</t>
   </si>
   <si>
     <t>NEOM Sports Club</t>
   </si>
   <si>
+    <t>Nafta Lendava</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-19 10:51:58</t>
+    <t>2026-08-19 13:01:38</t>
   </si>
 </sst>
 </file>
@@ -708,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -958,25 +1072,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I2">
         <v>5.7</v>
@@ -985,25 +1099,25 @@
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O2">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1.16</v>
@@ -1021,7 +1135,7 @@
         <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
         <v>8</v>
@@ -1093,7 +1207,7 @@
         <v>5.1</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
         <v>18.5</v>
@@ -1114,7 +1228,7 @@
         <v>6.2</v>
       </c>
       <c r="BB2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC2">
         <v>5.5</v>
@@ -1192,7 +1306,7 @@
         <v>14</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1200,16 +1314,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="F3">
         <v>1.66</v>
@@ -1227,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.29</v>
@@ -1326,22 +1440,22 @@
         <v>1.28</v>
       </c>
       <c r="AR3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AS3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AT3">
-        <v>1.15</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>1.28</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>1.28</v>
       </c>
       <c r="AW3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AX3">
         <v>7.2</v>
@@ -1353,25 +1467,25 @@
         <v>1.28</v>
       </c>
       <c r="BA3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BB3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BC3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BD3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BE3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BG3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1383,49 +1497,49 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1434,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1442,19 +1556,19 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G4">
         <v>1.6</v>
@@ -1478,16 +1592,16 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
         <v>1.31</v>
@@ -1619,55 +1733,55 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1676,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1684,716 +1798,716 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F5">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="G5">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="F6">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="G6">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="H6">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="I6">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>2.98</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="Q6">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>6.6</v>
+      </c>
+      <c r="H7">
+        <v>1.59</v>
+      </c>
+      <c r="I7">
+        <v>1.72</v>
+      </c>
+      <c r="J7">
+        <v>3.95</v>
+      </c>
+      <c r="K7">
+        <v>5.1</v>
+      </c>
+      <c r="L7">
+        <v>1.25</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>5.2</v>
+      </c>
+      <c r="O7">
+        <v>1.19</v>
+      </c>
+      <c r="P7">
+        <v>2.44</v>
+      </c>
+      <c r="Q7">
+        <v>1.56</v>
+      </c>
+      <c r="R7">
+        <v>1.57</v>
+      </c>
+      <c r="S7">
+        <v>2.38</v>
+      </c>
+      <c r="T7">
+        <v>1.65</v>
+      </c>
+      <c r="U7">
+        <v>2.26</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>29</v>
+      </c>
+      <c r="Y7">
+        <v>14</v>
+      </c>
+      <c r="Z7">
+        <v>14</v>
+      </c>
+      <c r="AA7">
+        <v>19.5</v>
+      </c>
+      <c r="AB7">
+        <v>29</v>
+      </c>
+      <c r="AC7">
+        <v>12.5</v>
+      </c>
+      <c r="AD7">
+        <v>12</v>
+      </c>
+      <c r="AE7">
+        <v>18.5</v>
+      </c>
+      <c r="AF7">
+        <v>55</v>
+      </c>
+      <c r="AG7">
+        <v>25</v>
+      </c>
+      <c r="AH7">
+        <v>21</v>
+      </c>
+      <c r="AI7">
+        <v>32</v>
+      </c>
+      <c r="AJ7">
+        <v>140</v>
+      </c>
+      <c r="AK7">
+        <v>70</v>
+      </c>
+      <c r="AL7">
+        <v>65</v>
+      </c>
+      <c r="AM7">
         <v>90</v>
       </c>
-      <c r="D7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7">
+      <c r="AN7">
+        <v>65</v>
+      </c>
+      <c r="AO7">
+        <v>8</v>
+      </c>
+      <c r="AP7">
+        <v>18.5</v>
+      </c>
+      <c r="AQ7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS7">
+        <v>12.5</v>
+      </c>
+      <c r="AT7">
+        <v>19</v>
+      </c>
+      <c r="AU7">
+        <v>8.4</v>
+      </c>
+      <c r="AV7">
+        <v>8</v>
+      </c>
+      <c r="AW7">
+        <v>12</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>16</v>
+      </c>
+      <c r="AZ7">
+        <v>14</v>
+      </c>
+      <c r="BA7">
+        <v>20</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>5.4</v>
+      </c>
+      <c r="BH7">
+        <v>4.5</v>
+      </c>
+      <c r="BI7">
+        <v>3.55</v>
+      </c>
+      <c r="BJ7">
         <v>9.800000000000001</v>
       </c>
-      <c r="G7">
-        <v>14</v>
-      </c>
-      <c r="H7">
-        <v>1.28</v>
-      </c>
-      <c r="I7">
-        <v>1.33</v>
-      </c>
-      <c r="J7">
-        <v>6.6</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>3.35</v>
-      </c>
-      <c r="Q7">
-        <v>1.34</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7">
-        <v>0</v>
-      </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-      <c r="BF7">
-        <v>0</v>
-      </c>
-      <c r="BG7">
-        <v>0</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
       <c r="BK7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2402,482 +2516,482 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F8">
-        <v>1.86</v>
+        <v>2.94</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H8">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>1.52</v>
       </c>
       <c r="J8">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="F9">
-        <v>2.78</v>
+        <v>1.3</v>
       </c>
       <c r="G9">
-        <v>3.1</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="I9">
-        <v>2.6</v>
+        <v>870</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -2886,482 +3000,482 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="F10">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.75</v>
+        <v>3.8</v>
       </c>
       <c r="H10">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="I10">
-        <v>5.9</v>
+        <v>870</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="F11">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="G11">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="H11">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P11">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q11">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3370,240 +3484,240 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F12">
+        <v>2.32</v>
+      </c>
+      <c r="G12">
+        <v>2.6</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>3.55</v>
+      </c>
+      <c r="J12">
+        <v>3.3</v>
+      </c>
+      <c r="K12">
         <v>4.3</v>
       </c>
-      <c r="G12">
-        <v>4.9</v>
-      </c>
-      <c r="H12">
-        <v>1.75</v>
-      </c>
-      <c r="I12">
-        <v>1.87</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-      <c r="K12">
-        <v>4.5</v>
-      </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="Q12">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3612,249 +3726,3153 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G13">
+        <v>13.5</v>
+      </c>
+      <c r="H13">
+        <v>1.27</v>
+      </c>
+      <c r="I13">
+        <v>1.33</v>
+      </c>
+      <c r="J13">
+        <v>6.6</v>
+      </c>
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>3.5</v>
+      </c>
+      <c r="Q13">
+        <v>1.32</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14">
+        <v>1.7</v>
+      </c>
+      <c r="G14">
+        <v>1.83</v>
+      </c>
+      <c r="H14">
+        <v>4.3</v>
+      </c>
+      <c r="I14">
+        <v>4.9</v>
+      </c>
+      <c r="J14">
+        <v>4.2</v>
+      </c>
+      <c r="K14">
+        <v>5.1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.7</v>
+      </c>
+      <c r="Q14">
+        <v>1.48</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15">
+        <v>2.8</v>
+      </c>
+      <c r="G15">
+        <v>3.05</v>
+      </c>
+      <c r="H15">
+        <v>2.44</v>
+      </c>
+      <c r="I15">
+        <v>2.66</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>3.95</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>2.14</v>
+      </c>
+      <c r="Q15">
+        <v>1.77</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16">
+        <v>2.92</v>
+      </c>
+      <c r="G16">
+        <v>3.95</v>
+      </c>
+      <c r="H16">
+        <v>2.04</v>
+      </c>
+      <c r="I16">
+        <v>2.68</v>
+      </c>
+      <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>6</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.99</v>
+      </c>
+      <c r="Q16">
+        <v>1.58</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17">
+        <v>2.78</v>
+      </c>
+      <c r="G17">
+        <v>3.3</v>
+      </c>
+      <c r="H17">
+        <v>2.3</v>
+      </c>
+      <c r="I17">
+        <v>2.54</v>
+      </c>
+      <c r="J17">
+        <v>3.85</v>
+      </c>
+      <c r="K17">
+        <v>4.4</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.48</v>
+      </c>
+      <c r="Q17">
+        <v>1.56</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18">
+        <v>3.45</v>
+      </c>
+      <c r="G18">
+        <v>3.9</v>
+      </c>
+      <c r="H18">
+        <v>2.06</v>
+      </c>
+      <c r="I18">
+        <v>2.24</v>
+      </c>
+      <c r="J18">
+        <v>3.55</v>
+      </c>
+      <c r="K18">
+        <v>4.2</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>2.12</v>
+      </c>
+      <c r="Q18">
+        <v>1.7</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19">
+        <v>1.64</v>
+      </c>
+      <c r="G19">
+        <v>1.75</v>
+      </c>
+      <c r="H19">
+        <v>5.2</v>
+      </c>
+      <c r="I19">
+        <v>5.9</v>
+      </c>
+      <c r="J19">
+        <v>4.1</v>
+      </c>
+      <c r="K19">
+        <v>4.7</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2.26</v>
+      </c>
+      <c r="Q19">
+        <v>1.57</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20">
+        <v>1.53</v>
+      </c>
+      <c r="G20">
+        <v>1.67</v>
+      </c>
+      <c r="H20">
+        <v>7.6</v>
+      </c>
+      <c r="I20">
+        <v>10.5</v>
+      </c>
+      <c r="J20">
+        <v>3.35</v>
+      </c>
+      <c r="K20">
+        <v>4.7</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1.55</v>
+      </c>
+      <c r="Q20">
+        <v>2.34</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21">
+        <v>1.74</v>
+      </c>
+      <c r="G21">
+        <v>1.92</v>
+      </c>
+      <c r="H21">
+        <v>3.9</v>
+      </c>
+      <c r="I21">
+        <v>5.1</v>
+      </c>
+      <c r="J21">
+        <v>4.2</v>
+      </c>
+      <c r="K21">
+        <v>5.1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.78</v>
+      </c>
+      <c r="Q21">
+        <v>1.45</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22">
+        <v>4.3</v>
+      </c>
+      <c r="G22">
+        <v>4.9</v>
+      </c>
+      <c r="H22">
+        <v>1.75</v>
+      </c>
+      <c r="I22">
+        <v>1.87</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4.7</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.36</v>
+      </c>
+      <c r="Q22">
+        <v>1.61</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
         <v>107</v>
       </c>
-      <c r="E13" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13">
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.24</v>
+      </c>
+      <c r="Q23">
+        <v>1.01</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24">
+        <v>1.77</v>
+      </c>
+      <c r="G24">
+        <v>1.8</v>
+      </c>
+      <c r="H24">
+        <v>4.6</v>
+      </c>
+      <c r="I24">
+        <v>4.9</v>
+      </c>
+      <c r="J24">
+        <v>4.3</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.04</v>
+      </c>
+      <c r="N24">
+        <v>5.7</v>
+      </c>
+      <c r="O24">
+        <v>1.19</v>
+      </c>
+      <c r="P24">
+        <v>2.62</v>
+      </c>
+      <c r="Q24">
+        <v>1.59</v>
+      </c>
+      <c r="R24">
+        <v>1.65</v>
+      </c>
+      <c r="S24">
+        <v>2.44</v>
+      </c>
+      <c r="T24">
+        <v>1.61</v>
+      </c>
+      <c r="U24">
+        <v>2.52</v>
+      </c>
+      <c r="V24">
+        <v>1.26</v>
+      </c>
+      <c r="W24">
+        <v>2.24</v>
+      </c>
+      <c r="X24">
+        <v>25</v>
+      </c>
+      <c r="Y24">
+        <v>24</v>
+      </c>
+      <c r="Z24">
+        <v>40</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>13</v>
+      </c>
+      <c r="AC24">
+        <v>10</v>
+      </c>
+      <c r="AD24">
+        <v>19.5</v>
+      </c>
+      <c r="AE24">
+        <v>170</v>
+      </c>
+      <c r="AF24">
+        <v>13.5</v>
+      </c>
+      <c r="AG24">
+        <v>10.5</v>
+      </c>
+      <c r="AH24">
+        <v>16.5</v>
+      </c>
+      <c r="AI24">
+        <v>160</v>
+      </c>
+      <c r="AJ24">
+        <v>20</v>
+      </c>
+      <c r="AK24">
+        <v>16.5</v>
+      </c>
+      <c r="AL24">
+        <v>29</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>7.4</v>
+      </c>
+      <c r="AO24">
+        <v>38</v>
+      </c>
+      <c r="AP24">
+        <v>21</v>
+      </c>
+      <c r="AQ24">
+        <v>21</v>
+      </c>
+      <c r="AR24">
+        <v>32</v>
+      </c>
+      <c r="AS24">
+        <v>38</v>
+      </c>
+      <c r="AT24">
+        <v>11.5</v>
+      </c>
+      <c r="AU24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV24">
+        <v>17</v>
+      </c>
+      <c r="AW24">
+        <v>26</v>
+      </c>
+      <c r="AX24">
+        <v>11.5</v>
+      </c>
+      <c r="AY24">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24">
+        <v>14.5</v>
+      </c>
+      <c r="BA24">
+        <v>26</v>
+      </c>
+      <c r="BB24">
+        <v>17.5</v>
+      </c>
+      <c r="BC24">
+        <v>14.5</v>
+      </c>
+      <c r="BD24">
+        <v>19</v>
+      </c>
+      <c r="BE24">
+        <v>30</v>
+      </c>
+      <c r="BF24">
+        <v>6.8</v>
+      </c>
+      <c r="BG24">
+        <v>30</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.04</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.04</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.04</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.04</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.04</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.04</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.04</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25">
         <v>2.14</v>
       </c>
-      <c r="G13">
-        <v>2.16</v>
-      </c>
-      <c r="H13">
-        <v>3.85</v>
-      </c>
-      <c r="I13">
+      <c r="G25">
+        <v>2.18</v>
+      </c>
+      <c r="H25">
+        <v>3.8</v>
+      </c>
+      <c r="I25">
         <v>3.9</v>
       </c>
-      <c r="J13">
+      <c r="J25">
         <v>3.55</v>
       </c>
-      <c r="K13">
+      <c r="K25">
         <v>3.65</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>1.08</v>
       </c>
-      <c r="N13">
+      <c r="N25">
         <v>3.65</v>
       </c>
-      <c r="O13">
+      <c r="O25">
         <v>1.35</v>
       </c>
-      <c r="P13">
+      <c r="P25">
         <v>1.89</v>
       </c>
-      <c r="Q13">
+      <c r="Q25">
         <v>2.06</v>
       </c>
-      <c r="R13">
+      <c r="R25">
         <v>1.33</v>
       </c>
-      <c r="S13">
-        <v>3.8</v>
-      </c>
-      <c r="T13">
+      <c r="S25">
+        <v>3.75</v>
+      </c>
+      <c r="T25">
         <v>1.86</v>
       </c>
-      <c r="U13">
-        <v>2.1</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
+      <c r="U25">
+        <v>2.12</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
         <v>13.5</v>
       </c>
-      <c r="Y13">
+      <c r="Y25">
         <v>13.5</v>
       </c>
-      <c r="Z13">
+      <c r="Z25">
+        <v>26</v>
+      </c>
+      <c r="AA25">
+        <v>80</v>
+      </c>
+      <c r="AB25">
+        <v>9.4</v>
+      </c>
+      <c r="AC25">
+        <v>7.8</v>
+      </c>
+      <c r="AD25">
+        <v>16</v>
+      </c>
+      <c r="AE25">
+        <v>55</v>
+      </c>
+      <c r="AF25">
+        <v>13</v>
+      </c>
+      <c r="AG25">
+        <v>11</v>
+      </c>
+      <c r="AH25">
+        <v>20</v>
+      </c>
+      <c r="AI25">
+        <v>60</v>
+      </c>
+      <c r="AJ25">
+        <v>27</v>
+      </c>
+      <c r="AK25">
+        <v>24</v>
+      </c>
+      <c r="AL25">
+        <v>42</v>
+      </c>
+      <c r="AM25">
+        <v>120</v>
+      </c>
+      <c r="AN25">
+        <v>17.5</v>
+      </c>
+      <c r="AO25">
+        <v>55</v>
+      </c>
+      <c r="AP25">
+        <v>12</v>
+      </c>
+      <c r="AQ25">
+        <v>12</v>
+      </c>
+      <c r="AR25">
+        <v>17.5</v>
+      </c>
+      <c r="AS25">
+        <v>34</v>
+      </c>
+      <c r="AT25">
+        <v>8.6</v>
+      </c>
+      <c r="AU25">
+        <v>7.2</v>
+      </c>
+      <c r="AV25">
+        <v>13.5</v>
+      </c>
+      <c r="AW25">
+        <v>40</v>
+      </c>
+      <c r="AX25">
+        <v>11.5</v>
+      </c>
+      <c r="AY25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ25">
+        <v>17</v>
+      </c>
+      <c r="BA25">
+        <v>30</v>
+      </c>
+      <c r="BB25">
+        <v>21</v>
+      </c>
+      <c r="BC25">
+        <v>20</v>
+      </c>
+      <c r="BD25">
+        <v>32</v>
+      </c>
+      <c r="BE25">
+        <v>40</v>
+      </c>
+      <c r="BF25">
+        <v>15.5</v>
+      </c>
+      <c r="BG25">
         <v>28</v>
       </c>
-      <c r="AA13">
-        <v>80</v>
-      </c>
-      <c r="AB13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC13">
-        <v>7.8</v>
-      </c>
-      <c r="AD13">
-        <v>16</v>
-      </c>
-      <c r="AE13">
-        <v>55</v>
-      </c>
-      <c r="AF13">
-        <v>12.5</v>
-      </c>
-      <c r="AG13">
-        <v>11</v>
-      </c>
-      <c r="AH13">
-        <v>20</v>
-      </c>
-      <c r="AI13">
-        <v>60</v>
-      </c>
-      <c r="AJ13">
-        <v>27</v>
-      </c>
-      <c r="AK13">
-        <v>24</v>
-      </c>
-      <c r="AL13">
-        <v>42</v>
-      </c>
-      <c r="AM13">
-        <v>130</v>
-      </c>
-      <c r="AN13">
-        <v>17.5</v>
-      </c>
-      <c r="AO13">
-        <v>55</v>
-      </c>
-      <c r="AP13">
-        <v>12</v>
-      </c>
-      <c r="AQ13">
-        <v>12</v>
-      </c>
-      <c r="AR13">
-        <v>18</v>
-      </c>
-      <c r="AS13">
-        <v>34</v>
-      </c>
-      <c r="AT13">
-        <v>8.4</v>
-      </c>
-      <c r="AU13">
-        <v>7.2</v>
-      </c>
-      <c r="AV13">
-        <v>14</v>
-      </c>
-      <c r="AW13">
-        <v>40</v>
-      </c>
-      <c r="AX13">
-        <v>11.5</v>
-      </c>
-      <c r="AY13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ13">
-        <v>17</v>
-      </c>
-      <c r="BA13">
-        <v>30</v>
-      </c>
-      <c r="BB13">
-        <v>21</v>
-      </c>
-      <c r="BC13">
-        <v>20</v>
-      </c>
-      <c r="BD13">
-        <v>32</v>
-      </c>
-      <c r="BE13">
-        <v>40</v>
-      </c>
-      <c r="BF13">
-        <v>15.5</v>
-      </c>
-      <c r="BG13">
-        <v>28</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
         <v>1.04</v>
       </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
         <v>1.04</v>
       </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
         <v>1.04</v>
       </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
         <v>1.04</v>
       </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
         <v>1.04</v>
       </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
         <v>1.04</v>
       </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
         <v>1.04</v>
       </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
         <v>1.04</v>
       </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
         <v>1.04</v>
       </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
         <v>1.04</v>
       </c>
-      <c r="CB13" t="s">
-        <v>120</v>
+      <c r="CB25" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="321">
   <si>
     <t>League</t>
   </si>
@@ -334,12 +334,12 @@
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
     <t>Bosnian Premier League</t>
   </si>
   <si>
-    <t>Dutch Eerste Divisie</t>
-  </si>
-  <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
@@ -355,12 +355,12 @@
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
+    <t>Welsh Premiership</t>
+  </si>
+  <si>
     <t>Irish Premier Division</t>
   </si>
   <si>
-    <t>Welsh Premiership</t>
-  </si>
-  <si>
     <t>Irish Division 1</t>
   </si>
   <si>
@@ -385,6 +385,9 @@
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
     <t>2026-08-21</t>
   </si>
   <si>
@@ -598,27 +601,27 @@
     <t>Boulogne</t>
   </si>
   <si>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>Den Bosch</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>Vitesse Arnhem</t>
+  </si>
+  <si>
+    <t>MVV Maastricht</t>
+  </si>
+  <si>
     <t>Sarajevo</t>
   </si>
   <si>
-    <t>Helmond Sport</t>
-  </si>
-  <si>
-    <t>Den Bosch</t>
-  </si>
-  <si>
-    <t>FC Dordrecht</t>
-  </si>
-  <si>
-    <t>Vitesse Arnhem</t>
-  </si>
-  <si>
-    <t>MVV Maastricht</t>
-  </si>
-  <si>
-    <t>Emmen</t>
-  </si>
-  <si>
     <t>Dunkerque</t>
   </si>
   <si>
@@ -643,30 +646,30 @@
     <t>Lechia Gdansk</t>
   </si>
   <si>
+    <t>Colwyn Bay</t>
+  </si>
+  <si>
+    <t>Cardiff Metropolitan</t>
+  </si>
+  <si>
+    <t>Flint Town United</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Cardiff Metropolitan</t>
-  </si>
-  <si>
-    <t>Flint Town United</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Colwyn Bay</t>
-  </si>
-  <si>
     <t>Drogheda</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Kerry FC</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>Finn Harps</t>
   </si>
   <si>
@@ -700,15 +703,18 @@
     <t>Albion FC</t>
   </si>
   <si>
+    <t>Grotta</t>
+  </si>
+  <si>
     <t>Tondela</t>
   </si>
   <si>
-    <t>Grotta</t>
-  </si>
-  <si>
     <t>Alianza Atletico</t>
   </si>
   <si>
+    <t>Academia Anzoategui FC</t>
+  </si>
+  <si>
     <t>Rosario Central</t>
   </si>
   <si>
@@ -856,27 +862,27 @@
     <t>Red Star</t>
   </si>
   <si>
+    <t>Jong AZ Alkmaar</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>Almere City</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
     <t>FK BSK Banja Luka</t>
   </si>
   <si>
-    <t>RKC Waalwijk</t>
-  </si>
-  <si>
-    <t>FC Eindhoven</t>
-  </si>
-  <si>
-    <t>Roda JC</t>
-  </si>
-  <si>
-    <t>Almere City</t>
-  </si>
-  <si>
-    <t>FC Volendam</t>
-  </si>
-  <si>
-    <t>Jong AZ Alkmaar</t>
-  </si>
-  <si>
     <t>Montpellier</t>
   </si>
   <si>
@@ -901,30 +907,30 @@
     <t>Pogon Siedlce</t>
   </si>
   <si>
+    <t>Airbus UK Broughton</t>
+  </si>
+  <si>
+    <t>The New Saints</t>
+  </si>
+  <si>
+    <t>Briton Ferry Llansawel</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
     <t>Galway Utd</t>
   </si>
   <si>
-    <t>The New Saints</t>
-  </si>
-  <si>
-    <t>Briton Ferry Llansawel</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Airbus UK Broughton</t>
-  </si>
-  <si>
     <t>St Patricks</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
@@ -958,16 +964,19 @@
     <t>Boston River</t>
   </si>
   <si>
+    <t>IR Reykjavik</t>
+  </si>
+  <si>
     <t>Academica</t>
   </si>
   <si>
-    <t>IR Reykjavik</t>
-  </si>
-  <si>
     <t>Sporting Cristal</t>
   </si>
   <si>
-    <t>2026-08-19 17:25:47</t>
+    <t>Trujillanos</t>
+  </si>
+  <si>
+    <t>2026-08-19 19:39:32</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB87"/>
+  <dimension ref="A1:CB88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1549,22 +1558,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H2">
         <v>5.1</v>
@@ -1603,7 +1612,7 @@
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U2">
         <v>1.57</v>
@@ -1612,13 +1621,13 @@
         <v>1.21</v>
       </c>
       <c r="W2">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
         <v>7.4</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
         <v>42</v>
@@ -1675,13 +1684,13 @@
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AT2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
@@ -1690,7 +1699,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX2">
         <v>8.800000000000001</v>
@@ -1699,28 +1708,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA2">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB2">
         <v>21</v>
       </c>
       <c r="BC2">
+        <v>8</v>
+      </c>
+      <c r="BD2">
+        <v>9.4</v>
+      </c>
+      <c r="BE2">
+        <v>4.3</v>
+      </c>
+      <c r="BF2">
         <v>7.8</v>
       </c>
-      <c r="BD2">
-        <v>9</v>
-      </c>
-      <c r="BE2">
+      <c r="BG2">
         <v>4.2</v>
-      </c>
-      <c r="BF2">
-        <v>7.6</v>
-      </c>
-      <c r="BG2">
-        <v>5.9</v>
       </c>
       <c r="BH2">
         <v>2.48</v>
@@ -1738,16 +1747,16 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BN2">
         <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2">
         <v>9</v>
@@ -1762,7 +1771,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1774,16 +1783,16 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1791,16 +1800,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F3">
         <v>1.66</v>
@@ -1812,13 +1821,13 @@
         <v>5.6</v>
       </c>
       <c r="I3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.29</v>
@@ -1851,7 +1860,7 @@
         <v>1.96</v>
       </c>
       <c r="V3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
         <v>2.36</v>
@@ -1860,34 +1869,34 @@
         <v>22</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI3">
         <v>100</v>
@@ -1914,13 +1923,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ3">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="AR3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AS3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1929,40 +1938,40 @@
         <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="AW3">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="AX3">
         <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ3">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="BA3">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="BB3">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="BC3">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="BD3">
-        <v>1.31</v>
+        <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>1.35</v>
+        <v>20</v>
       </c>
       <c r="BF3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BG3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2025,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -2033,16 +2042,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F4">
         <v>1.52</v>
@@ -2054,7 +2063,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>4.2</v>
@@ -2069,16 +2078,16 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R4">
         <v>1.31</v>
@@ -2093,55 +2102,55 @@
         <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
         <v>2.66</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4">
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -2153,58 +2162,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2267,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2275,16 +2284,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F5">
         <v>1.33</v>
@@ -2509,7 +2518,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2517,16 +2526,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F6">
         <v>2.34</v>
@@ -2607,7 +2616,7 @@
         <v>70</v>
       </c>
       <c r="AF6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG6">
         <v>14.5</v>
@@ -2637,7 +2646,7 @@
         <v>95</v>
       </c>
       <c r="AP6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6">
         <v>7.8</v>
@@ -2646,7 +2655,7 @@
         <v>18</v>
       </c>
       <c r="AS6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT6">
         <v>5.8</v>
@@ -2658,7 +2667,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2682,7 +2691,7 @@
         <v>4.2</v>
       </c>
       <c r="BE6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF6">
         <v>4</v>
@@ -2751,7 +2760,7 @@
         <v>4.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2759,16 +2768,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2777,7 +2786,7 @@
         <v>6.6</v>
       </c>
       <c r="H7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I7">
         <v>1.72</v>
@@ -2816,7 +2825,7 @@
         <v>1.64</v>
       </c>
       <c r="U7">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2879,7 +2888,7 @@
         <v>8</v>
       </c>
       <c r="AP7">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7">
         <v>9.199999999999999</v>
@@ -2993,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -3001,16 +3010,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F8">
         <v>1.92</v>
@@ -3235,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3243,16 +3252,16 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F9">
         <v>7.2</v>
@@ -3282,7 +3291,7 @@
         <v>3.85</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
         <v>2.08</v>
@@ -3477,7 +3486,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3485,19 +3494,19 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="G10">
         <v>1.65</v>
@@ -3521,13 +3530,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O10">
         <v>1.19</v>
       </c>
       <c r="P10">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q10">
         <v>1.18</v>
@@ -3536,7 +3545,7 @@
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3545,7 +3554,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
         <v>2.52</v>
@@ -3719,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3727,31 +3736,31 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F11">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3763,13 +3772,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q11">
         <v>1.18</v>
@@ -3790,7 +3799,7 @@
         <v>1.02</v>
       </c>
       <c r="W11">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3961,7 +3970,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3969,16 +3978,16 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F12">
         <v>2.32</v>
@@ -4203,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -4211,16 +4220,16 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F13">
         <v>1.91</v>
@@ -4256,10 +4265,10 @@
         <v>2.84</v>
       </c>
       <c r="Q13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R13">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S13">
         <v>1.89</v>
@@ -4274,7 +4283,7 @@
         <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4445,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4453,31 +4462,31 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G14">
         <v>990</v>
       </c>
       <c r="H14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4489,16 +4498,16 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O14">
         <v>1.24</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="R14">
         <v>1.18</v>
@@ -4513,10 +4522,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4687,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4695,16 +4704,16 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F15">
         <v>2.06</v>
@@ -4815,58 +4824,58 @@
         <v>44</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH15">
         <v>4.3</v>
@@ -4929,7 +4938,7 @@
         <v>4</v>
       </c>
       <c r="CB15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4937,22 +4946,22 @@
         <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F16">
         <v>2.62</v>
       </c>
       <c r="G16">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="H16">
         <v>2.12</v>
@@ -5000,7 +5009,7 @@
         <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5171,7 +5180,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -5179,16 +5188,16 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F17">
         <v>1.62</v>
@@ -5206,7 +5215,7 @@
         <v>3.55</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5227,7 +5236,7 @@
         <v>1.58</v>
       </c>
       <c r="R17">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S17">
         <v>2.74</v>
@@ -5413,7 +5422,7 @@
         <v>1.28</v>
       </c>
       <c r="CB17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5421,16 +5430,16 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E18" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F18">
         <v>1.37</v>
@@ -5655,7 +5664,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5663,22 +5672,22 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F19">
         <v>2.1</v>
       </c>
       <c r="G19">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="H19">
         <v>2.46</v>
@@ -5726,7 +5735,7 @@
         <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5897,7 +5906,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5905,16 +5914,16 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F20">
         <v>1.99</v>
@@ -6139,7 +6148,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -6147,19 +6156,19 @@
         <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G21">
         <v>1.8</v>
@@ -6180,7 +6189,7 @@
         <v>1.22</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
         <v>5.9</v>
@@ -6189,10 +6198,10 @@
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R21">
         <v>1.66</v>
@@ -6213,7 +6222,7 @@
         <v>2.24</v>
       </c>
       <c r="X21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y21">
         <v>30</v>
@@ -6273,10 +6282,10 @@
         <v>20</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT21">
         <v>12</v>
@@ -6312,13 +6321,13 @@
         <v>21</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF21">
         <v>6</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH21">
         <v>5.6</v>
@@ -6381,7 +6390,7 @@
         <v>3.5</v>
       </c>
       <c r="CB21" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6389,16 +6398,16 @@
         <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F22">
         <v>2.8</v>
@@ -6425,7 +6434,7 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
         <v>1.23</v>
@@ -6623,7 +6632,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6631,16 +6640,16 @@
         <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F23">
         <v>1.12</v>
@@ -6673,7 +6682,7 @@
         <v>1.08</v>
       </c>
       <c r="P23">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q23">
         <v>1.08</v>
@@ -6865,7 +6874,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6873,16 +6882,16 @@
         <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E24" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F24">
         <v>2.62</v>
@@ -7107,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -7115,16 +7124,16 @@
         <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F25">
         <v>9.800000000000001</v>
@@ -7139,7 +7148,7 @@
         <v>1.33</v>
       </c>
       <c r="J25">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K25">
         <v>9.199999999999999</v>
@@ -7169,13 +7178,13 @@
         <v>1.8</v>
       </c>
       <c r="T25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U25">
         <v>2.18</v>
       </c>
       <c r="V25">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="W25">
         <v>1.09</v>
@@ -7349,7 +7358,7 @@
         <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7357,16 +7366,16 @@
         <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F26">
         <v>3.2</v>
@@ -7591,7 +7600,7 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7599,16 +7608,16 @@
         <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F27">
         <v>2.78</v>
@@ -7623,7 +7632,7 @@
         <v>2.54</v>
       </c>
       <c r="J27">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K27">
         <v>4.3</v>
@@ -7659,10 +7668,10 @@
         <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7833,7 +7842,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7841,16 +7850,16 @@
         <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F28">
         <v>3.45</v>
@@ -8075,7 +8084,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -8083,58 +8092,58 @@
         <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E29" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F29">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="G29">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I29">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J29">
+        <v>4.4</v>
+      </c>
+      <c r="K29">
         <v>4.5</v>
       </c>
-      <c r="K29">
-        <v>4.6</v>
-      </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N29">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R29">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="S29">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="T29">
         <v>1.41</v>
@@ -8143,16 +8152,16 @@
         <v>2.52</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X29">
         <v>42</v>
       </c>
       <c r="Y29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z29">
         <v>44</v>
@@ -8164,46 +8173,46 @@
         <v>18</v>
       </c>
       <c r="AC29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD29">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE29">
         <v>44</v>
       </c>
       <c r="AF29">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG29">
         <v>12</v>
       </c>
       <c r="AH29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI29">
         <v>42</v>
       </c>
       <c r="AJ29">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK29">
         <v>18</v>
       </c>
       <c r="AL29">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AM29">
         <v>65</v>
       </c>
       <c r="AN29">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AO29">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ29">
         <v>16.5</v>
@@ -8212,7 +8221,7 @@
         <v>28</v>
       </c>
       <c r="AS29">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT29">
         <v>15</v>
@@ -8251,10 +8260,10 @@
         <v>32</v>
       </c>
       <c r="BF29">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG29">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8317,7 +8326,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8325,16 +8334,16 @@
         <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F30">
         <v>1.81</v>
@@ -8358,7 +8367,7 @@
         <v>1.31</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
         <v>3.45</v>
@@ -8559,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8567,19 +8576,19 @@
         <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F31">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="G31">
         <v>2.3</v>
@@ -8594,7 +8603,7 @@
         <v>3.15</v>
       </c>
       <c r="K31">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8618,7 +8627,7 @@
         <v>1.24</v>
       </c>
       <c r="S31">
-        <v>2.84</v>
+        <v>1.05</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8744,64 +8753,64 @@
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8809,16 +8818,16 @@
         <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F32">
         <v>4.6</v>
@@ -8845,10 +8854,10 @@
         <v>1.12</v>
       </c>
       <c r="N32">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O32">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P32">
         <v>1.43</v>
@@ -9043,7 +9052,7 @@
         <v>1.53</v>
       </c>
       <c r="CB32" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -9051,34 +9060,34 @@
         <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F33">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="G33">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="H33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="J33">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K33">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -9087,7 +9096,7 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O33">
         <v>1.01</v>
@@ -9111,10 +9120,10 @@
         <v>1.11</v>
       </c>
       <c r="V33">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W33">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9285,7 +9294,7 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9293,16 +9302,16 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F34">
         <v>1.52</v>
@@ -9527,7 +9536,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9535,16 +9544,16 @@
         <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F35">
         <v>2.62</v>
@@ -9769,7 +9778,7 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9777,16 +9786,16 @@
         <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F36">
         <v>2.6</v>
@@ -10011,7 +10020,7 @@
         <v>1.04</v>
       </c>
       <c r="CB36" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -10019,16 +10028,16 @@
         <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F37">
         <v>1.64</v>
@@ -10061,10 +10070,10 @@
         <v>1.23</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q37">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R37">
         <v>1.5</v>
@@ -10082,7 +10091,7 @@
         <v>1.2</v>
       </c>
       <c r="W37">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X37">
         <v>25</v>
@@ -10145,10 +10154,10 @@
         <v>16</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT37">
         <v>7.8</v>
@@ -10160,7 +10169,7 @@
         <v>15.5</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX37">
         <v>8.4</v>
@@ -10172,7 +10181,7 @@
         <v>13.5</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB37">
         <v>12.5</v>
@@ -10184,13 +10193,13 @@
         <v>21</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF37">
         <v>6</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10253,7 +10262,7 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -10261,16 +10270,16 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F38">
         <v>1.53</v>
@@ -10387,10 +10396,10 @@
         <v>12.5</v>
       </c>
       <c r="AR38">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AT38">
         <v>4.1</v>
@@ -10399,10 +10408,10 @@
         <v>6.2</v>
       </c>
       <c r="AV38">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AX38">
         <v>5.3</v>
@@ -10414,7 +10423,7 @@
         <v>19</v>
       </c>
       <c r="BA38">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BB38">
         <v>9.6</v>
@@ -10423,16 +10432,16 @@
         <v>13.5</v>
       </c>
       <c r="BD38">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BE38">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BF38">
         <v>8.800000000000001</v>
       </c>
       <c r="BG38">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BH38">
         <v>3.45</v>
@@ -10495,7 +10504,7 @@
         <v>1.42</v>
       </c>
       <c r="CB38" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10503,16 +10512,16 @@
         <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F39">
         <v>3.55</v>
@@ -10524,7 +10533,7 @@
         <v>1.98</v>
       </c>
       <c r="I39">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="J39">
         <v>3.8</v>
@@ -10563,7 +10572,7 @@
         <v>1.11</v>
       </c>
       <c r="V39">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="W39">
         <v>1.33</v>
@@ -10623,52 +10632,52 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
@@ -10737,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10745,16 +10754,16 @@
         <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E40" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F40">
         <v>3.9</v>
@@ -10979,7 +10988,7 @@
         <v>1.74</v>
       </c>
       <c r="CB40" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10987,16 +10996,16 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F41">
         <v>3.6</v>
@@ -11032,7 +11041,7 @@
         <v>2.2</v>
       </c>
       <c r="Q41">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="R41">
         <v>1.39</v>
@@ -11107,52 +11116,52 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41">
         <v>1.01</v>
@@ -11221,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -11229,31 +11238,31 @@
         <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F42">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H42">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I42">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K42">
         <v>3.15</v>
@@ -11262,7 +11271,7 @@
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N42">
         <v>2.48</v>
@@ -11289,10 +11298,10 @@
         <v>1.74</v>
       </c>
       <c r="V42">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X42">
         <v>9.199999999999999</v>
@@ -11349,13 +11358,13 @@
         <v>38</v>
       </c>
       <c r="AP42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ42">
         <v>6.2</v>
       </c>
       <c r="AR42">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS42">
         <v>6.4</v>
@@ -11406,19 +11415,19 @@
         <v>1000</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BJ42">
         <v>16</v>
       </c>
       <c r="BK42">
-        <v>7.6</v>
+        <v>1.54</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>21</v>
+        <v>1.7</v>
       </c>
       <c r="BN42">
         <v>9.6</v>
@@ -11430,13 +11439,13 @@
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>21</v>
+        <v>1.66</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>21</v>
+        <v>1.67</v>
       </c>
       <c r="BT42">
         <v>6.4</v>
@@ -11448,22 +11457,22 @@
         <v>30</v>
       </c>
       <c r="BW42">
-        <v>13.5</v>
+        <v>1.61</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>21</v>
+        <v>1.66</v>
       </c>
       <c r="BZ42">
         <v>1000</v>
       </c>
       <c r="CA42">
-        <v>21</v>
+        <v>1.66</v>
       </c>
       <c r="CB42" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11471,16 +11480,16 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -11489,7 +11498,7 @@
         <v>2.1</v>
       </c>
       <c r="H43">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I43">
         <v>4.2</v>
@@ -11522,13 +11531,13 @@
         <v>1.36</v>
       </c>
       <c r="S43">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T43">
         <v>1.75</v>
       </c>
       <c r="U43">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V43">
         <v>1.31</v>
@@ -11540,7 +11549,7 @@
         <v>17</v>
       </c>
       <c r="Y43">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z43">
         <v>34</v>
@@ -11705,7 +11714,7 @@
         <v>16.5</v>
       </c>
       <c r="CB43" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11713,16 +11722,16 @@
         <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E44" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F44">
         <v>2.22</v>
@@ -11734,7 +11743,7 @@
         <v>3.25</v>
       </c>
       <c r="I44">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J44">
         <v>3.45</v>
@@ -11755,7 +11764,7 @@
         <v>1.31</v>
       </c>
       <c r="P44">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q44">
         <v>1.92</v>
@@ -11767,13 +11776,13 @@
         <v>3.2</v>
       </c>
       <c r="T44">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44">
         <v>2.08</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
         <v>1.74</v>
@@ -11842,7 +11851,7 @@
         <v>17</v>
       </c>
       <c r="AS44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT44">
         <v>7.6</v>
@@ -11866,7 +11875,7 @@
         <v>1.03</v>
       </c>
       <c r="BA44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44">
         <v>1.03</v>
@@ -11947,7 +11956,7 @@
         <v>1.32</v>
       </c>
       <c r="CB44" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11955,28 +11964,28 @@
         <v>94</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F45">
         <v>4.3</v>
       </c>
       <c r="G45">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H45">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I45">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="J45">
         <v>4</v>
@@ -12000,7 +12009,7 @@
         <v>2.36</v>
       </c>
       <c r="Q45">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R45">
         <v>1.54</v>
@@ -12015,10 +12024,10 @@
         <v>2.32</v>
       </c>
       <c r="V45">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="W45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X45">
         <v>23</v>
@@ -12033,7 +12042,7 @@
         <v>20</v>
       </c>
       <c r="AB45">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC45">
         <v>10.5</v>
@@ -12063,7 +12072,7 @@
         <v>60</v>
       </c>
       <c r="AL45">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM45">
         <v>85</v>
@@ -12111,7 +12120,7 @@
         <v>17.5</v>
       </c>
       <c r="BB45">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC45">
         <v>30</v>
@@ -12120,7 +12129,7 @@
         <v>30</v>
       </c>
       <c r="BE45">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF45">
         <v>25</v>
@@ -12132,64 +12141,64 @@
         <v>1000</v>
       </c>
       <c r="BI45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ45">
         <v>1000</v>
       </c>
       <c r="BK45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN45">
         <v>1000</v>
       </c>
       <c r="BO45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP45">
         <v>1000</v>
       </c>
       <c r="BQ45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR45">
         <v>1000</v>
       </c>
       <c r="BS45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT45">
         <v>1000</v>
       </c>
       <c r="BU45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV45">
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ45">
         <v>1000</v>
       </c>
       <c r="CA45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB45" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -12197,16 +12206,16 @@
         <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E46" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F46">
         <v>1.77</v>
@@ -12224,7 +12233,7 @@
         <v>4.3</v>
       </c>
       <c r="K46">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12245,7 +12254,7 @@
         <v>1.45</v>
       </c>
       <c r="R46">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="S46">
         <v>2.1</v>
@@ -12266,16 +12275,16 @@
         <v>36</v>
       </c>
       <c r="Y46">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z46">
         <v>44</v>
       </c>
       <c r="AA46">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB46">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC46">
         <v>13.5</v>
@@ -12311,7 +12320,7 @@
         <v>65</v>
       </c>
       <c r="AN46">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO46">
         <v>32</v>
@@ -12332,7 +12341,7 @@
         <v>11.5</v>
       </c>
       <c r="AU46">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV46">
         <v>13.5</v>
@@ -12341,7 +12350,7 @@
         <v>4.6</v>
       </c>
       <c r="AX46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY46">
         <v>8.6</v>
@@ -12353,7 +12362,7 @@
         <v>4.6</v>
       </c>
       <c r="BB46">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC46">
         <v>12.5</v>
@@ -12365,7 +12374,7 @@
         <v>4.7</v>
       </c>
       <c r="BF46">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG46">
         <v>20</v>
@@ -12431,7 +12440,7 @@
         <v>1.01</v>
       </c>
       <c r="CB46" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12439,28 +12448,28 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E47" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F47">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="G47">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H47">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I47">
-        <v>970</v>
+        <v>3.1</v>
       </c>
       <c r="J47">
         <v>4.1</v>
@@ -12475,7 +12484,7 @@
         <v>1.01</v>
       </c>
       <c r="N47">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O47">
         <v>1.06</v>
@@ -12487,22 +12496,22 @@
         <v>1.06</v>
       </c>
       <c r="R47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S47">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="W47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12673,7 +12682,7 @@
         <v>1.01</v>
       </c>
       <c r="CB47" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:80">
@@ -12681,16 +12690,16 @@
         <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E48" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F48">
         <v>2.98</v>
@@ -12735,10 +12744,10 @@
         <v>3.55</v>
       </c>
       <c r="T48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V48">
         <v>1.58</v>
@@ -12858,64 +12867,64 @@
         <v>1000</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ48">
         <v>1000</v>
       </c>
       <c r="BK48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN48">
         <v>1000</v>
       </c>
       <c r="BO48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP48">
         <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR48">
         <v>1000</v>
       </c>
       <c r="BS48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT48">
         <v>1000</v>
       </c>
       <c r="BU48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV48">
         <v>1000</v>
       </c>
       <c r="BW48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX48">
         <v>1000</v>
       </c>
       <c r="BY48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ48">
         <v>1000</v>
       </c>
       <c r="CA48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB48" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:80">
@@ -12923,16 +12932,16 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D49" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F49">
         <v>2.62</v>
@@ -13052,7 +13061,7 @@
         <v>14</v>
       </c>
       <c r="AS49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT49">
         <v>7.8</v>
@@ -13076,25 +13085,25 @@
         <v>14.5</v>
       </c>
       <c r="BA49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC49">
         <v>1.03</v>
       </c>
       <c r="BD49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF49">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BG49">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH49">
         <v>3.85</v>
@@ -13157,7 +13166,7 @@
         <v>3.25</v>
       </c>
       <c r="CB49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:80">
@@ -13165,22 +13174,22 @@
         <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F50">
         <v>3.35</v>
       </c>
       <c r="G50">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H50">
         <v>2.32</v>
@@ -13192,7 +13201,7 @@
         <v>3.1</v>
       </c>
       <c r="K50">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13207,7 +13216,7 @@
         <v>1.41</v>
       </c>
       <c r="P50">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q50">
         <v>2.24</v>
@@ -13294,7 +13303,7 @@
         <v>11</v>
       </c>
       <c r="AS50">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT50">
         <v>9.6</v>
@@ -13306,7 +13315,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW50">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX50">
         <v>18</v>
@@ -13318,22 +13327,22 @@
         <v>15</v>
       </c>
       <c r="BA50">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB50">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC50">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD50">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE50">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF50">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG50">
         <v>21</v>
@@ -13399,7 +13408,7 @@
         <v>1.4</v>
       </c>
       <c r="CB50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:80">
@@ -13407,31 +13416,31 @@
         <v>106</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F51">
-        <v>1.47</v>
+        <v>2.36</v>
       </c>
       <c r="G51">
-        <v>1.59</v>
+        <v>2.6</v>
       </c>
       <c r="H51">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I51">
-        <v>11.5</v>
+        <v>2.94</v>
       </c>
       <c r="J51">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K51">
         <v>4.7</v>
@@ -13440,145 +13449,145 @@
         <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O51">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="P51">
-        <v>1.81</v>
+        <v>2.86</v>
       </c>
       <c r="Q51">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="R51">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="S51">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="T51">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="U51">
-        <v>1.72</v>
+        <v>2.84</v>
       </c>
       <c r="V51">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="X51">
+        <v>38</v>
+      </c>
+      <c r="Y51">
+        <v>24</v>
+      </c>
+      <c r="Z51">
+        <v>29</v>
+      </c>
+      <c r="AA51">
+        <v>48</v>
+      </c>
+      <c r="AB51">
+        <v>22</v>
+      </c>
+      <c r="AC51">
+        <v>13</v>
+      </c>
+      <c r="AD51">
+        <v>16</v>
+      </c>
+      <c r="AE51">
+        <v>29</v>
+      </c>
+      <c r="AF51">
+        <v>26</v>
+      </c>
+      <c r="AG51">
+        <v>15</v>
+      </c>
+      <c r="AH51">
         <v>16.5</v>
       </c>
-      <c r="Y51">
-        <v>28</v>
-      </c>
-      <c r="Z51">
-        <v>95</v>
-      </c>
-      <c r="AA51">
-        <v>410</v>
-      </c>
-      <c r="AB51">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC51">
-        <v>12</v>
-      </c>
-      <c r="AD51">
+      <c r="AI51">
+        <v>32</v>
+      </c>
+      <c r="AJ51">
         <v>40</v>
       </c>
-      <c r="AE51">
-        <v>200</v>
-      </c>
-      <c r="AF51">
+      <c r="AK51">
+        <v>26</v>
+      </c>
+      <c r="AL51">
+        <v>30</v>
+      </c>
+      <c r="AM51">
+        <v>55</v>
+      </c>
+      <c r="AN51">
+        <v>12.5</v>
+      </c>
+      <c r="AO51">
+        <v>15</v>
+      </c>
+      <c r="AP51">
+        <v>4.5</v>
+      </c>
+      <c r="AQ51">
+        <v>15.5</v>
+      </c>
+      <c r="AR51">
+        <v>18.5</v>
+      </c>
+      <c r="AS51">
+        <v>4.6</v>
+      </c>
+      <c r="AT51">
+        <v>14.5</v>
+      </c>
+      <c r="AU51">
+        <v>8.6</v>
+      </c>
+      <c r="AV51">
+        <v>10.5</v>
+      </c>
+      <c r="AW51">
+        <v>19</v>
+      </c>
+      <c r="AX51">
+        <v>16.5</v>
+      </c>
+      <c r="AY51">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG51">
-        <v>12.5</v>
-      </c>
-      <c r="AH51">
-        <v>36</v>
-      </c>
-      <c r="AI51">
-        <v>180</v>
-      </c>
-      <c r="AJ51">
-        <v>16.5</v>
-      </c>
-      <c r="AK51">
-        <v>22</v>
-      </c>
-      <c r="AL51">
-        <v>60</v>
-      </c>
-      <c r="AM51">
-        <v>240</v>
-      </c>
-      <c r="AN51">
-        <v>12</v>
-      </c>
-      <c r="AO51">
-        <v>330</v>
-      </c>
-      <c r="AP51">
-        <v>1.01</v>
-      </c>
-      <c r="AQ51">
-        <v>1.01</v>
-      </c>
-      <c r="AR51">
-        <v>1.01</v>
-      </c>
-      <c r="AS51">
-        <v>1.01</v>
-      </c>
-      <c r="AT51">
-        <v>1.01</v>
-      </c>
-      <c r="AU51">
-        <v>1.01</v>
-      </c>
-      <c r="AV51">
-        <v>1.01</v>
-      </c>
-      <c r="AW51">
-        <v>1.01</v>
-      </c>
-      <c r="AX51">
-        <v>1.01</v>
-      </c>
-      <c r="AY51">
-        <v>1.01</v>
-      </c>
       <c r="AZ51">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA51">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB51">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC51">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD51">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE51">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF51">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG51">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13641,24 +13650,24 @@
         <v>1.01</v>
       </c>
       <c r="CB51" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:80">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F52">
         <v>3.6</v>
@@ -13700,13 +13709,13 @@
         <v>1.43</v>
       </c>
       <c r="S52">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T52">
         <v>1.57</v>
       </c>
       <c r="U52">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V52">
         <v>1.84</v>
@@ -13826,81 +13835,81 @@
         <v>1000</v>
       </c>
       <c r="BI52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ52">
         <v>1000</v>
       </c>
       <c r="BK52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52">
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52">
         <v>1000</v>
       </c>
       <c r="BO52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52">
         <v>1000</v>
       </c>
       <c r="BQ52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52">
         <v>1000</v>
       </c>
       <c r="BS52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52">
         <v>1000</v>
       </c>
       <c r="BU52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52">
         <v>1000</v>
       </c>
       <c r="CA52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB52" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:80">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F53">
         <v>2.04</v>
@@ -13942,13 +13951,13 @@
         <v>1.59</v>
       </c>
       <c r="S53">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T53">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U53">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V53">
         <v>1.38</v>
@@ -14125,24 +14134,24 @@
         <v>1.01</v>
       </c>
       <c r="CB53" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:80">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E54" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F54">
         <v>2.56</v>
@@ -14151,13 +14160,13 @@
         <v>2.94</v>
       </c>
       <c r="H54">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I54">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J54">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K54">
         <v>4.1</v>
@@ -14169,7 +14178,7 @@
         <v>1.05</v>
       </c>
       <c r="N54">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O54">
         <v>1.26</v>
@@ -14178,19 +14187,19 @@
         <v>2.08</v>
       </c>
       <c r="Q54">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R54">
         <v>1.43</v>
       </c>
       <c r="S54">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="T54">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U54">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V54">
         <v>1.52</v>
@@ -14199,10 +14208,10 @@
         <v>1.52</v>
       </c>
       <c r="X54">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y54">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z54">
         <v>21</v>
@@ -14211,7 +14220,7 @@
         <v>55</v>
       </c>
       <c r="AB54">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC54">
         <v>9</v>
@@ -14229,7 +14238,7 @@
         <v>13.5</v>
       </c>
       <c r="AH54">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI54">
         <v>50</v>
@@ -14250,10 +14259,10 @@
         <v>22</v>
       </c>
       <c r="AO54">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP54">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ54">
         <v>11</v>
@@ -14268,7 +14277,7 @@
         <v>11</v>
       </c>
       <c r="AU54">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV54">
         <v>10.5</v>
@@ -14283,7 +14292,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ54">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA54">
         <v>26</v>
@@ -14301,10 +14310,10 @@
         <v>1.01</v>
       </c>
       <c r="BF54">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG54">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14367,24 +14376,24 @@
         <v>1.01</v>
       </c>
       <c r="CB54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:80">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F55">
         <v>2.08</v>
@@ -14420,7 +14429,7 @@
         <v>2.38</v>
       </c>
       <c r="Q55">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R55">
         <v>1.56</v>
@@ -14609,24 +14618,24 @@
         <v>1.01</v>
       </c>
       <c r="CB55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:80">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E56" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F56">
         <v>3.9</v>
@@ -14644,7 +14653,7 @@
         <v>4</v>
       </c>
       <c r="K56">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14659,22 +14668,22 @@
         <v>1.16</v>
       </c>
       <c r="P56">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q56">
         <v>1.52</v>
       </c>
       <c r="R56">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S56">
         <v>2.2</v>
       </c>
       <c r="T56">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U56">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V56">
         <v>2.02</v>
@@ -14851,7 +14860,7 @@
         <v>1.01</v>
       </c>
       <c r="CB56" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:80">
@@ -14859,241 +14868,241 @@
         <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E57" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F57">
-        <v>2.36</v>
+        <v>1.47</v>
       </c>
       <c r="G57">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="H57">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="I57">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="J57">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K57">
         <v>4.7</v>
       </c>
       <c r="L57">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M57">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N57">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="O57">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="P57">
+        <v>1.81</v>
+      </c>
+      <c r="Q57">
+        <v>1.97</v>
+      </c>
+      <c r="R57">
+        <v>1.31</v>
+      </c>
+      <c r="S57">
+        <v>3.5</v>
+      </c>
+      <c r="T57">
+        <v>2.14</v>
+      </c>
+      <c r="U57">
+        <v>1.72</v>
+      </c>
+      <c r="V57">
+        <v>1.1</v>
+      </c>
+      <c r="W57">
+        <v>2.74</v>
+      </c>
+      <c r="X57">
+        <v>16.5</v>
+      </c>
+      <c r="Y57">
+        <v>28</v>
+      </c>
+      <c r="Z57">
+        <v>95</v>
+      </c>
+      <c r="AA57">
+        <v>410</v>
+      </c>
+      <c r="AB57">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC57">
+        <v>12</v>
+      </c>
+      <c r="AD57">
+        <v>40</v>
+      </c>
+      <c r="AE57">
+        <v>200</v>
+      </c>
+      <c r="AF57">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG57">
+        <v>12.5</v>
+      </c>
+      <c r="AH57">
+        <v>36</v>
+      </c>
+      <c r="AI57">
+        <v>180</v>
+      </c>
+      <c r="AJ57">
+        <v>16.5</v>
+      </c>
+      <c r="AK57">
+        <v>22</v>
+      </c>
+      <c r="AL57">
+        <v>60</v>
+      </c>
+      <c r="AM57">
+        <v>240</v>
+      </c>
+      <c r="AN57">
+        <v>12</v>
+      </c>
+      <c r="AO57">
+        <v>330</v>
+      </c>
+      <c r="AP57">
+        <v>3.45</v>
+      </c>
+      <c r="AQ57">
+        <v>3.8</v>
+      </c>
+      <c r="AR57">
+        <v>4.2</v>
+      </c>
+      <c r="AS57">
+        <v>4.3</v>
+      </c>
+      <c r="AT57">
         <v>2.86</v>
       </c>
-      <c r="Q57">
-        <v>1.44</v>
-      </c>
-      <c r="R57">
-        <v>1.76</v>
-      </c>
-      <c r="S57">
-        <v>2.1</v>
-      </c>
-      <c r="T57">
-        <v>1.44</v>
-      </c>
-      <c r="U57">
-        <v>2.84</v>
-      </c>
-      <c r="V57">
-        <v>1.53</v>
-      </c>
-      <c r="W57">
-        <v>1.62</v>
-      </c>
-      <c r="X57">
-        <v>38</v>
-      </c>
-      <c r="Y57">
-        <v>24</v>
-      </c>
-      <c r="Z57">
-        <v>29</v>
-      </c>
-      <c r="AA57">
-        <v>48</v>
-      </c>
-      <c r="AB57">
-        <v>22</v>
-      </c>
-      <c r="AC57">
-        <v>13</v>
-      </c>
-      <c r="AD57">
-        <v>16</v>
-      </c>
-      <c r="AE57">
-        <v>29</v>
-      </c>
-      <c r="AF57">
-        <v>26</v>
-      </c>
-      <c r="AG57">
-        <v>15</v>
-      </c>
-      <c r="AH57">
-        <v>16.5</v>
-      </c>
-      <c r="AI57">
-        <v>32</v>
-      </c>
-      <c r="AJ57">
-        <v>40</v>
-      </c>
-      <c r="AK57">
-        <v>26</v>
-      </c>
-      <c r="AL57">
-        <v>30</v>
-      </c>
-      <c r="AM57">
-        <v>55</v>
-      </c>
-      <c r="AN57">
-        <v>12.5</v>
-      </c>
-      <c r="AO57">
-        <v>15</v>
-      </c>
-      <c r="AP57">
-        <v>1.03</v>
-      </c>
-      <c r="AQ57">
-        <v>15.5</v>
-      </c>
-      <c r="AR57">
-        <v>18.5</v>
-      </c>
-      <c r="AS57">
-        <v>1.01</v>
-      </c>
-      <c r="AT57">
-        <v>14.5</v>
-      </c>
       <c r="AU57">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="AV57">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW57">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="AX57">
-        <v>16.5</v>
+        <v>3</v>
       </c>
       <c r="AY57">
-        <v>9.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AZ57">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BA57">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="BB57">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BC57">
-        <v>17</v>
+        <v>3.65</v>
       </c>
       <c r="BD57">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE57">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF57">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="BG57">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BH57">
         <v>1000</v>
       </c>
       <c r="BI57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ57">
         <v>1000</v>
       </c>
       <c r="BK57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL57">
         <v>1000</v>
       </c>
       <c r="BM57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN57">
         <v>1000</v>
       </c>
       <c r="BO57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP57">
         <v>1000</v>
       </c>
       <c r="BQ57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR57">
         <v>1000</v>
       </c>
       <c r="BS57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT57">
         <v>1000</v>
       </c>
       <c r="BU57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV57">
         <v>1000</v>
       </c>
       <c r="BW57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX57">
         <v>1000</v>
       </c>
       <c r="BY57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ57">
         <v>1000</v>
       </c>
       <c r="CA57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:80">
@@ -15101,16 +15110,16 @@
         <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F58">
         <v>2.46</v>
@@ -15158,7 +15167,7 @@
         <v>1.5</v>
       </c>
       <c r="U58">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V58">
         <v>1.46</v>
@@ -15173,13 +15182,13 @@
         <v>15.5</v>
       </c>
       <c r="Z58">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA58">
         <v>65</v>
       </c>
       <c r="AB58">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC58">
         <v>10</v>
@@ -15335,7 +15344,7 @@
         <v>1.3</v>
       </c>
       <c r="CB58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:80">
@@ -15343,19 +15352,19 @@
         <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E59" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F59">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G59">
         <v>1.71</v>
@@ -15364,7 +15373,7 @@
         <v>6.4</v>
       </c>
       <c r="I59">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J59">
         <v>3.8</v>
@@ -15403,7 +15412,7 @@
         <v>1.75</v>
       </c>
       <c r="V59">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W59">
         <v>2.4</v>
@@ -15412,7 +15421,7 @@
         <v>14.5</v>
       </c>
       <c r="Y59">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z59">
         <v>70</v>
@@ -15421,34 +15430,34 @@
         <v>270</v>
       </c>
       <c r="AB59">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AC59">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD59">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE59">
         <v>140</v>
       </c>
       <c r="AF59">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG59">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH59">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI59">
         <v>140</v>
       </c>
       <c r="AJ59">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK59">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL59">
         <v>55</v>
@@ -15457,7 +15466,7 @@
         <v>200</v>
       </c>
       <c r="AN59">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO59">
         <v>220</v>
@@ -15469,10 +15478,10 @@
         <v>16</v>
       </c>
       <c r="AR59">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS59">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT59">
         <v>6</v>
@@ -15484,7 +15493,7 @@
         <v>21</v>
       </c>
       <c r="AW59">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX59">
         <v>7.6</v>
@@ -15496,7 +15505,7 @@
         <v>21</v>
       </c>
       <c r="BA59">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB59">
         <v>13.5</v>
@@ -15508,13 +15517,13 @@
         <v>36</v>
       </c>
       <c r="BE59">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF59">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG59">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH59">
         <v>3.9</v>
@@ -15577,7 +15586,7 @@
         <v>1.35</v>
       </c>
       <c r="CB59" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:80">
@@ -15585,34 +15594,34 @@
         <v>87</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E60" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F60">
         <v>1.55</v>
       </c>
       <c r="G60">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H60">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I60">
         <v>7.8</v>
       </c>
       <c r="J60">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K60">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -15621,34 +15630,34 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O60">
         <v>1.22</v>
       </c>
       <c r="P60">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q60">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R60">
         <v>1.42</v>
       </c>
       <c r="S60">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V60">
         <v>1.14</v>
       </c>
       <c r="W60">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -15705,52 +15714,52 @@
         <v>1000</v>
       </c>
       <c r="AP60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF60">
         <v>1.01</v>
@@ -15819,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="CB60" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:80">
@@ -15827,22 +15836,22 @@
         <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F61">
         <v>8.800000000000001</v>
       </c>
       <c r="G61">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H61">
         <v>1.42</v>
@@ -15881,7 +15890,7 @@
         <v>2.88</v>
       </c>
       <c r="T61">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="U61">
         <v>1.86</v>
@@ -15920,7 +15929,7 @@
         <v>85</v>
       </c>
       <c r="AG61">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH61">
         <v>28</v>
@@ -15932,7 +15941,7 @@
         <v>400</v>
       </c>
       <c r="AK61">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL61">
         <v>150</v>
@@ -15941,7 +15950,7 @@
         <v>170</v>
       </c>
       <c r="AN61">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AO61">
         <v>7.2</v>
@@ -16061,7 +16070,7 @@
         <v>1.01</v>
       </c>
       <c r="CB61" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:80">
@@ -16069,16 +16078,16 @@
         <v>110</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E62" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F62">
         <v>2.6</v>
@@ -16096,7 +16105,7 @@
         <v>3.55</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L62">
         <v>1.01</v>
@@ -16111,13 +16120,13 @@
         <v>1.27</v>
       </c>
       <c r="P62">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q62">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R62">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S62">
         <v>3.1</v>
@@ -16252,58 +16261,58 @@
         <v>1000</v>
       </c>
       <c r="BK62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BL62">
         <v>1000</v>
       </c>
       <c r="BM62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BN62">
         <v>1000</v>
       </c>
       <c r="BO62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BP62">
         <v>1000</v>
       </c>
       <c r="BQ62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BR62">
         <v>1000</v>
       </c>
       <c r="BS62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT62">
         <v>1000</v>
       </c>
       <c r="BU62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BV62">
         <v>1000</v>
       </c>
       <c r="BW62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BX62">
         <v>1000</v>
       </c>
       <c r="BY62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BZ62">
         <v>1000</v>
       </c>
       <c r="CA62">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="CB62" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:80">
@@ -16311,16 +16320,16 @@
         <v>111</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E63" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F63">
         <v>2.64</v>
@@ -16353,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="P63">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q63">
         <v>2.16</v>
@@ -16545,7 +16554,7 @@
         <v>0</v>
       </c>
       <c r="CB63" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:80">
@@ -16553,175 +16562,175 @@
         <v>112</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F64">
         <v>2.08</v>
       </c>
       <c r="G64">
-        <v>600</v>
+        <v>2.22</v>
       </c>
       <c r="H64">
-        <v>1.36</v>
+        <v>3.55</v>
       </c>
       <c r="I64">
-        <v>870</v>
+        <v>3.95</v>
       </c>
       <c r="J64">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="K64">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L64">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M64">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N64">
-        <v>1.26</v>
+        <v>4.1</v>
       </c>
       <c r="O64">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P64">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q64">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="R64">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S64">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="T64">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U64">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V64">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W64">
         <v>1.01</v>
       </c>
       <c r="X64">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y64">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z64">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA64">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB64">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC64">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD64">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE64">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF64">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG64">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH64">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI64">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ64">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK64">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL64">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM64">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN64">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO64">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP64">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ64">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR64">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS64">
         <v>1.01</v>
       </c>
       <c r="AT64">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU64">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV64">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW64">
         <v>1.01</v>
       </c>
       <c r="AX64">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY64">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ64">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA64">
         <v>1.01</v>
       </c>
       <c r="BB64">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC64">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE64">
         <v>1.01</v>
       </c>
       <c r="BF64">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG64">
         <v>1.01</v>
@@ -16787,7 +16796,7 @@
         <v>0</v>
       </c>
       <c r="CB64" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65" spans="1:80">
@@ -16795,16 +16804,16 @@
         <v>89</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F65">
         <v>2.34</v>
@@ -16831,7 +16840,7 @@
         <v>1.01</v>
       </c>
       <c r="N65">
-        <v>2.44</v>
+        <v>1.1</v>
       </c>
       <c r="O65">
         <v>1.26</v>
@@ -16840,7 +16849,7 @@
         <v>2.02</v>
       </c>
       <c r="Q65">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R65">
         <v>1.37</v>
@@ -16849,10 +16858,10 @@
         <v>2.88</v>
       </c>
       <c r="T65">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U65">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V65">
         <v>1.45</v>
@@ -16915,52 +16924,52 @@
         <v>1000</v>
       </c>
       <c r="AP65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF65">
         <v>1.01</v>
@@ -17029,7 +17038,7 @@
         <v>0</v>
       </c>
       <c r="CB65" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="1:80">
@@ -17037,34 +17046,34 @@
         <v>113</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F66">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="G66">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="H66">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I66">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K66">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -17073,34 +17082,34 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="O66">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P66">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="Q66">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R66">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S66">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="T66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V66">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W66">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -17157,52 +17166,52 @@
         <v>1000</v>
       </c>
       <c r="AP66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF66">
         <v>1.01</v>
@@ -17271,186 +17280,186 @@
         <v>0</v>
       </c>
       <c r="CB66" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="1:80">
       <c r="A67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F67">
+        <v>7.2</v>
+      </c>
+      <c r="G67">
+        <v>11.5</v>
+      </c>
+      <c r="H67">
+        <v>1.4</v>
+      </c>
+      <c r="I67">
+        <v>1.47</v>
+      </c>
+      <c r="J67">
+        <v>4.3</v>
+      </c>
+      <c r="K67">
+        <v>5.5</v>
+      </c>
+      <c r="L67">
+        <v>1.01</v>
+      </c>
+      <c r="M67">
+        <v>1.05</v>
+      </c>
+      <c r="N67">
+        <v>4.2</v>
+      </c>
+      <c r="O67">
+        <v>1.24</v>
+      </c>
+      <c r="P67">
+        <v>2.14</v>
+      </c>
+      <c r="Q67">
+        <v>1.71</v>
+      </c>
+      <c r="R67">
+        <v>1.46</v>
+      </c>
+      <c r="S67">
+        <v>2.58</v>
+      </c>
+      <c r="T67">
+        <v>1.99</v>
+      </c>
+      <c r="U67">
+        <v>1.86</v>
+      </c>
+      <c r="V67">
+        <v>3</v>
+      </c>
+      <c r="W67">
+        <v>1.11</v>
+      </c>
+      <c r="X67">
+        <v>23</v>
+      </c>
+      <c r="Y67">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z67">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA67">
+        <v>12.5</v>
+      </c>
+      <c r="AB67">
+        <v>30</v>
+      </c>
+      <c r="AC67">
+        <v>12</v>
+      </c>
+      <c r="AD67">
+        <v>10.5</v>
+      </c>
+      <c r="AE67">
+        <v>15.5</v>
+      </c>
+      <c r="AF67">
+        <v>95</v>
+      </c>
+      <c r="AG67">
+        <v>34</v>
+      </c>
+      <c r="AH67">
+        <v>27</v>
+      </c>
+      <c r="AI67">
+        <v>38</v>
+      </c>
+      <c r="AJ67">
+        <v>360</v>
+      </c>
+      <c r="AK67">
+        <v>170</v>
+      </c>
+      <c r="AL67">
+        <v>140</v>
+      </c>
+      <c r="AM67">
+        <v>170</v>
+      </c>
+      <c r="AN67">
+        <v>220</v>
+      </c>
+      <c r="AO67">
+        <v>6.6</v>
+      </c>
+      <c r="AP67">
+        <v>7.2</v>
+      </c>
+      <c r="AQ67">
+        <v>4.8</v>
+      </c>
+      <c r="AR67">
+        <v>4.8</v>
+      </c>
+      <c r="AS67">
+        <v>5.8</v>
+      </c>
+      <c r="AT67">
+        <v>7.8</v>
+      </c>
+      <c r="AU67">
+        <v>5.7</v>
+      </c>
+      <c r="AV67">
         <v>5.3</v>
       </c>
-      <c r="G67">
-        <v>16</v>
-      </c>
-      <c r="H67">
-        <v>1.28</v>
-      </c>
-      <c r="I67">
-        <v>1.34</v>
-      </c>
-      <c r="J67">
+      <c r="AW67">
+        <v>6.2</v>
+      </c>
+      <c r="AX67">
+        <v>9.6</v>
+      </c>
+      <c r="AY67">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ67">
+        <v>7.6</v>
+      </c>
+      <c r="BA67">
+        <v>8.4</v>
+      </c>
+      <c r="BB67">
+        <v>10.5</v>
+      </c>
+      <c r="BC67">
+        <v>10</v>
+      </c>
+      <c r="BD67">
+        <v>10</v>
+      </c>
+      <c r="BE67">
+        <v>10</v>
+      </c>
+      <c r="BF67">
+        <v>10</v>
+      </c>
+      <c r="BG67">
         <v>4.1</v>
-      </c>
-      <c r="K67">
-        <v>6.6</v>
-      </c>
-      <c r="L67">
-        <v>1.01</v>
-      </c>
-      <c r="M67">
-        <v>1.01</v>
-      </c>
-      <c r="N67">
-        <v>4.3</v>
-      </c>
-      <c r="O67">
-        <v>1.2</v>
-      </c>
-      <c r="P67">
-        <v>2.26</v>
-      </c>
-      <c r="Q67">
-        <v>1.54</v>
-      </c>
-      <c r="R67">
-        <v>1.38</v>
-      </c>
-      <c r="S67">
-        <v>2.24</v>
-      </c>
-      <c r="T67">
-        <v>1.01</v>
-      </c>
-      <c r="U67">
-        <v>1.01</v>
-      </c>
-      <c r="V67">
-        <v>3.4</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1000</v>
-      </c>
-      <c r="Y67">
-        <v>1000</v>
-      </c>
-      <c r="Z67">
-        <v>1000</v>
-      </c>
-      <c r="AA67">
-        <v>1000</v>
-      </c>
-      <c r="AB67">
-        <v>1000</v>
-      </c>
-      <c r="AC67">
-        <v>1000</v>
-      </c>
-      <c r="AD67">
-        <v>1000</v>
-      </c>
-      <c r="AE67">
-        <v>1000</v>
-      </c>
-      <c r="AF67">
-        <v>1000</v>
-      </c>
-      <c r="AG67">
-        <v>1000</v>
-      </c>
-      <c r="AH67">
-        <v>1000</v>
-      </c>
-      <c r="AI67">
-        <v>1000</v>
-      </c>
-      <c r="AJ67">
-        <v>1000</v>
-      </c>
-      <c r="AK67">
-        <v>1000</v>
-      </c>
-      <c r="AL67">
-        <v>1000</v>
-      </c>
-      <c r="AM67">
-        <v>1000</v>
-      </c>
-      <c r="AN67">
-        <v>1000</v>
-      </c>
-      <c r="AO67">
-        <v>1000</v>
-      </c>
-      <c r="AP67">
-        <v>1.01</v>
-      </c>
-      <c r="AQ67">
-        <v>1.01</v>
-      </c>
-      <c r="AR67">
-        <v>1.01</v>
-      </c>
-      <c r="AS67">
-        <v>1.01</v>
-      </c>
-      <c r="AT67">
-        <v>1.01</v>
-      </c>
-      <c r="AU67">
-        <v>1.01</v>
-      </c>
-      <c r="AV67">
-        <v>1.01</v>
-      </c>
-      <c r="AW67">
-        <v>1.01</v>
-      </c>
-      <c r="AX67">
-        <v>1.01</v>
-      </c>
-      <c r="AY67">
-        <v>1.01</v>
-      </c>
-      <c r="AZ67">
-        <v>1.01</v>
-      </c>
-      <c r="BA67">
-        <v>1.01</v>
-      </c>
-      <c r="BB67">
-        <v>1.01</v>
-      </c>
-      <c r="BC67">
-        <v>1.01</v>
-      </c>
-      <c r="BD67">
-        <v>1.01</v>
-      </c>
-      <c r="BE67">
-        <v>1.01</v>
-      </c>
-      <c r="BF67">
-        <v>1.01</v>
-      </c>
-      <c r="BG67">
-        <v>1.01</v>
       </c>
       <c r="BH67">
         <v>1000</v>
@@ -17513,24 +17522,24 @@
         <v>0</v>
       </c>
       <c r="CB67" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:80">
       <c r="A68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E68" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F68">
         <v>1.99</v>
@@ -17542,7 +17551,7 @@
         <v>2.82</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J68">
         <v>3.35</v>
@@ -17575,10 +17584,10 @@
         <v>2.28</v>
       </c>
       <c r="T68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V68">
         <v>1.35</v>
@@ -17641,52 +17650,52 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF68">
         <v>1.01</v>
@@ -17755,27 +17764,27 @@
         <v>0</v>
       </c>
       <c r="CB68" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69" spans="1:80">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C69" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E69" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F69">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G69">
         <v>2.3</v>
@@ -17793,19 +17802,19 @@
         <v>3.75</v>
       </c>
       <c r="L69">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M69">
         <v>1.08</v>
       </c>
       <c r="N69">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O69">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P69">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q69">
         <v>2.14</v>
@@ -17817,7 +17826,7 @@
         <v>3.7</v>
       </c>
       <c r="T69">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U69">
         <v>1.84</v>
@@ -17826,7 +17835,7 @@
         <v>1.29</v>
       </c>
       <c r="W69">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="X69">
         <v>13.5</v>
@@ -17883,7 +17892,7 @@
         <v>80</v>
       </c>
       <c r="AP69">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ69">
         <v>10</v>
@@ -17892,7 +17901,7 @@
         <v>21</v>
       </c>
       <c r="AS69">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT69">
         <v>6.6</v>
@@ -17904,7 +17913,7 @@
         <v>12.5</v>
       </c>
       <c r="AW69">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX69">
         <v>10</v>
@@ -17916,7 +17925,7 @@
         <v>15</v>
       </c>
       <c r="BA69">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB69">
         <v>21</v>
@@ -17925,16 +17934,16 @@
         <v>19</v>
       </c>
       <c r="BD69">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE69">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF69">
         <v>15.5</v>
       </c>
       <c r="BG69">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH69">
         <v>1000</v>
@@ -17997,7 +18006,7 @@
         <v>1.01</v>
       </c>
       <c r="CB69" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70" spans="1:80">
@@ -18005,34 +18014,34 @@
         <v>114</v>
       </c>
       <c r="B70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D70" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E70" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F70">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="G70">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="H70">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="I70">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="J70">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K70">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18041,34 +18050,34 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>3.65</v>
+        <v>2.32</v>
       </c>
       <c r="O70">
+        <v>1.18</v>
+      </c>
+      <c r="P70">
+        <v>2.32</v>
+      </c>
+      <c r="Q70">
+        <v>1.55</v>
+      </c>
+      <c r="R70">
+        <v>1.44</v>
+      </c>
+      <c r="S70">
+        <v>2.32</v>
+      </c>
+      <c r="T70">
+        <v>1.11</v>
+      </c>
+      <c r="U70">
+        <v>1.11</v>
+      </c>
+      <c r="V70">
         <v>1.21</v>
       </c>
-      <c r="P70">
-        <v>2.06</v>
-      </c>
-      <c r="Q70">
-        <v>1.65</v>
-      </c>
-      <c r="R70">
-        <v>1.5</v>
-      </c>
-      <c r="S70">
-        <v>2.58</v>
-      </c>
-      <c r="T70">
-        <v>1.01</v>
-      </c>
-      <c r="U70">
-        <v>1.01</v>
-      </c>
-      <c r="V70">
-        <v>1.14</v>
-      </c>
       <c r="W70">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -18125,52 +18134,52 @@
         <v>1000</v>
       </c>
       <c r="AP70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF70">
         <v>1.01</v>
@@ -18239,24 +18248,24 @@
         <v>0</v>
       </c>
       <c r="CB70" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="1:80">
       <c r="A71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F71">
         <v>5.4</v>
@@ -18376,40 +18385,40 @@
         <v>7.4</v>
       </c>
       <c r="AS71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV71">
         <v>7.4</v>
       </c>
       <c r="AW71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX71">
         <v>1.01</v>
       </c>
       <c r="AY71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB71">
         <v>1.01</v>
       </c>
       <c r="BC71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE71">
         <v>1.01</v>
@@ -18481,7 +18490,7 @@
         <v>0</v>
       </c>
       <c r="CB71" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72" spans="1:80">
@@ -18489,31 +18498,31 @@
         <v>115</v>
       </c>
       <c r="B72" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E72" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F72">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="G72">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="H72">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="I72">
+        <v>1.68</v>
+      </c>
+      <c r="J72">
         <v>3.1</v>
-      </c>
-      <c r="J72">
-        <v>3</v>
       </c>
       <c r="K72">
         <v>5.3</v>
@@ -18531,28 +18540,28 @@
         <v>1.23</v>
       </c>
       <c r="P72">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q72">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="R72">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S72">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T72">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U72">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V72">
-        <v>1.48</v>
+        <v>2.48</v>
       </c>
       <c r="W72">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="X72">
         <v>1000</v>
@@ -18609,52 +18618,52 @@
         <v>1000</v>
       </c>
       <c r="AP72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF72">
         <v>1.01</v>
@@ -18723,7 +18732,7 @@
         <v>0</v>
       </c>
       <c r="CB72" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73" spans="1:80">
@@ -18731,34 +18740,34 @@
         <v>115</v>
       </c>
       <c r="B73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C73" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D73" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E73" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F73">
-        <v>7.2</v>
+        <v>2.62</v>
       </c>
       <c r="G73">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="H73">
-        <v>1.52</v>
+        <v>2.48</v>
       </c>
       <c r="I73">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="J73">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K73">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -18767,34 +18776,34 @@
         <v>1.01</v>
       </c>
       <c r="N73">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O73">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P73">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q73">
         <v>1.74</v>
       </c>
       <c r="R73">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S73">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="T73">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U73">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V73">
-        <v>2.48</v>
+        <v>1.47</v>
       </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
       <c r="X73">
         <v>1000</v>
@@ -18851,52 +18860,52 @@
         <v>1000</v>
       </c>
       <c r="AP73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF73">
         <v>1.01</v>
@@ -18965,7 +18974,7 @@
         <v>0</v>
       </c>
       <c r="CB73" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74" spans="1:80">
@@ -18973,16 +18982,16 @@
         <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E74" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F74">
         <v>3.25</v>
@@ -19015,7 +19024,7 @@
         <v>1.2</v>
       </c>
       <c r="P74">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q74">
         <v>1.65</v>
@@ -19027,10 +19036,10 @@
         <v>2.6</v>
       </c>
       <c r="T74">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U74">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V74">
         <v>1.73</v>
@@ -19093,52 +19102,52 @@
         <v>1000</v>
       </c>
       <c r="AP74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF74">
         <v>1.01</v>
@@ -19150,55 +19159,55 @@
         <v>1000</v>
       </c>
       <c r="BI74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ74">
         <v>1000</v>
       </c>
       <c r="BK74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL74">
         <v>1000</v>
       </c>
       <c r="BM74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN74">
         <v>1000</v>
       </c>
       <c r="BO74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP74">
         <v>1000</v>
       </c>
       <c r="BQ74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR74">
         <v>1000</v>
       </c>
       <c r="BS74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT74">
         <v>1000</v>
       </c>
       <c r="BU74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV74">
         <v>1000</v>
       </c>
       <c r="BW74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX74">
         <v>1000</v>
       </c>
       <c r="BY74">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ74">
         <v>0</v>
@@ -19207,7 +19216,7 @@
         <v>0</v>
       </c>
       <c r="CB74" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="1:80">
@@ -19215,19 +19224,19 @@
         <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C75" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E75" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F75">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G75">
         <v>1.8</v>
@@ -19236,13 +19245,13 @@
         <v>4.6</v>
       </c>
       <c r="I75">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J75">
         <v>4.3</v>
       </c>
       <c r="K75">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L75">
         <v>1.01</v>
@@ -19257,7 +19266,7 @@
         <v>1.19</v>
       </c>
       <c r="P75">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q75">
         <v>1.59</v>
@@ -19272,13 +19281,13 @@
         <v>1.61</v>
       </c>
       <c r="U75">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V75">
         <v>1.26</v>
       </c>
       <c r="W75">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X75">
         <v>24</v>
@@ -19314,7 +19323,7 @@
         <v>16.5</v>
       </c>
       <c r="AI75">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AJ75">
         <v>20</v>
@@ -19449,7 +19458,7 @@
         <v>0</v>
       </c>
       <c r="CB75" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:80">
@@ -19457,16 +19466,16 @@
         <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F76">
         <v>1.86</v>
@@ -19511,10 +19520,10 @@
         <v>3.6</v>
       </c>
       <c r="T76">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U76">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V76">
         <v>1.24</v>
@@ -19691,7 +19700,7 @@
         <v>1.71</v>
       </c>
       <c r="CB76" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="1:80">
@@ -19699,16 +19708,16 @@
         <v>115</v>
       </c>
       <c r="B77" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C77" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E77" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F77">
         <v>2.14</v>
@@ -19729,7 +19738,7 @@
         <v>4.8</v>
       </c>
       <c r="L77">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M77">
         <v>1.01</v>
@@ -19753,10 +19762,10 @@
         <v>3</v>
       </c>
       <c r="T77">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U77">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V77">
         <v>1.37</v>
@@ -19819,52 +19828,52 @@
         <v>1000</v>
       </c>
       <c r="AP77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF77">
         <v>1.01</v>
@@ -19876,55 +19885,55 @@
         <v>1000</v>
       </c>
       <c r="BI77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ77">
         <v>1000</v>
       </c>
       <c r="BK77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL77">
         <v>1000</v>
       </c>
       <c r="BM77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN77">
         <v>1000</v>
       </c>
       <c r="BO77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP77">
         <v>1000</v>
       </c>
       <c r="BQ77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR77">
         <v>1000</v>
       </c>
       <c r="BS77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT77">
         <v>1000</v>
       </c>
       <c r="BU77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV77">
         <v>1000</v>
       </c>
       <c r="BW77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX77">
         <v>1000</v>
       </c>
       <c r="BY77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ77">
         <v>0</v>
@@ -19933,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="CB77" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="78" spans="1:80">
@@ -19941,16 +19950,16 @@
         <v>118</v>
       </c>
       <c r="B78" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E78" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F78">
         <v>1.2</v>
@@ -19986,16 +19995,16 @@
         <v>2.58</v>
       </c>
       <c r="Q78">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R78">
         <v>1.6</v>
       </c>
       <c r="S78">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T78">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U78">
         <v>1.6</v>
@@ -20022,7 +20031,7 @@
         <v>9</v>
       </c>
       <c r="AC78">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AD78">
         <v>70</v>
@@ -20037,7 +20046,7 @@
         <v>12.5</v>
       </c>
       <c r="AH78">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI78">
         <v>300</v>
@@ -20055,7 +20064,7 @@
         <v>300</v>
       </c>
       <c r="AN78">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AO78">
         <v>500</v>
@@ -20070,7 +20079,7 @@
         <v>95</v>
       </c>
       <c r="AS78">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AT78">
         <v>8.199999999999999</v>
@@ -20094,7 +20103,7 @@
         <v>44</v>
       </c>
       <c r="BA78">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BB78">
         <v>7.4</v>
@@ -20130,7 +20139,7 @@
         <v>1000</v>
       </c>
       <c r="BM78">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="BN78">
         <v>3.5</v>
@@ -20175,7 +20184,7 @@
         <v>7.2</v>
       </c>
       <c r="CB78" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="79" spans="1:80">
@@ -20183,34 +20192,34 @@
         <v>119</v>
       </c>
       <c r="B79" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C79" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E79" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F79">
         <v>1.04</v>
       </c>
       <c r="G79">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H79">
         <v>1.04</v>
       </c>
       <c r="I79">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K79">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L79">
         <v>1.01</v>
@@ -20222,25 +20231,25 @@
         <v>1.24</v>
       </c>
       <c r="O79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P79">
         <v>1.24</v>
       </c>
       <c r="Q79">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="R79">
         <v>1.18</v>
       </c>
       <c r="S79">
-        <v>1.02</v>
+        <v>1.74</v>
       </c>
       <c r="T79">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U79">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V79">
         <v>1.01</v>
@@ -20303,52 +20312,52 @@
         <v>1000</v>
       </c>
       <c r="AP79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF79">
         <v>1.01</v>
@@ -20360,64 +20369,64 @@
         <v>1000</v>
       </c>
       <c r="BI79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ79">
         <v>1000</v>
       </c>
       <c r="BK79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL79">
         <v>1000</v>
       </c>
       <c r="BM79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN79">
         <v>1000</v>
       </c>
       <c r="BO79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP79">
         <v>1000</v>
       </c>
       <c r="BQ79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR79">
         <v>1000</v>
       </c>
       <c r="BS79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT79">
         <v>1000</v>
       </c>
       <c r="BU79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV79">
         <v>1000</v>
       </c>
       <c r="BW79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX79">
         <v>1000</v>
       </c>
       <c r="BY79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ79">
         <v>1000</v>
       </c>
       <c r="CA79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB79" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="80" spans="1:80">
@@ -20425,16 +20434,16 @@
         <v>119</v>
       </c>
       <c r="B80" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C80" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E80" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F80">
         <v>1.04</v>
@@ -20449,7 +20458,7 @@
         <v>1000</v>
       </c>
       <c r="J80">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K80">
         <v>950</v>
@@ -20461,28 +20470,28 @@
         <v>1.01</v>
       </c>
       <c r="N80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q80">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R80">
         <v>1.18</v>
       </c>
       <c r="S80">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="T80">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U80">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V80">
         <v>1.01</v>
@@ -20545,52 +20554,52 @@
         <v>1000</v>
       </c>
       <c r="AP80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF80">
         <v>1.01</v>
@@ -20659,7 +20668,7 @@
         <v>1.01</v>
       </c>
       <c r="CB80" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:80">
@@ -20667,34 +20676,34 @@
         <v>119</v>
       </c>
       <c r="B81" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C81" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E81" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F81">
         <v>1.04</v>
       </c>
       <c r="G81">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H81">
         <v>1.04</v>
       </c>
       <c r="I81">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J81">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K81">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L81">
         <v>1.01</v>
@@ -20718,13 +20727,13 @@
         <v>1.18</v>
       </c>
       <c r="S81">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T81">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U81">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V81">
         <v>1.01</v>
@@ -20787,52 +20796,52 @@
         <v>1000</v>
       </c>
       <c r="AP81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF81">
         <v>1.01</v>
@@ -20901,7 +20910,7 @@
         <v>1.01</v>
       </c>
       <c r="CB81" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="82" spans="1:80">
@@ -20909,16 +20918,16 @@
         <v>120</v>
       </c>
       <c r="B82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E82" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F82">
         <v>2.14</v>
@@ -20939,7 +20948,7 @@
         <v>3.65</v>
       </c>
       <c r="L82">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M82">
         <v>1.08</v>
@@ -20954,19 +20963,19 @@
         <v>1.89</v>
       </c>
       <c r="Q82">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R82">
         <v>1.33</v>
       </c>
       <c r="S82">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T82">
         <v>1.86</v>
       </c>
       <c r="U82">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V82">
         <v>1.34</v>
@@ -21056,7 +21065,7 @@
         <v>11.5</v>
       </c>
       <c r="AY82">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ82">
         <v>17</v>
@@ -21083,10 +21092,10 @@
         <v>42</v>
       </c>
       <c r="BH82">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI82">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="BJ82">
         <v>13.5</v>
@@ -21098,25 +21107,25 @@
         <v>1000</v>
       </c>
       <c r="BM82">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="BN82">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO82">
         <v>3.6</v>
       </c>
       <c r="BP82">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ82">
-        <v>1.72</v>
+        <v>3.95</v>
       </c>
       <c r="BR82">
         <v>44</v>
       </c>
       <c r="BS82">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="BT82">
         <v>9.800000000000001</v>
@@ -21128,22 +21137,22 @@
         <v>46</v>
       </c>
       <c r="BW82">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="BX82">
         <v>1000</v>
       </c>
       <c r="BY82">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BZ82">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA82">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="CB82" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83" spans="1:80">
@@ -21151,22 +21160,22 @@
         <v>121</v>
       </c>
       <c r="B83" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C83" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E83" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F83">
         <v>3.15</v>
       </c>
       <c r="G83">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H83">
         <v>2.28</v>
@@ -21184,7 +21193,7 @@
         <v>1.01</v>
       </c>
       <c r="M83">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N83">
         <v>3.9</v>
@@ -21196,7 +21205,7 @@
         <v>1.98</v>
       </c>
       <c r="Q83">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R83">
         <v>1.38</v>
@@ -21208,13 +21217,13 @@
         <v>1.72</v>
       </c>
       <c r="U83">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V83">
         <v>1.69</v>
       </c>
       <c r="W83">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X83">
         <v>18.5</v>
@@ -21280,7 +21289,7 @@
         <v>13.5</v>
       </c>
       <c r="AS83">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AT83">
         <v>12</v>
@@ -21385,7 +21394,7 @@
         <v>1.01</v>
       </c>
       <c r="CB83" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="84" spans="1:80">
@@ -21393,16 +21402,16 @@
         <v>122</v>
       </c>
       <c r="B84" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D84" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E84" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F84">
         <v>2.52</v>
@@ -21450,7 +21459,7 @@
         <v>1.84</v>
       </c>
       <c r="U84">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V84">
         <v>1.38</v>
@@ -21513,52 +21522,52 @@
         <v>1000</v>
       </c>
       <c r="AP84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF84">
         <v>1.01</v>
@@ -21627,240 +21636,240 @@
         <v>1.43</v>
       </c>
       <c r="CB84" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="85" spans="1:80">
       <c r="A85" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B85" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D85" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E85" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F85">
-        <v>1.95</v>
+        <v>1.12</v>
       </c>
       <c r="G85">
-        <v>2.16</v>
+        <v>600</v>
       </c>
       <c r="H85">
-        <v>3.9</v>
+        <v>1.12</v>
       </c>
       <c r="I85">
-        <v>4.9</v>
+        <v>870</v>
       </c>
       <c r="J85">
-        <v>3.4</v>
+        <v>1.16</v>
       </c>
       <c r="K85">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q85">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R85">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S85">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V85">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W85">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="X85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH85">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI85">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BJ85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BL85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BN85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BP85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BR85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BT85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BV85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BX85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY85">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BZ85">
         <v>0</v>
@@ -21869,240 +21878,240 @@
         <v>0</v>
       </c>
       <c r="CB85" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="86" spans="1:80">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D86" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E86" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F86">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="G86">
-        <v>600</v>
+        <v>2.16</v>
       </c>
       <c r="H86">
-        <v>1.12</v>
+        <v>3.9</v>
       </c>
       <c r="I86">
-        <v>870</v>
+        <v>4.9</v>
       </c>
       <c r="J86">
+        <v>3.4</v>
+      </c>
+      <c r="K86">
+        <v>4.4</v>
+      </c>
+      <c r="L86">
+        <v>1.01</v>
+      </c>
+      <c r="M86">
+        <v>1.08</v>
+      </c>
+      <c r="N86">
+        <v>3</v>
+      </c>
+      <c r="O86">
+        <v>1.36</v>
+      </c>
+      <c r="P86">
+        <v>1.68</v>
+      </c>
+      <c r="Q86">
+        <v>2.14</v>
+      </c>
+      <c r="R86">
         <v>1.16</v>
       </c>
-      <c r="K86">
-        <v>950</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>1.24</v>
-      </c>
-      <c r="Q86">
-        <v>1.01</v>
-      </c>
-      <c r="R86">
-        <v>0</v>
-      </c>
       <c r="S86">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH86">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI86">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BL86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BN86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BP86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BR86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BT86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BV86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BX86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BZ86">
         <v>0</v>
@@ -22111,7 +22120,7 @@
         <v>0</v>
       </c>
       <c r="CB86" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="87" spans="1:80">
@@ -22119,16 +22128,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C87" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E87" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F87">
         <v>2.98</v>
@@ -22146,7 +22155,7 @@
         <v>3.25</v>
       </c>
       <c r="K87">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L87">
         <v>1.01</v>
@@ -22155,7 +22164,7 @@
         <v>1.06</v>
       </c>
       <c r="N87">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O87">
         <v>1.34</v>
@@ -22164,16 +22173,16 @@
         <v>1.8</v>
       </c>
       <c r="Q87">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R87">
         <v>1.3</v>
       </c>
       <c r="S87">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T87">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="U87">
         <v>1.9</v>
@@ -22194,7 +22203,7 @@
         <v>17</v>
       </c>
       <c r="AA87">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB87">
         <v>12</v>
@@ -22206,7 +22215,7 @@
         <v>12.5</v>
       </c>
       <c r="AE87">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF87">
         <v>22</v>
@@ -22224,13 +22233,13 @@
         <v>60</v>
       </c>
       <c r="AK87">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL87">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM87">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN87">
         <v>36</v>
@@ -22239,7 +22248,7 @@
         <v>27</v>
       </c>
       <c r="AP87">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ87">
         <v>9</v>
@@ -22260,7 +22269,7 @@
         <v>10.5</v>
       </c>
       <c r="AW87">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX87">
         <v>17.5</v>
@@ -22287,7 +22296,7 @@
         <v>80</v>
       </c>
       <c r="BF87">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BG87">
         <v>19</v>
@@ -22353,7 +22362,249 @@
         <v>0</v>
       </c>
       <c r="CB87" t="s">
-        <v>317</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="1:80">
+      <c r="A88" t="s">
+        <v>123</v>
+      </c>
+      <c r="B88" t="s">
+        <v>124</v>
+      </c>
+      <c r="C88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D88" t="s">
+        <v>232</v>
+      </c>
+      <c r="E88" t="s">
+        <v>319</v>
+      </c>
+      <c r="F88">
+        <v>1.04</v>
+      </c>
+      <c r="G88">
+        <v>990</v>
+      </c>
+      <c r="H88">
+        <v>1.04</v>
+      </c>
+      <c r="I88">
+        <v>990</v>
+      </c>
+      <c r="J88">
+        <v>1.02</v>
+      </c>
+      <c r="K88">
+        <v>500</v>
+      </c>
+      <c r="L88">
+        <v>1.01</v>
+      </c>
+      <c r="M88">
+        <v>1.01</v>
+      </c>
+      <c r="N88">
+        <v>1.24</v>
+      </c>
+      <c r="O88">
+        <v>1.41</v>
+      </c>
+      <c r="P88">
+        <v>1.24</v>
+      </c>
+      <c r="Q88">
+        <v>1.41</v>
+      </c>
+      <c r="R88">
+        <v>1.18</v>
+      </c>
+      <c r="S88">
+        <v>1.4</v>
+      </c>
+      <c r="T88">
+        <v>1.11</v>
+      </c>
+      <c r="U88">
+        <v>1.11</v>
+      </c>
+      <c r="V88">
+        <v>1.01</v>
+      </c>
+      <c r="W88">
+        <v>1.01</v>
+      </c>
+      <c r="X88">
+        <v>1000</v>
+      </c>
+      <c r="Y88">
+        <v>1000</v>
+      </c>
+      <c r="Z88">
+        <v>1000</v>
+      </c>
+      <c r="AA88">
+        <v>1000</v>
+      </c>
+      <c r="AB88">
+        <v>1000</v>
+      </c>
+      <c r="AC88">
+        <v>1000</v>
+      </c>
+      <c r="AD88">
+        <v>1000</v>
+      </c>
+      <c r="AE88">
+        <v>1000</v>
+      </c>
+      <c r="AF88">
+        <v>1000</v>
+      </c>
+      <c r="AG88">
+        <v>1000</v>
+      </c>
+      <c r="AH88">
+        <v>1000</v>
+      </c>
+      <c r="AI88">
+        <v>1000</v>
+      </c>
+      <c r="AJ88">
+        <v>1000</v>
+      </c>
+      <c r="AK88">
+        <v>1000</v>
+      </c>
+      <c r="AL88">
+        <v>1000</v>
+      </c>
+      <c r="AM88">
+        <v>1000</v>
+      </c>
+      <c r="AN88">
+        <v>1000</v>
+      </c>
+      <c r="AO88">
+        <v>1000</v>
+      </c>
+      <c r="AP88">
+        <v>1.01</v>
+      </c>
+      <c r="AQ88">
+        <v>1.01</v>
+      </c>
+      <c r="AR88">
+        <v>1.01</v>
+      </c>
+      <c r="AS88">
+        <v>1.01</v>
+      </c>
+      <c r="AT88">
+        <v>1.01</v>
+      </c>
+      <c r="AU88">
+        <v>1.01</v>
+      </c>
+      <c r="AV88">
+        <v>1.01</v>
+      </c>
+      <c r="AW88">
+        <v>1.01</v>
+      </c>
+      <c r="AX88">
+        <v>1.01</v>
+      </c>
+      <c r="AY88">
+        <v>1.01</v>
+      </c>
+      <c r="AZ88">
+        <v>1.01</v>
+      </c>
+      <c r="BA88">
+        <v>1.01</v>
+      </c>
+      <c r="BB88">
+        <v>1.01</v>
+      </c>
+      <c r="BC88">
+        <v>1.01</v>
+      </c>
+      <c r="BD88">
+        <v>1.01</v>
+      </c>
+      <c r="BE88">
+        <v>1.01</v>
+      </c>
+      <c r="BF88">
+        <v>1.01</v>
+      </c>
+      <c r="BG88">
+        <v>1.01</v>
+      </c>
+      <c r="BH88">
+        <v>1000</v>
+      </c>
+      <c r="BI88">
+        <v>1.04</v>
+      </c>
+      <c r="BJ88">
+        <v>1000</v>
+      </c>
+      <c r="BK88">
+        <v>1.04</v>
+      </c>
+      <c r="BL88">
+        <v>1000</v>
+      </c>
+      <c r="BM88">
+        <v>1.04</v>
+      </c>
+      <c r="BN88">
+        <v>1000</v>
+      </c>
+      <c r="BO88">
+        <v>1.04</v>
+      </c>
+      <c r="BP88">
+        <v>1000</v>
+      </c>
+      <c r="BQ88">
+        <v>1.04</v>
+      </c>
+      <c r="BR88">
+        <v>1000</v>
+      </c>
+      <c r="BS88">
+        <v>1.04</v>
+      </c>
+      <c r="BT88">
+        <v>1000</v>
+      </c>
+      <c r="BU88">
+        <v>1.04</v>
+      </c>
+      <c r="BV88">
+        <v>1000</v>
+      </c>
+      <c r="BW88">
+        <v>1.04</v>
+      </c>
+      <c r="BX88">
+        <v>1000</v>
+      </c>
+      <c r="BY88">
+        <v>1.04</v>
+      </c>
+      <c r="BZ88">
+        <v>1000</v>
+      </c>
+      <c r="CA88">
+        <v>1.04</v>
+      </c>
+      <c r="CB88" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="323">
   <si>
     <t>League</t>
   </si>
@@ -370,21 +370,21 @@
     <t>Belgian Pro League</t>
   </si>
   <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>Italian Serie C</t>
+  </si>
+  <si>
     <t>English Premier League</t>
   </si>
   <si>
-    <t>Italian Serie C</t>
-  </si>
-  <si>
-    <t>Spanish La Liga</t>
-  </si>
-  <si>
-    <t>Spanish Segunda Division</t>
-  </si>
-  <si>
-    <t>Uruguayan Primera Division</t>
-  </si>
-  <si>
     <t>Venezuelan Primera Division</t>
   </si>
   <si>
@@ -682,27 +682,30 @@
     <t>Wexford F.C</t>
   </si>
   <si>
+    <t>Albion FC</t>
+  </si>
+  <si>
+    <t>Cordoba</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>Union Brescia</t>
+  </si>
+  <si>
+    <t>FC Vado</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>Arsenal</t>
   </si>
   <si>
     <t>ASD Alcione</t>
   </si>
   <si>
-    <t>FC Vado</t>
-  </si>
-  <si>
-    <t>Union Brescia</t>
-  </si>
-  <si>
-    <t>Betis</t>
-  </si>
-  <si>
-    <t>Cordoba</t>
-  </si>
-  <si>
-    <t>Albion FC</t>
-  </si>
-  <si>
     <t>Grotta</t>
   </si>
   <si>
@@ -943,27 +946,30 @@
     <t>Athlone Town</t>
   </si>
   <si>
+    <t>Boston River</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Carpi</t>
+  </si>
+  <si>
+    <t>Atalanta U23</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
     <t>Coventry</t>
   </si>
   <si>
     <t>Renate</t>
   </si>
   <si>
-    <t>Atalanta U23</t>
-  </si>
-  <si>
-    <t>Carpi</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Girona</t>
-  </si>
-  <si>
-    <t>Boston River</t>
-  </si>
-  <si>
     <t>IR Reykjavik</t>
   </si>
   <si>
@@ -976,7 +982,7 @@
     <t>Trujillanos</t>
   </si>
   <si>
-    <t>2026-08-19 19:39:32</t>
+    <t>2026-08-19 21:52:20</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB88"/>
+  <dimension ref="A1:CB89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1567,22 +1573,22 @@
         <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F2">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.25</v>
@@ -1591,19 +1597,19 @@
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
         <v>2.3</v>
       </c>
       <c r="O2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P2">
         <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
         <v>1.16</v>
@@ -1612,16 +1618,16 @@
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="X2">
         <v>7.4</v>
@@ -1630,37 +1636,37 @@
         <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AB2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>40</v>
       </c>
       <c r="AI2">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>36</v>
@@ -1669,37 +1675,37 @@
         <v>95</v>
       </c>
       <c r="AM2">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO2">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="AP2">
         <v>5.7</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX2">
         <v>8.800000000000001</v>
@@ -1708,34 +1714,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
         <v>21</v>
       </c>
       <c r="BC2">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BD2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG2">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI2">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2">
         <v>13.5</v>
@@ -1750,16 +1756,16 @@
         <v>2.16</v>
       </c>
       <c r="BN2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO2">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1768,16 +1774,16 @@
         <v>13.5</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>2.12</v>
+        <v>14.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1786,13 +1792,13 @@
         <v>15.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA2">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="CB2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1809,13 +1815,13 @@
         <v>147</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F3">
         <v>1.66</v>
       </c>
       <c r="G3">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H3">
         <v>5.6</v>
@@ -1854,7 +1860,7 @@
         <v>3</v>
       </c>
       <c r="T3">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="U3">
         <v>1.96</v>
@@ -1863,7 +1869,7 @@
         <v>1.19</v>
       </c>
       <c r="W3">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X3">
         <v>22</v>
@@ -1872,7 +1878,7 @@
         <v>950</v>
       </c>
       <c r="Z3">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1890,7 +1896,7 @@
         <v>100</v>
       </c>
       <c r="AF3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AG3">
         <v>950</v>
@@ -1920,16 +1926,16 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="AQ3">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AR3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AS3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1938,40 +1944,40 @@
         <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AW3">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY3">
         <v>7.2</v>
       </c>
       <c r="AZ3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB3">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BC3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BD3">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BF3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BG3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2034,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -2051,7 +2057,7 @@
         <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F4">
         <v>1.52</v>
@@ -2078,7 +2084,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
         <v>1.29</v>
@@ -2087,7 +2093,7 @@
         <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R4">
         <v>1.31</v>
@@ -2114,13 +2120,13 @@
         <v>950</v>
       </c>
       <c r="Z4">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AC4">
         <v>950</v>
@@ -2132,7 +2138,7 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AG4">
         <v>950</v>
@@ -2144,13 +2150,13 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AK4">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AL4">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -2162,58 +2168,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AQ4">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AR4">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AS4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AT4">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="AU4">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AV4">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AW4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AX4">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AY4">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AZ4">
-        <v>1.17</v>
+        <v>5.4</v>
       </c>
       <c r="BA4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BB4">
         <v>3.95</v>
       </c>
       <c r="BC4">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD4">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BE4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BF4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2276,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2293,7 +2299,7 @@
         <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F5">
         <v>1.33</v>
@@ -2308,7 +2314,7 @@
         <v>990</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>10.5</v>
@@ -2323,7 +2329,7 @@
         <v>3.05</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
         <v>1.86</v>
@@ -2347,7 +2353,7 @@
         <v>1.01</v>
       </c>
       <c r="W5">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2518,7 +2524,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2535,7 +2541,7 @@
         <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F6">
         <v>2.34</v>
@@ -2547,16 +2553,16 @@
         <v>3.6</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
         <v>1.12</v>
@@ -2565,46 +2571,46 @@
         <v>2.6</v>
       </c>
       <c r="O6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P6">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q6">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
         <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA6">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>8.6</v>
@@ -2613,19 +2619,19 @@
         <v>20</v>
       </c>
       <c r="AE6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
         <v>44</v>
@@ -2637,19 +2643,19 @@
         <v>75</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO6">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
         <v>18</v>
@@ -2658,13 +2664,13 @@
         <v>4.2</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU6">
         <v>5.4</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW6">
         <v>4.1</v>
@@ -2673,10 +2679,10 @@
         <v>10</v>
       </c>
       <c r="AY6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
         <v>4.2</v>
@@ -2685,10 +2691,10 @@
         <v>4</v>
       </c>
       <c r="BC6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BD6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE6">
         <v>4.3</v>
@@ -2700,28 +2706,28 @@
         <v>4.2</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6">
         <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN6">
         <v>5.9</v>
       </c>
       <c r="BO6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP6">
         <v>25</v>
@@ -2733,7 +2739,7 @@
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT6">
         <v>8</v>
@@ -2745,22 +2751,22 @@
         <v>44</v>
       </c>
       <c r="BW6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX6">
         <v>70</v>
       </c>
       <c r="BY6">
+        <v>4.7</v>
+      </c>
+      <c r="BZ6">
+        <v>60</v>
+      </c>
+      <c r="CA6">
         <v>4.6</v>
       </c>
-      <c r="BZ6">
-        <v>55</v>
-      </c>
-      <c r="CA6">
-        <v>4.5</v>
-      </c>
       <c r="CB6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2777,7 +2783,7 @@
         <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3002,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -3019,7 +3025,7 @@
         <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F8">
         <v>1.92</v>
@@ -3046,7 +3052,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="O8">
         <v>1.19</v>
@@ -3244,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3261,7 +3267,7 @@
         <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9">
         <v>7.2</v>
@@ -3486,7 +3492,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3503,7 +3509,7 @@
         <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F10">
         <v>1.35</v>
@@ -3530,13 +3536,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O10">
         <v>1.19</v>
       </c>
       <c r="P10">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q10">
         <v>1.18</v>
@@ -3728,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3745,13 +3751,13 @@
         <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F11">
         <v>1.35</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="H11">
         <v>2.3</v>
@@ -3760,7 +3766,7 @@
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.45</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3772,13 +3778,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q11">
         <v>1.18</v>
@@ -3970,7 +3976,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3987,7 +3993,7 @@
         <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F12">
         <v>2.32</v>
@@ -4005,7 +4011,7 @@
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -4020,10 +4026,10 @@
         <v>1.32</v>
       </c>
       <c r="P12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R12">
         <v>1.32</v>
@@ -4212,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -4229,7 +4235,7 @@
         <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F13">
         <v>1.91</v>
@@ -4268,7 +4274,7 @@
         <v>1.43</v>
       </c>
       <c r="R13">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="S13">
         <v>1.89</v>
@@ -4454,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4471,7 +4477,7 @@
         <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F14">
         <v>1.55</v>
@@ -4498,13 +4504,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O14">
         <v>1.24</v>
       </c>
       <c r="P14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q14">
         <v>1.66</v>
@@ -4696,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4713,193 +4719,193 @@
         <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F15">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G15">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H15">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I15">
+        <v>3.55</v>
+      </c>
+      <c r="J15">
+        <v>3.6</v>
+      </c>
+      <c r="K15">
         <v>4.4</v>
       </c>
-      <c r="J15">
-        <v>3.5</v>
-      </c>
-      <c r="K15">
-        <v>4.1</v>
-      </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O15">
         <v>1.23</v>
       </c>
       <c r="P15">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="Q15">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="R15">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="S15">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X15">
+        <v>26</v>
+      </c>
+      <c r="Y15">
         <v>21</v>
       </c>
-      <c r="Y15">
-        <v>18.5</v>
-      </c>
       <c r="Z15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA15">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB15">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF15">
         <v>18</v>
       </c>
       <c r="AG15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AI15">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK15">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN15">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO15">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AP15">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ15">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR15">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS15">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AT15">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="AU15">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="AV15">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AW15">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AX15">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AY15">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AZ15">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BA15">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB15">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BC15">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD15">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE15">
+        <v>5</v>
+      </c>
+      <c r="BF15">
         <v>4</v>
       </c>
-      <c r="BF15">
-        <v>3.4</v>
-      </c>
       <c r="BG15">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH15">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BI15">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="BJ15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BL15">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BM15">
         <v>4.5</v>
       </c>
       <c r="BN15">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BO15">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BP15">
         <v>18.5</v>
@@ -4908,37 +4914,37 @@
         <v>3.75</v>
       </c>
       <c r="BR15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU15">
         <v>3</v>
       </c>
       <c r="BV15">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BW15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BX15">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BY15">
         <v>4.2</v>
       </c>
       <c r="BZ15">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="CA15">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="CB15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4955,13 +4961,13 @@
         <v>160</v>
       </c>
       <c r="E16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F16">
         <v>2.62</v>
       </c>
       <c r="G16">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H16">
         <v>2.12</v>
@@ -5009,7 +5015,7 @@
         <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5180,7 +5186,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -5197,7 +5203,7 @@
         <v>161</v>
       </c>
       <c r="E17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F17">
         <v>1.62</v>
@@ -5248,7 +5254,7 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W17">
         <v>2.02</v>
@@ -5422,7 +5428,7 @@
         <v>1.28</v>
       </c>
       <c r="CB17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5439,7 +5445,7 @@
         <v>162</v>
       </c>
       <c r="E18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F18">
         <v>1.37</v>
@@ -5475,7 +5481,7 @@
         <v>2.86</v>
       </c>
       <c r="Q18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R18">
         <v>1.75</v>
@@ -5511,7 +5517,7 @@
         <v>14.5</v>
       </c>
       <c r="AC18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD18">
         <v>32</v>
@@ -5520,7 +5526,7 @@
         <v>110</v>
       </c>
       <c r="AF18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
@@ -5550,16 +5556,16 @@
         <v>95</v>
       </c>
       <c r="AP18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18">
         <v>11</v>
@@ -5571,7 +5577,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5583,7 +5589,7 @@
         <v>18</v>
       </c>
       <c r="BA18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB18">
         <v>11</v>
@@ -5595,13 +5601,13 @@
         <v>9</v>
       </c>
       <c r="BE18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF18">
         <v>3.85</v>
       </c>
       <c r="BG18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5664,7 +5670,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5681,7 +5687,7 @@
         <v>163</v>
       </c>
       <c r="E19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F19">
         <v>2.1</v>
@@ -5906,7 +5912,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5923,7 +5929,7 @@
         <v>164</v>
       </c>
       <c r="E20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F20">
         <v>1.99</v>
@@ -5941,7 +5947,7 @@
         <v>3.55</v>
       </c>
       <c r="K20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
         <v>1.27</v>
@@ -5953,10 +5959,10 @@
         <v>3.8</v>
       </c>
       <c r="O20">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q20">
         <v>1.71</v>
@@ -5965,7 +5971,7 @@
         <v>1.37</v>
       </c>
       <c r="S20">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="T20">
         <v>1.11</v>
@@ -5974,7 +5980,7 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
         <v>1.81</v>
@@ -6148,7 +6154,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -6165,25 +6171,25 @@
         <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F21">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="G21">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="H21">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I21">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J21">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L21">
         <v>1.22</v>
@@ -6198,133 +6204,133 @@
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="Q21">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="R21">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S21">
         <v>2.22</v>
       </c>
       <c r="T21">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="U21">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="X21">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Y21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z21">
+        <v>60</v>
+      </c>
+      <c r="AA21">
+        <v>130</v>
+      </c>
+      <c r="AB21">
+        <v>13.5</v>
+      </c>
+      <c r="AC21">
+        <v>15</v>
+      </c>
+      <c r="AD21">
+        <v>27</v>
+      </c>
+      <c r="AE21">
+        <v>65</v>
+      </c>
+      <c r="AF21">
+        <v>15.5</v>
+      </c>
+      <c r="AG21">
+        <v>12.5</v>
+      </c>
+      <c r="AH21">
+        <v>23</v>
+      </c>
+      <c r="AI21">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
+        <v>18</v>
+      </c>
+      <c r="AK21">
+        <v>18</v>
+      </c>
+      <c r="AL21">
+        <v>29</v>
+      </c>
+      <c r="AM21">
+        <v>85</v>
+      </c>
+      <c r="AN21">
+        <v>6.2</v>
+      </c>
+      <c r="AO21">
         <v>48</v>
       </c>
-      <c r="AA21">
-        <v>110</v>
-      </c>
-      <c r="AB21">
-        <v>15</v>
-      </c>
-      <c r="AC21">
+      <c r="AP21">
+        <v>4.9</v>
+      </c>
+      <c r="AQ21">
+        <v>19.5</v>
+      </c>
+      <c r="AR21">
+        <v>5.1</v>
+      </c>
+      <c r="AS21">
+        <v>5.4</v>
+      </c>
+      <c r="AT21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU21">
+        <v>10.5</v>
+      </c>
+      <c r="AV21">
+        <v>18</v>
+      </c>
+      <c r="AW21">
+        <v>36</v>
+      </c>
+      <c r="AX21">
+        <v>9.6</v>
+      </c>
+      <c r="AY21">
+        <v>7.6</v>
+      </c>
+      <c r="AZ21">
         <v>13.5</v>
       </c>
-      <c r="AD21">
-        <v>23</v>
-      </c>
-      <c r="AE21">
-        <v>55</v>
-      </c>
-      <c r="AF21">
-        <v>15</v>
-      </c>
-      <c r="AG21">
-        <v>13</v>
-      </c>
-      <c r="AH21">
-        <v>17</v>
-      </c>
-      <c r="AI21">
-        <v>55</v>
-      </c>
-      <c r="AJ21">
-        <v>24</v>
-      </c>
-      <c r="AK21">
-        <v>17.5</v>
-      </c>
-      <c r="AL21">
-        <v>32</v>
-      </c>
-      <c r="AM21">
-        <v>75</v>
-      </c>
-      <c r="AN21">
-        <v>7.4</v>
-      </c>
-      <c r="AO21">
-        <v>34</v>
-      </c>
-      <c r="AP21">
+      <c r="BA21">
+        <v>5.1</v>
+      </c>
+      <c r="BB21">
+        <v>12</v>
+      </c>
+      <c r="BC21">
+        <v>10.5</v>
+      </c>
+      <c r="BD21">
         <v>20</v>
       </c>
-      <c r="AQ21">
-        <v>20</v>
-      </c>
-      <c r="AR21">
-        <v>5.2</v>
-      </c>
-      <c r="AS21">
-        <v>5.5</v>
-      </c>
-      <c r="AT21">
-        <v>12</v>
-      </c>
-      <c r="AU21">
-        <v>9.4</v>
-      </c>
-      <c r="AV21">
-        <v>13.5</v>
-      </c>
-      <c r="AW21">
-        <v>34</v>
-      </c>
-      <c r="AX21">
-        <v>12</v>
-      </c>
-      <c r="AY21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21">
-        <v>12</v>
-      </c>
-      <c r="BA21">
-        <v>32</v>
-      </c>
-      <c r="BB21">
-        <v>14.5</v>
-      </c>
-      <c r="BC21">
-        <v>12</v>
-      </c>
-      <c r="BD21">
-        <v>21</v>
-      </c>
       <c r="BE21">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF21">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BG21">
         <v>5</v>
@@ -6336,61 +6342,61 @@
         <v>3.65</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK21">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BL21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BN21">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BO21">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BP21">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ21">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BR21">
         <v>24</v>
       </c>
       <c r="BS21">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BT21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU21">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BV21">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BW21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BX21">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BY21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA21">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CB21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6407,19 +6413,19 @@
         <v>166</v>
       </c>
       <c r="E22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F22">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="G22">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="H22">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="I22">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="J22">
         <v>3.55</v>
@@ -6431,19 +6437,19 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P22">
         <v>2.14</v>
       </c>
       <c r="Q22">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R22">
         <v>1.37</v>
@@ -6458,10 +6464,10 @@
         <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6632,7 +6638,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6649,7 +6655,7 @@
         <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F23">
         <v>1.12</v>
@@ -6874,7 +6880,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6891,7 +6897,7 @@
         <v>168</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F24">
         <v>2.62</v>
@@ -7116,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -7133,7 +7139,7 @@
         <v>169</v>
       </c>
       <c r="E25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F25">
         <v>9.800000000000001</v>
@@ -7169,7 +7175,7 @@
         <v>3.5</v>
       </c>
       <c r="Q25">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R25">
         <v>2</v>
@@ -7358,7 +7364,7 @@
         <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7375,22 +7381,22 @@
         <v>170</v>
       </c>
       <c r="E26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F26">
         <v>3.2</v>
       </c>
       <c r="G26">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H26">
         <v>1.87</v>
       </c>
       <c r="I26">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="J26">
-        <v>1.09</v>
+        <v>2.72</v>
       </c>
       <c r="K26">
         <v>6.6</v>
@@ -7402,19 +7408,19 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.34</v>
+        <v>1.1</v>
       </c>
       <c r="O26">
         <v>1.2</v>
       </c>
       <c r="P26">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
         <v>1.57</v>
       </c>
       <c r="R26">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S26">
         <v>2.42</v>
@@ -7423,10 +7429,10 @@
         <v>1.48</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W26">
         <v>1.28</v>
@@ -7600,7 +7606,7 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7617,22 +7623,22 @@
         <v>171</v>
       </c>
       <c r="E27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F27">
         <v>2.78</v>
       </c>
       <c r="G27">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H27">
         <v>2.3</v>
       </c>
       <c r="I27">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="J27">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K27">
         <v>4.3</v>
@@ -7644,19 +7650,19 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O27">
         <v>1.15</v>
       </c>
       <c r="P27">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q27">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="R27">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S27">
         <v>2.3</v>
@@ -7842,7 +7848,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7859,7 +7865,7 @@
         <v>172</v>
       </c>
       <c r="E28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F28">
         <v>3.45</v>
@@ -8084,7 +8090,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -8101,13 +8107,13 @@
         <v>173</v>
       </c>
       <c r="E29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F29">
         <v>1.93</v>
       </c>
       <c r="G29">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H29">
         <v>3.85</v>
@@ -8143,19 +8149,19 @@
         <v>1.81</v>
       </c>
       <c r="S29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T29">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="U29">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="V29">
         <v>1.34</v>
       </c>
       <c r="W29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X29">
         <v>42</v>
@@ -8170,19 +8176,19 @@
         <v>100</v>
       </c>
       <c r="AB29">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC29">
         <v>12</v>
       </c>
       <c r="AD29">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE29">
         <v>44</v>
       </c>
       <c r="AF29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -8191,13 +8197,13 @@
         <v>15.5</v>
       </c>
       <c r="AI29">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK29">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL29">
         <v>29</v>
@@ -8206,52 +8212,52 @@
         <v>65</v>
       </c>
       <c r="AN29">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO29">
         <v>20</v>
       </c>
       <c r="AP29">
+        <v>7.4</v>
+      </c>
+      <c r="AQ29">
+        <v>21</v>
+      </c>
+      <c r="AR29">
         <v>7.6</v>
-      </c>
-      <c r="AQ29">
-        <v>16.5</v>
-      </c>
-      <c r="AR29">
-        <v>28</v>
       </c>
       <c r="AS29">
         <v>8.4</v>
       </c>
       <c r="AT29">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU29">
         <v>10</v>
       </c>
       <c r="AV29">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW29">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="AX29">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY29">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA29">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BB29">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC29">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD29">
         <v>19.5</v>
@@ -8263,7 +8269,7 @@
         <v>6.2</v>
       </c>
       <c r="BG29">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8326,7 +8332,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8343,7 +8349,7 @@
         <v>174</v>
       </c>
       <c r="E30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F30">
         <v>1.81</v>
@@ -8568,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8585,10 +8591,10 @@
         <v>175</v>
       </c>
       <c r="E31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F31">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="G31">
         <v>2.3</v>
@@ -8600,7 +8606,7 @@
         <v>4.6</v>
       </c>
       <c r="J31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K31">
         <v>950</v>
@@ -8624,10 +8630,10 @@
         <v>2</v>
       </c>
       <c r="R31">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8810,7 +8816,7 @@
         <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8827,7 +8833,7 @@
         <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F32">
         <v>4.6</v>
@@ -9052,7 +9058,7 @@
         <v>1.53</v>
       </c>
       <c r="CB32" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -9069,7 +9075,7 @@
         <v>177</v>
       </c>
       <c r="E33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F33">
         <v>1.2</v>
@@ -9237,64 +9243,64 @@
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9311,7 +9317,7 @@
         <v>178</v>
       </c>
       <c r="E34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F34">
         <v>1.52</v>
@@ -9536,7 +9542,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9553,7 +9559,7 @@
         <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F35">
         <v>2.62</v>
@@ -9778,7 +9784,7 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9795,7 +9801,7 @@
         <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F36">
         <v>2.6</v>
@@ -9846,10 +9852,10 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -10020,7 +10026,7 @@
         <v>1.04</v>
       </c>
       <c r="CB36" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -10037,67 +10043,67 @@
         <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F37">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G37">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="H37">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I37">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K37">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L37">
         <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="O37">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P37">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q37">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R37">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S37">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T37">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U37">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W37">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="X37">
         <v>25</v>
       </c>
       <c r="Y37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z37">
         <v>55</v>
@@ -10106,43 +10112,43 @@
         <v>160</v>
       </c>
       <c r="AB37">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC37">
         <v>12.5</v>
       </c>
       <c r="AD37">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE37">
         <v>80</v>
       </c>
       <c r="AF37">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AG37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI37">
         <v>75</v>
       </c>
       <c r="AJ37">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AK37">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AL37">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM37">
         <v>110</v>
       </c>
       <c r="AN37">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO37">
         <v>80</v>
@@ -10151,55 +10157,55 @@
         <v>15</v>
       </c>
       <c r="AQ37">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AR37">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="AS37">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU37">
+        <v>8</v>
+      </c>
+      <c r="AV37">
+        <v>20</v>
+      </c>
+      <c r="AW37">
         <v>7.8</v>
       </c>
-      <c r="AU37">
-        <v>7.4</v>
-      </c>
-      <c r="AV37">
-        <v>15.5</v>
-      </c>
-      <c r="AW37">
-        <v>4</v>
-      </c>
       <c r="AX37">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY37">
+        <v>9</v>
+      </c>
+      <c r="AZ37">
+        <v>17.5</v>
+      </c>
+      <c r="BA37">
         <v>7.6</v>
       </c>
-      <c r="AZ37">
+      <c r="BB37">
         <v>13.5</v>
-      </c>
-      <c r="BA37">
-        <v>4</v>
-      </c>
-      <c r="BB37">
-        <v>12.5</v>
       </c>
       <c r="BC37">
         <v>12</v>
       </c>
       <c r="BD37">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BE37">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BF37">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG37">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10262,7 +10268,7 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -10279,7 +10285,7 @@
         <v>182</v>
       </c>
       <c r="E38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F38">
         <v>1.53</v>
@@ -10504,7 +10510,7 @@
         <v>1.42</v>
       </c>
       <c r="CB38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10521,10 +10527,10 @@
         <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F39">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G39">
         <v>3.95</v>
@@ -10533,7 +10539,7 @@
         <v>1.98</v>
       </c>
       <c r="I39">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J39">
         <v>3.8</v>
@@ -10548,7 +10554,7 @@
         <v>1.02</v>
       </c>
       <c r="N39">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O39">
         <v>1.14</v>
@@ -10566,13 +10572,13 @@
         <v>2.06</v>
       </c>
       <c r="T39">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="U39">
-        <v>1.11</v>
+        <v>2.68</v>
       </c>
       <c r="V39">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W39">
         <v>1.33</v>
@@ -10746,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10763,7 +10769,7 @@
         <v>184</v>
       </c>
       <c r="E40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F40">
         <v>3.9</v>
@@ -10796,10 +10802,10 @@
         <v>1.39</v>
       </c>
       <c r="P40">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="R40">
         <v>1.2</v>
@@ -10820,7 +10826,7 @@
         <v>1.32</v>
       </c>
       <c r="X40">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y40">
         <v>11.5</v>
@@ -10877,7 +10883,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ40">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="AR40">
         <v>9.4</v>
@@ -10886,13 +10892,13 @@
         <v>19</v>
       </c>
       <c r="AT40">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AU40">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AV40">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AW40">
         <v>17.5</v>
@@ -10901,28 +10907,28 @@
         <v>16.5</v>
       </c>
       <c r="AY40">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="AZ40">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="BA40">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="BB40">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="BC40">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="BD40">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="BE40">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="BF40">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="BG40">
         <v>15.5</v>
@@ -10988,7 +10994,7 @@
         <v>1.74</v>
       </c>
       <c r="CB40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -11005,7 +11011,7 @@
         <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F41">
         <v>3.6</v>
@@ -11041,7 +11047,7 @@
         <v>2.2</v>
       </c>
       <c r="Q41">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="R41">
         <v>1.39</v>
@@ -11173,55 +11179,55 @@
         <v>1000</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ41">
         <v>1000</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN41">
         <v>1000</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP41">
         <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT41">
         <v>1000</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV41">
         <v>1000</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ41">
         <v>0</v>
@@ -11230,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -11247,22 +11253,22 @@
         <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F42">
+        <v>3.7</v>
+      </c>
+      <c r="G42">
         <v>4</v>
       </c>
-      <c r="G42">
-        <v>4.5</v>
-      </c>
       <c r="H42">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="I42">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="J42">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K42">
         <v>3.15</v>
@@ -11271,13 +11277,13 @@
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N42">
         <v>2.48</v>
       </c>
       <c r="O42">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P42">
         <v>1.5</v>
@@ -11298,10 +11304,10 @@
         <v>1.74</v>
       </c>
       <c r="V42">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X42">
         <v>9.199999999999999</v>
@@ -11316,7 +11322,7 @@
         <v>38</v>
       </c>
       <c r="AB42">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC42">
         <v>7.2</v>
@@ -11331,7 +11337,7 @@
         <v>30</v>
       </c>
       <c r="AG42">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH42">
         <v>25</v>
@@ -11343,7 +11349,7 @@
         <v>110</v>
       </c>
       <c r="AK42">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL42">
         <v>110</v>
@@ -11367,7 +11373,7 @@
         <v>11</v>
       </c>
       <c r="AS42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT42">
         <v>8.800000000000001</v>
@@ -11379,76 +11385,76 @@
         <v>10.5</v>
       </c>
       <c r="AW42">
+        <v>6.6</v>
+      </c>
+      <c r="AX42">
         <v>6.4</v>
-      </c>
-      <c r="AX42">
-        <v>6</v>
       </c>
       <c r="AY42">
         <v>13</v>
       </c>
       <c r="AZ42">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA42">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB42">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC42">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD42">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE42">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF42">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH42">
         <v>1000</v>
       </c>
       <c r="BI42">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BJ42">
         <v>16</v>
       </c>
       <c r="BK42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BN42">
         <v>9.6</v>
       </c>
       <c r="BO42">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP42">
         <v>1000</v>
       </c>
       <c r="BQ42">
+        <v>1.64</v>
+      </c>
+      <c r="BR42">
+        <v>1000</v>
+      </c>
+      <c r="BS42">
         <v>1.66</v>
       </c>
-      <c r="BR42">
-        <v>1000</v>
-      </c>
-      <c r="BS42">
-        <v>1.67</v>
-      </c>
       <c r="BT42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU42">
         <v>3.55</v>
@@ -11457,22 +11463,22 @@
         <v>30</v>
       </c>
       <c r="BW42">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BZ42">
         <v>1000</v>
       </c>
       <c r="CA42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CB42" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11489,7 +11495,7 @@
         <v>187</v>
       </c>
       <c r="E43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -11534,7 +11540,7 @@
         <v>3.25</v>
       </c>
       <c r="T43">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U43">
         <v>2.14</v>
@@ -11714,7 +11720,7 @@
         <v>16.5</v>
       </c>
       <c r="CB43" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11731,7 +11737,7 @@
         <v>188</v>
       </c>
       <c r="E44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F44">
         <v>2.22</v>
@@ -11743,7 +11749,7 @@
         <v>3.25</v>
       </c>
       <c r="I44">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J44">
         <v>3.45</v>
@@ -11755,10 +11761,10 @@
         <v>1.01</v>
       </c>
       <c r="M44">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N44">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O44">
         <v>1.31</v>
@@ -11770,16 +11776,16 @@
         <v>1.92</v>
       </c>
       <c r="R44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S44">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T44">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U44">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V44">
         <v>1.38</v>
@@ -11956,7 +11962,7 @@
         <v>1.32</v>
       </c>
       <c r="CB44" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11973,7 +11979,7 @@
         <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F45">
         <v>4.3</v>
@@ -12084,7 +12090,7 @@
         <v>8.6</v>
       </c>
       <c r="AP45">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AQ45">
         <v>10</v>
@@ -12198,7 +12204,7 @@
         <v>1.04</v>
       </c>
       <c r="CB45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -12215,7 +12221,7 @@
         <v>190</v>
       </c>
       <c r="E46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F46">
         <v>1.77</v>
@@ -12257,13 +12263,13 @@
         <v>1.72</v>
       </c>
       <c r="S46">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T46">
         <v>1.5</v>
       </c>
       <c r="U46">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V46">
         <v>1.27</v>
@@ -12374,7 +12380,7 @@
         <v>4.7</v>
       </c>
       <c r="BF46">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG46">
         <v>20</v>
@@ -12440,7 +12446,7 @@
         <v>1.01</v>
       </c>
       <c r="CB46" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12457,10 +12463,10 @@
         <v>191</v>
       </c>
       <c r="E47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F47">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="G47">
         <v>990</v>
@@ -12469,10 +12475,10 @@
         <v>1.05</v>
       </c>
       <c r="I47">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="J47">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12484,7 +12490,7 @@
         <v>1.01</v>
       </c>
       <c r="N47">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O47">
         <v>1.06</v>
@@ -12496,7 +12502,7 @@
         <v>1.06</v>
       </c>
       <c r="R47">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="S47">
         <v>1.05</v>
@@ -12508,7 +12514,7 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="W47">
         <v>1.02</v>
@@ -12682,7 +12688,7 @@
         <v>1.01</v>
       </c>
       <c r="CB47" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" spans="1:80">
@@ -12699,7 +12705,7 @@
         <v>192</v>
       </c>
       <c r="E48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F48">
         <v>2.98</v>
@@ -12717,7 +12723,7 @@
         <v>3.25</v>
       </c>
       <c r="K48">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L48">
         <v>1.37</v>
@@ -12726,13 +12732,13 @@
         <v>1.01</v>
       </c>
       <c r="N48">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O48">
         <v>1.38</v>
       </c>
       <c r="P48">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q48">
         <v>2.02</v>
@@ -12924,7 +12930,7 @@
         <v>1.04</v>
       </c>
       <c r="CB48" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" spans="1:80">
@@ -12941,7 +12947,7 @@
         <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F49">
         <v>2.62</v>
@@ -12950,10 +12956,10 @@
         <v>2.86</v>
       </c>
       <c r="H49">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I49">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J49">
         <v>3.35</v>
@@ -12992,7 +12998,7 @@
         <v>2.04</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
         <v>1.53</v>
@@ -13109,7 +13115,7 @@
         <v>3.85</v>
       </c>
       <c r="BI49">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ49">
         <v>13.5</v>
@@ -13166,7 +13172,7 @@
         <v>3.25</v>
       </c>
       <c r="CB49" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:80">
@@ -13183,25 +13189,25 @@
         <v>194</v>
       </c>
       <c r="E50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F50">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G50">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H50">
         <v>2.32</v>
       </c>
       <c r="I50">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J50">
         <v>3.1</v>
       </c>
       <c r="K50">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13234,10 +13240,10 @@
         <v>1.91</v>
       </c>
       <c r="V50">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X50">
         <v>12.5</v>
@@ -13408,7 +13414,7 @@
         <v>1.4</v>
       </c>
       <c r="CB50" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:80">
@@ -13425,7 +13431,7 @@
         <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F51">
         <v>2.36</v>
@@ -13437,7 +13443,7 @@
         <v>2.6</v>
       </c>
       <c r="I51">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J51">
         <v>3.95</v>
@@ -13452,7 +13458,7 @@
         <v>1.03</v>
       </c>
       <c r="N51">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O51">
         <v>1.14</v>
@@ -13476,7 +13482,7 @@
         <v>2.84</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
         <v>1.63</v>
@@ -13650,7 +13656,7 @@
         <v>1.01</v>
       </c>
       <c r="CB51" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:80">
@@ -13667,7 +13673,7 @@
         <v>196</v>
       </c>
       <c r="E52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F52">
         <v>3.6</v>
@@ -13700,7 +13706,7 @@
         <v>1.24</v>
       </c>
       <c r="P52">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q52">
         <v>1.71</v>
@@ -13892,7 +13898,7 @@
         <v>1.04</v>
       </c>
       <c r="CB52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:80">
@@ -13909,7 +13915,7 @@
         <v>197</v>
       </c>
       <c r="E53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F53">
         <v>2.04</v>
@@ -14134,7 +14140,7 @@
         <v>1.01</v>
       </c>
       <c r="CB53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:80">
@@ -14151,7 +14157,7 @@
         <v>198</v>
       </c>
       <c r="E54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F54">
         <v>2.56</v>
@@ -14160,7 +14166,7 @@
         <v>2.94</v>
       </c>
       <c r="H54">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I54">
         <v>2.94</v>
@@ -14172,7 +14178,7 @@
         <v>4.1</v>
       </c>
       <c r="L54">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M54">
         <v>1.05</v>
@@ -14184,7 +14190,7 @@
         <v>1.26</v>
       </c>
       <c r="P54">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q54">
         <v>1.76</v>
@@ -14196,10 +14202,10 @@
         <v>2.92</v>
       </c>
       <c r="T54">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U54">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V54">
         <v>1.52</v>
@@ -14376,7 +14382,7 @@
         <v>1.01</v>
       </c>
       <c r="CB54" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:80">
@@ -14393,13 +14399,13 @@
         <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F55">
         <v>2.08</v>
       </c>
       <c r="G55">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H55">
         <v>3.2</v>
@@ -14408,7 +14414,7 @@
         <v>3.85</v>
       </c>
       <c r="J55">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K55">
         <v>4.5</v>
@@ -14438,16 +14444,16 @@
         <v>2.34</v>
       </c>
       <c r="T55">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U55">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V55">
         <v>1.35</v>
       </c>
       <c r="W55">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X55">
         <v>1000</v>
@@ -14618,7 +14624,7 @@
         <v>1.01</v>
       </c>
       <c r="CB55" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:80">
@@ -14635,7 +14641,7 @@
         <v>200</v>
       </c>
       <c r="E56" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F56">
         <v>3.9</v>
@@ -14644,13 +14650,13 @@
         <v>4.9</v>
       </c>
       <c r="H56">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I56">
         <v>1.97</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K56">
         <v>4.7</v>
@@ -14668,13 +14674,13 @@
         <v>1.16</v>
       </c>
       <c r="P56">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="Q56">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R56">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="S56">
         <v>2.2</v>
@@ -14860,7 +14866,7 @@
         <v>1.01</v>
       </c>
       <c r="CB56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:80">
@@ -14877,7 +14883,7 @@
         <v>201</v>
       </c>
       <c r="E57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F57">
         <v>1.47</v>
@@ -15102,7 +15108,7 @@
         <v>1.04</v>
       </c>
       <c r="CB57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:80">
@@ -15119,7 +15125,7 @@
         <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F58">
         <v>2.46</v>
@@ -15344,7 +15350,7 @@
         <v>1.3</v>
       </c>
       <c r="CB58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:80">
@@ -15361,10 +15367,10 @@
         <v>203</v>
       </c>
       <c r="E59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F59">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G59">
         <v>1.71</v>
@@ -15586,7 +15592,7 @@
         <v>1.35</v>
       </c>
       <c r="CB59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:80">
@@ -15603,7 +15609,7 @@
         <v>204</v>
       </c>
       <c r="E60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F60">
         <v>1.55</v>
@@ -15618,7 +15624,7 @@
         <v>7.8</v>
       </c>
       <c r="J60">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K60">
         <v>4.8</v>
@@ -15645,7 +15651,7 @@
         <v>1.42</v>
       </c>
       <c r="S60">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T60">
         <v>1.11</v>
@@ -15828,7 +15834,7 @@
         <v>0</v>
       </c>
       <c r="CB60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:80">
@@ -15845,25 +15851,25 @@
         <v>205</v>
       </c>
       <c r="E61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F61">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G61">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H61">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="I61">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J61">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K61">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L61">
         <v>1.31</v>
@@ -15878,13 +15884,13 @@
         <v>1.25</v>
       </c>
       <c r="P61">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q61">
         <v>1.75</v>
       </c>
       <c r="R61">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S61">
         <v>2.88</v>
@@ -15893,13 +15899,13 @@
         <v>2</v>
       </c>
       <c r="U61">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V61">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
         <v>19.5</v>
@@ -15914,7 +15920,7 @@
         <v>12.5</v>
       </c>
       <c r="AB61">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC61">
         <v>12</v>
@@ -15938,22 +15944,22 @@
         <v>38</v>
       </c>
       <c r="AJ61">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="AK61">
         <v>150</v>
       </c>
       <c r="AL61">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AM61">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN61">
         <v>190</v>
       </c>
       <c r="AO61">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AP61">
         <v>16.5</v>
@@ -15980,10 +15986,10 @@
         <v>13.5</v>
       </c>
       <c r="AX61">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY61">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AZ61">
         <v>23</v>
@@ -15992,19 +15998,19 @@
         <v>30</v>
       </c>
       <c r="BB61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC61">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BD61">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BE61">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF61">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG61">
         <v>6.2</v>
@@ -16013,37 +16019,37 @@
         <v>1000</v>
       </c>
       <c r="BI61">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ61">
         <v>16</v>
       </c>
       <c r="BK61">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BL61">
         <v>1000</v>
       </c>
       <c r="BM61">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BN61">
         <v>17</v>
       </c>
       <c r="BO61">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BP61">
         <v>1000</v>
       </c>
       <c r="BQ61">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BR61">
         <v>1000</v>
       </c>
       <c r="BS61">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BT61">
         <v>5.1</v>
@@ -16055,22 +16061,22 @@
         <v>11.5</v>
       </c>
       <c r="BW61">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX61">
         <v>34</v>
       </c>
       <c r="BY61">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BZ61">
         <v>20</v>
       </c>
       <c r="CA61">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="CB61" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:80">
@@ -16087,25 +16093,25 @@
         <v>206</v>
       </c>
       <c r="E62" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F62">
         <v>2.6</v>
       </c>
       <c r="G62">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="H62">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I62">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="J62">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K62">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L62">
         <v>1.01</v>
@@ -16117,16 +16123,16 @@
         <v>3.95</v>
       </c>
       <c r="O62">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P62">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
       </c>
       <c r="R62">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S62">
         <v>3.1</v>
@@ -16312,7 +16318,7 @@
         <v>1.3</v>
       </c>
       <c r="CB62" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:80">
@@ -16329,7 +16335,7 @@
         <v>207</v>
       </c>
       <c r="E63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F63">
         <v>2.64</v>
@@ -16338,7 +16344,7 @@
         <v>2.88</v>
       </c>
       <c r="H63">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I63">
         <v>3.15</v>
@@ -16554,7 +16560,7 @@
         <v>0</v>
       </c>
       <c r="CB63" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:80">
@@ -16571,7 +16577,7 @@
         <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F64">
         <v>2.08</v>
@@ -16586,7 +16592,7 @@
         <v>3.95</v>
       </c>
       <c r="J64">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K64">
         <v>3.9</v>
@@ -16607,7 +16613,7 @@
         <v>2.06</v>
       </c>
       <c r="Q64">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R64">
         <v>1.4</v>
@@ -16619,7 +16625,7 @@
         <v>1.61</v>
       </c>
       <c r="U64">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V64">
         <v>1.01</v>
@@ -16796,7 +16802,7 @@
         <v>0</v>
       </c>
       <c r="CB64" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:80">
@@ -16813,10 +16819,10 @@
         <v>209</v>
       </c>
       <c r="E65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F65">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G65">
         <v>2.64</v>
@@ -16825,7 +16831,7 @@
         <v>2.82</v>
       </c>
       <c r="I65">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J65">
         <v>3.6</v>
@@ -16864,7 +16870,7 @@
         <v>1.11</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W65">
         <v>1.6</v>
@@ -16987,49 +16993,49 @@
         <v>1000</v>
       </c>
       <c r="BK65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN65">
         <v>1000</v>
       </c>
       <c r="BO65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP65">
         <v>1000</v>
       </c>
       <c r="BQ65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR65">
         <v>1000</v>
       </c>
       <c r="BS65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT65">
         <v>1000</v>
       </c>
       <c r="BU65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV65">
         <v>1000</v>
       </c>
       <c r="BW65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX65">
         <v>1000</v>
       </c>
       <c r="BY65">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ65">
         <v>0</v>
@@ -17038,7 +17044,7 @@
         <v>0</v>
       </c>
       <c r="CB65" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:80">
@@ -17055,25 +17061,25 @@
         <v>210</v>
       </c>
       <c r="E66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F66">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="G66">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="H66">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I66">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="J66">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K66">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -17085,7 +17091,7 @@
         <v>3.7</v>
       </c>
       <c r="O66">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P66">
         <v>2.06</v>
@@ -17094,7 +17100,7 @@
         <v>1.67</v>
       </c>
       <c r="R66">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S66">
         <v>2.64</v>
@@ -17106,10 +17112,10 @@
         <v>1.11</v>
       </c>
       <c r="V66">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W66">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -17280,7 +17286,7 @@
         <v>0</v>
       </c>
       <c r="CB66" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" spans="1:80">
@@ -17297,7 +17303,7 @@
         <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F67">
         <v>7.2</v>
@@ -17324,7 +17330,7 @@
         <v>1.05</v>
       </c>
       <c r="N67">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O67">
         <v>1.24</v>
@@ -17342,7 +17348,7 @@
         <v>2.58</v>
       </c>
       <c r="T67">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U67">
         <v>1.86</v>
@@ -17522,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="CB67" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="1:80">
@@ -17539,7 +17545,7 @@
         <v>212</v>
       </c>
       <c r="E68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F68">
         <v>1.99</v>
@@ -17551,7 +17557,7 @@
         <v>2.82</v>
       </c>
       <c r="I68">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J68">
         <v>3.35</v>
@@ -17590,7 +17596,7 @@
         <v>1.11</v>
       </c>
       <c r="V68">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W68">
         <v>1.72</v>
@@ -17707,55 +17713,55 @@
         <v>1000</v>
       </c>
       <c r="BI68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ68">
         <v>1000</v>
       </c>
       <c r="BK68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL68">
         <v>1000</v>
       </c>
       <c r="BM68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN68">
         <v>1000</v>
       </c>
       <c r="BO68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP68">
         <v>1000</v>
       </c>
       <c r="BQ68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR68">
         <v>1000</v>
       </c>
       <c r="BS68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT68">
         <v>1000</v>
       </c>
       <c r="BU68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV68">
         <v>1000</v>
       </c>
       <c r="BW68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX68">
         <v>1000</v>
       </c>
       <c r="BY68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ68">
         <v>0</v>
@@ -17764,7 +17770,7 @@
         <v>0</v>
       </c>
       <c r="CB68" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:80">
@@ -17781,13 +17787,13 @@
         <v>213</v>
       </c>
       <c r="E69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F69">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G69">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H69">
         <v>3.7</v>
@@ -17817,25 +17823,25 @@
         <v>1.68</v>
       </c>
       <c r="Q69">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R69">
         <v>1.27</v>
       </c>
       <c r="S69">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T69">
         <v>1.86</v>
       </c>
       <c r="U69">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V69">
         <v>1.29</v>
       </c>
       <c r="W69">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X69">
         <v>13.5</v>
@@ -17955,58 +17961,58 @@
         <v>1000</v>
       </c>
       <c r="BK69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL69">
         <v>1000</v>
       </c>
       <c r="BM69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN69">
         <v>1000</v>
       </c>
       <c r="BO69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP69">
         <v>1000</v>
       </c>
       <c r="BQ69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR69">
         <v>1000</v>
       </c>
       <c r="BS69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT69">
         <v>1000</v>
       </c>
       <c r="BU69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV69">
         <v>1000</v>
       </c>
       <c r="BW69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX69">
         <v>1000</v>
       </c>
       <c r="BY69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ69">
         <v>1000</v>
       </c>
       <c r="CA69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB69" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:80">
@@ -18023,7 +18029,7 @@
         <v>214</v>
       </c>
       <c r="E70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F70">
         <v>1.72</v>
@@ -18035,10 +18041,10 @@
         <v>4.3</v>
       </c>
       <c r="I70">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J70">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K70">
         <v>5.3</v>
@@ -18074,7 +18080,7 @@
         <v>1.11</v>
       </c>
       <c r="V70">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W70">
         <v>2.1</v>
@@ -18248,7 +18254,7 @@
         <v>0</v>
       </c>
       <c r="CB70" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:80">
@@ -18265,7 +18271,7 @@
         <v>215</v>
       </c>
       <c r="E71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F71">
         <v>5.4</v>
@@ -18298,10 +18304,10 @@
         <v>1.32</v>
       </c>
       <c r="P71">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q71">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R71">
         <v>1.32</v>
@@ -18490,7 +18496,7 @@
         <v>0</v>
       </c>
       <c r="CB71" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:80">
@@ -18507,7 +18513,7 @@
         <v>216</v>
       </c>
       <c r="E72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F72">
         <v>7.2</v>
@@ -18516,7 +18522,7 @@
         <v>12.5</v>
       </c>
       <c r="H72">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I72">
         <v>1.68</v>
@@ -18525,7 +18531,7 @@
         <v>3.1</v>
       </c>
       <c r="K72">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L72">
         <v>1.01</v>
@@ -18534,7 +18540,7 @@
         <v>1.01</v>
       </c>
       <c r="N72">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O72">
         <v>1.23</v>
@@ -18546,10 +18552,10 @@
         <v>1.74</v>
       </c>
       <c r="R72">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S72">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="T72">
         <v>1.11</v>
@@ -18732,7 +18738,7 @@
         <v>0</v>
       </c>
       <c r="CB72" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="73" spans="1:80">
@@ -18749,13 +18755,13 @@
         <v>217</v>
       </c>
       <c r="E73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F73">
         <v>2.62</v>
       </c>
       <c r="G73">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H73">
         <v>2.48</v>
@@ -18797,7 +18803,7 @@
         <v>1.48</v>
       </c>
       <c r="U73">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V73">
         <v>1.47</v>
@@ -18974,7 +18980,7 @@
         <v>0</v>
       </c>
       <c r="CB73" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74" spans="1:80">
@@ -18991,10 +18997,10 @@
         <v>218</v>
       </c>
       <c r="E74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F74">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G74">
         <v>3.9</v>
@@ -19003,13 +19009,13 @@
         <v>2.08</v>
       </c>
       <c r="I74">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J74">
         <v>3.55</v>
       </c>
       <c r="K74">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L74">
         <v>1.01</v>
@@ -19018,7 +19024,7 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>2.74</v>
+        <v>4.1</v>
       </c>
       <c r="O74">
         <v>1.2</v>
@@ -19030,7 +19036,7 @@
         <v>1.65</v>
       </c>
       <c r="R74">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S74">
         <v>2.6</v>
@@ -19042,7 +19048,7 @@
         <v>1.11</v>
       </c>
       <c r="V74">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W74">
         <v>1.34</v>
@@ -19216,7 +19222,7 @@
         <v>0</v>
       </c>
       <c r="CB74" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:80">
@@ -19233,7 +19239,7 @@
         <v>219</v>
       </c>
       <c r="E75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F75">
         <v>1.77</v>
@@ -19245,7 +19251,7 @@
         <v>4.6</v>
       </c>
       <c r="I75">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J75">
         <v>4.3</v>
@@ -19260,52 +19266,52 @@
         <v>1.04</v>
       </c>
       <c r="N75">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>1.19</v>
       </c>
       <c r="P75">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q75">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R75">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S75">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T75">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U75">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V75">
         <v>1.26</v>
       </c>
       <c r="W75">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X75">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y75">
         <v>24</v>
       </c>
       <c r="Z75">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA75">
         <v>1000</v>
       </c>
       <c r="AB75">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC75">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD75">
         <v>19</v>
@@ -19314,7 +19320,7 @@
         <v>48</v>
       </c>
       <c r="AF75">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG75">
         <v>10.5</v>
@@ -19329,10 +19335,10 @@
         <v>20</v>
       </c>
       <c r="AK75">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL75">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM75">
         <v>65</v>
@@ -19344,7 +19350,7 @@
         <v>36</v>
       </c>
       <c r="AP75">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ75">
         <v>21</v>
@@ -19365,7 +19371,7 @@
         <v>17</v>
       </c>
       <c r="AW75">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AX75">
         <v>12</v>
@@ -19386,10 +19392,10 @@
         <v>14.5</v>
       </c>
       <c r="BD75">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE75">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF75">
         <v>7</v>
@@ -19458,7 +19464,7 @@
         <v>0</v>
       </c>
       <c r="CB75" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="76" spans="1:80">
@@ -19475,7 +19481,7 @@
         <v>220</v>
       </c>
       <c r="E76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F76">
         <v>1.86</v>
@@ -19517,7 +19523,7 @@
         <v>1.32</v>
       </c>
       <c r="S76">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T76">
         <v>1.11</v>
@@ -19553,7 +19559,7 @@
         <v>1000</v>
       </c>
       <c r="AE76">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF76">
         <v>1000</v>
@@ -19574,10 +19580,10 @@
         <v>1000</v>
       </c>
       <c r="AL76">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM76">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN76">
         <v>1000</v>
@@ -19586,121 +19592,121 @@
         <v>1000</v>
       </c>
       <c r="AP76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD76">
         <v>1.01</v>
       </c>
       <c r="BE76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH76">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI76">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="BJ76">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK76">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL76">
         <v>1000</v>
       </c>
       <c r="BM76">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="BN76">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BO76">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BP76">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BQ76">
-        <v>1.64</v>
+        <v>5</v>
       </c>
       <c r="BR76">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BS76">
-        <v>1.72</v>
+        <v>6</v>
       </c>
       <c r="BT76">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BU76">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="BV76">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW76">
-        <v>1.74</v>
+        <v>6.4</v>
       </c>
       <c r="BX76">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY76">
-        <v>1.75</v>
+        <v>6.6</v>
       </c>
       <c r="BZ76">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="CA76">
-        <v>1.71</v>
+        <v>6</v>
       </c>
       <c r="CB76" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" spans="1:80">
@@ -19717,25 +19723,25 @@
         <v>221</v>
       </c>
       <c r="E77" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F77">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G77">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H77">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I77">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J77">
         <v>3.55</v>
       </c>
       <c r="K77">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L77">
         <v>1.29</v>
@@ -19744,13 +19750,13 @@
         <v>1.01</v>
       </c>
       <c r="N77">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O77">
         <v>1.26</v>
       </c>
       <c r="P77">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -19768,10 +19774,10 @@
         <v>1.11</v>
       </c>
       <c r="V77">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -19942,7 +19948,7 @@
         <v>0</v>
       </c>
       <c r="CB77" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="78" spans="1:80">
@@ -19959,232 +19965,232 @@
         <v>222</v>
       </c>
       <c r="E78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F78">
-        <v>1.2</v>
+        <v>2.52</v>
       </c>
       <c r="G78">
-        <v>1.21</v>
+        <v>2.84</v>
       </c>
       <c r="H78">
-        <v>20</v>
+        <v>3.1</v>
       </c>
       <c r="I78">
-        <v>21</v>
+        <v>3.6</v>
       </c>
       <c r="J78">
-        <v>8.199999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="K78">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="L78">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M78">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N78">
-        <v>5.5</v>
+        <v>2.36</v>
       </c>
       <c r="O78">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P78">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q78">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="R78">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="S78">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="T78">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="U78">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="V78">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="W78">
-        <v>5.8</v>
+        <v>1.54</v>
       </c>
       <c r="X78">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y78">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z78">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AA78">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AB78">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC78">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AD78">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE78">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AF78">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG78">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH78">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI78">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AJ78">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AK78">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL78">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM78">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN78">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="AO78">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP78">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AQ78">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AR78">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="AS78">
-        <v>150</v>
+        <v>1.03</v>
       </c>
       <c r="AT78">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU78">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AV78">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="AW78">
-        <v>200</v>
+        <v>1.03</v>
       </c>
       <c r="AX78">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY78">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ78">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BA78">
-        <v>110</v>
+        <v>1.03</v>
       </c>
       <c r="BB78">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC78">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD78">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BE78">
-        <v>130</v>
+        <v>1.03</v>
       </c>
       <c r="BF78">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG78">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BH78">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BI78">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="BJ78">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK78">
-        <v>8.4</v>
+        <v>1.43</v>
       </c>
       <c r="BL78">
         <v>1000</v>
       </c>
       <c r="BM78">
-        <v>26</v>
+        <v>1.43</v>
       </c>
       <c r="BN78">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BO78">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="BP78">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ78">
-        <v>5.5</v>
+        <v>1.43</v>
       </c>
       <c r="BR78">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS78">
-        <v>10.5</v>
+        <v>1.43</v>
       </c>
       <c r="BT78">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BU78">
-        <v>9.800000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="BV78">
         <v>1000</v>
       </c>
       <c r="BW78">
-        <v>16.5</v>
+        <v>1.43</v>
       </c>
       <c r="BX78">
         <v>1000</v>
       </c>
       <c r="BY78">
-        <v>16</v>
+        <v>1.43</v>
       </c>
       <c r="BZ78">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA78">
-        <v>7.2</v>
+        <v>1.43</v>
       </c>
       <c r="CB78" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="79" spans="1:80">
@@ -20201,237 +20207,237 @@
         <v>223</v>
       </c>
       <c r="E79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F79">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G79">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H79">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I79">
-        <v>990</v>
+        <v>2.44</v>
       </c>
       <c r="J79">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K79">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L79">
         <v>1.01</v>
       </c>
       <c r="M79">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N79">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="O79">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P79">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q79">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="R79">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S79">
-        <v>1.74</v>
+        <v>3.25</v>
       </c>
       <c r="T79">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U79">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V79">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="W79">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X79">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y79">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z79">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA79">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB79">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC79">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD79">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE79">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF79">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG79">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH79">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI79">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ79">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK79">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL79">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM79">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN79">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO79">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP79">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ79">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR79">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS79">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AT79">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU79">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV79">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW79">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX79">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY79">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ79">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA79">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BB79">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BC79">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BD79">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BE79">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BF79">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG79">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH79">
         <v>1000</v>
       </c>
       <c r="BI79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ79">
         <v>1000</v>
       </c>
       <c r="BK79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL79">
         <v>1000</v>
       </c>
       <c r="BM79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN79">
         <v>1000</v>
       </c>
       <c r="BO79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP79">
         <v>1000</v>
       </c>
       <c r="BQ79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR79">
         <v>1000</v>
       </c>
       <c r="BS79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT79">
         <v>1000</v>
       </c>
       <c r="BU79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV79">
         <v>1000</v>
       </c>
       <c r="BW79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX79">
         <v>1000</v>
       </c>
       <c r="BY79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ79">
         <v>1000</v>
       </c>
       <c r="CA79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB79" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="80" spans="1:80">
       <c r="A80" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B80" t="s">
         <v>124</v>
@@ -20443,237 +20449,237 @@
         <v>224</v>
       </c>
       <c r="E80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F80">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G80">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H80">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I80">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J80">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="K80">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L80">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M80">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N80">
-        <v>1.25</v>
+        <v>3.65</v>
       </c>
       <c r="O80">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P80">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q80">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="R80">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S80">
-        <v>1.42</v>
+        <v>3.8</v>
       </c>
       <c r="T80">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U80">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V80">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W80">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X80">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y80">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z80">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA80">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB80">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC80">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD80">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE80">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF80">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG80">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH80">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI80">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ80">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK80">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL80">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM80">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN80">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO80">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP80">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ80">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR80">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AS80">
-        <v>1.03</v>
+        <v>65</v>
       </c>
       <c r="AT80">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU80">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV80">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW80">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AX80">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY80">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ80">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA80">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BB80">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BC80">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD80">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE80">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BF80">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG80">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH80">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI80">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ80">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK80">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL80">
         <v>1000</v>
       </c>
       <c r="BM80">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BN80">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO80">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP80">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ80">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BR80">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS80">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BT80">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU80">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV80">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW80">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BX80">
         <v>1000</v>
       </c>
       <c r="BY80">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BZ80">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA80">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="CB80" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" spans="1:80">
       <c r="A81" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B81" t="s">
         <v>124</v>
@@ -20685,7 +20691,7 @@
         <v>225</v>
       </c>
       <c r="E81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F81">
         <v>1.04</v>
@@ -20700,7 +20706,7 @@
         <v>990</v>
       </c>
       <c r="J81">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K81">
         <v>950</v>
@@ -20712,22 +20718,22 @@
         <v>1.01</v>
       </c>
       <c r="N81">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O81">
         <v>1.23</v>
       </c>
       <c r="P81">
+        <v>1.25</v>
+      </c>
+      <c r="Q81">
         <v>1.24</v>
-      </c>
-      <c r="Q81">
-        <v>1.23</v>
       </c>
       <c r="R81">
         <v>1.18</v>
       </c>
       <c r="S81">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="T81">
         <v>1.11</v>
@@ -20736,10 +20742,10 @@
         <v>1.11</v>
       </c>
       <c r="V81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
         <v>1000</v>
@@ -20910,12 +20916,12 @@
         <v>1.01</v>
       </c>
       <c r="CB81" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:80">
       <c r="A82" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B82" t="s">
         <v>124</v>
@@ -20927,237 +20933,237 @@
         <v>226</v>
       </c>
       <c r="E82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F82">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="G82">
-        <v>2.18</v>
+        <v>990</v>
       </c>
       <c r="H82">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I82">
-        <v>3.9</v>
+        <v>990</v>
       </c>
       <c r="J82">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="K82">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L82">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M82">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N82">
-        <v>3.65</v>
+        <v>1.26</v>
       </c>
       <c r="O82">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P82">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="Q82">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="R82">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S82">
-        <v>3.8</v>
+        <v>1.42</v>
       </c>
       <c r="T82">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U82">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V82">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="W82">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="X82">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y82">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z82">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA82">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB82">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC82">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD82">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE82">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF82">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG82">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH82">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI82">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ82">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK82">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL82">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM82">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN82">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO82">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP82">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ82">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR82">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AS82">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AT82">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU82">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV82">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW82">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AX82">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY82">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ82">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA82">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB82">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC82">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD82">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE82">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF82">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG82">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH82">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BI82">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ82">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK82">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL82">
         <v>1000</v>
       </c>
       <c r="BM82">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BN82">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO82">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP82">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ82">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BR82">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS82">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BT82">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU82">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV82">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW82">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX82">
         <v>1000</v>
       </c>
       <c r="BY82">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="BZ82">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA82">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="CB82" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="83" spans="1:80">
       <c r="A83" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B83" t="s">
         <v>124</v>
@@ -21169,232 +21175,232 @@
         <v>227</v>
       </c>
       <c r="E83" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F83">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="G83">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="H83">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I83">
-        <v>2.44</v>
+        <v>870</v>
       </c>
       <c r="J83">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K83">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="L83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N83">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q83">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="R83">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AH83">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI83">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ83">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AL83">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM83">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN83">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AO83">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AP83">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ83">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR83">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AS83">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AT83">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU83">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV83">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW83">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX83">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AY83">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ83">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA83">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BB83">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BC83">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BD83">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BE83">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BF83">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG83">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BH83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB83" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="84" spans="1:80">
@@ -21411,479 +21417,479 @@
         <v>228</v>
       </c>
       <c r="E84" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F84">
-        <v>2.52</v>
+        <v>1.2</v>
       </c>
       <c r="G84">
-        <v>2.84</v>
+        <v>1.21</v>
       </c>
       <c r="H84">
-        <v>3.1</v>
+        <v>20</v>
       </c>
       <c r="I84">
-        <v>3.6</v>
+        <v>21</v>
       </c>
       <c r="J84">
-        <v>2.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K84">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="L84">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N84">
-        <v>2.36</v>
+        <v>5.5</v>
       </c>
       <c r="O84">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P84">
-        <v>1.57</v>
+        <v>2.56</v>
       </c>
       <c r="Q84">
-        <v>2.44</v>
+        <v>1.62</v>
       </c>
       <c r="R84">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="S84">
-        <v>3.95</v>
+        <v>2.58</v>
       </c>
       <c r="T84">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="U84">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="V84">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="W84">
-        <v>1.54</v>
+        <v>5.8</v>
       </c>
       <c r="X84">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y84">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z84">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AA84">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AB84">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC84">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD84">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE84">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AF84">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AG84">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH84">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI84">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ84">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AK84">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL84">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM84">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN84">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="AO84">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP84">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AQ84">
-        <v>1.03</v>
+        <v>48</v>
       </c>
       <c r="AR84">
-        <v>1.03</v>
+        <v>95</v>
       </c>
       <c r="AS84">
-        <v>1.03</v>
+        <v>150</v>
       </c>
       <c r="AT84">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU84">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AV84">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="AW84">
-        <v>1.03</v>
+        <v>200</v>
       </c>
       <c r="AX84">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY84">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ84">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BA84">
-        <v>1.03</v>
+        <v>110</v>
       </c>
       <c r="BB84">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC84">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD84">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="BE84">
-        <v>1.03</v>
+        <v>130</v>
       </c>
       <c r="BF84">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG84">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BH84">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BI84">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BJ84">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK84">
-        <v>1.43</v>
+        <v>8.4</v>
       </c>
       <c r="BL84">
         <v>1000</v>
       </c>
       <c r="BM84">
-        <v>1.43</v>
+        <v>26</v>
       </c>
       <c r="BN84">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BO84">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="BP84">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BQ84">
-        <v>1.43</v>
+        <v>5.5</v>
       </c>
       <c r="BR84">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS84">
-        <v>1.43</v>
+        <v>10.5</v>
       </c>
       <c r="BT84">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU84">
-        <v>1.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV84">
         <v>1000</v>
       </c>
       <c r="BW84">
-        <v>1.43</v>
+        <v>16.5</v>
       </c>
       <c r="BX84">
         <v>1000</v>
       </c>
       <c r="BY84">
-        <v>1.43</v>
+        <v>16</v>
       </c>
       <c r="BZ84">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA84">
-        <v>1.43</v>
+        <v>7.2</v>
       </c>
       <c r="CB84" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="85" spans="1:80">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B85" t="s">
         <v>124</v>
       </c>
       <c r="C85" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D85" t="s">
         <v>229</v>
       </c>
       <c r="E85" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F85">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G85">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H85">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="I85">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J85">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="K85">
         <v>950</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P85">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q85">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB85" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="86" spans="1:80">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B86" t="s">
         <v>124</v>
@@ -21895,223 +21901,223 @@
         <v>230</v>
       </c>
       <c r="E86" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F86">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="G86">
-        <v>2.16</v>
+        <v>600</v>
       </c>
       <c r="H86">
-        <v>3.9</v>
+        <v>1.14</v>
       </c>
       <c r="I86">
-        <v>4.9</v>
+        <v>870</v>
       </c>
       <c r="J86">
-        <v>3.4</v>
+        <v>1.18</v>
       </c>
       <c r="K86">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L86">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M86">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q86">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R86">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S86">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF86">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG86">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH86">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI86">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BJ86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BL86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BN86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BP86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BR86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BT86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BV86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BX86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BZ86">
         <v>0</v>
@@ -22120,240 +22126,240 @@
         <v>0</v>
       </c>
       <c r="CB86" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:80">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B87" t="s">
         <v>124</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D87" t="s">
         <v>231</v>
       </c>
       <c r="E87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F87">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="G87">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="H87">
-        <v>2.52</v>
+        <v>3.85</v>
       </c>
       <c r="I87">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J87">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K87">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L87">
         <v>1.01</v>
       </c>
       <c r="M87">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N87">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P87">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Q87">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="R87">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="S87">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T87">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U87">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V87">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="W87">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="X87">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y87">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z87">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA87">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB87">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC87">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD87">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE87">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF87">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG87">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH87">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI87">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ87">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK87">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL87">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM87">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN87">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO87">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP87">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ87">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR87">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS87">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AT87">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU87">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV87">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW87">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX87">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY87">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ87">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA87">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BB87">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BC87">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BD87">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE87">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="BF87">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG87">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH87">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI87">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ87">
         <v>1000</v>
       </c>
       <c r="BK87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL87">
         <v>1000</v>
       </c>
       <c r="BM87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN87">
         <v>1000</v>
       </c>
       <c r="BO87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP87">
         <v>1000</v>
       </c>
       <c r="BQ87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR87">
         <v>1000</v>
       </c>
       <c r="BS87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT87">
         <v>1000</v>
       </c>
       <c r="BU87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV87">
         <v>1000</v>
       </c>
       <c r="BW87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX87">
         <v>1000</v>
       </c>
       <c r="BY87">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ87">
         <v>0</v>
@@ -22362,12 +22368,12 @@
         <v>0</v>
       </c>
       <c r="CB87" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="88" spans="1:80">
       <c r="A88" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B88" t="s">
         <v>124</v>
@@ -22379,232 +22385,474 @@
         <v>232</v>
       </c>
       <c r="E88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F88">
+        <v>2.98</v>
+      </c>
+      <c r="G88">
+        <v>3.25</v>
+      </c>
+      <c r="H88">
+        <v>2.52</v>
+      </c>
+      <c r="I88">
+        <v>2.6</v>
+      </c>
+      <c r="J88">
+        <v>3.25</v>
+      </c>
+      <c r="K88">
+        <v>3.6</v>
+      </c>
+      <c r="L88">
+        <v>1.01</v>
+      </c>
+      <c r="M88">
+        <v>1.07</v>
+      </c>
+      <c r="N88">
+        <v>3.25</v>
+      </c>
+      <c r="O88">
+        <v>1.34</v>
+      </c>
+      <c r="P88">
+        <v>1.8</v>
+      </c>
+      <c r="Q88">
+        <v>2</v>
+      </c>
+      <c r="R88">
+        <v>1.3</v>
+      </c>
+      <c r="S88">
+        <v>3.6</v>
+      </c>
+      <c r="T88">
+        <v>1.76</v>
+      </c>
+      <c r="U88">
+        <v>1.9</v>
+      </c>
+      <c r="V88">
+        <v>1.62</v>
+      </c>
+      <c r="W88">
+        <v>1.44</v>
+      </c>
+      <c r="X88">
+        <v>15</v>
+      </c>
+      <c r="Y88">
+        <v>11</v>
+      </c>
+      <c r="Z88">
+        <v>17</v>
+      </c>
+      <c r="AA88">
+        <v>40</v>
+      </c>
+      <c r="AB88">
+        <v>12</v>
+      </c>
+      <c r="AC88">
+        <v>8</v>
+      </c>
+      <c r="AD88">
+        <v>12.5</v>
+      </c>
+      <c r="AE88">
+        <v>36</v>
+      </c>
+      <c r="AF88">
+        <v>22</v>
+      </c>
+      <c r="AG88">
+        <v>14</v>
+      </c>
+      <c r="AH88">
+        <v>18.5</v>
+      </c>
+      <c r="AI88">
+        <v>55</v>
+      </c>
+      <c r="AJ88">
+        <v>60</v>
+      </c>
+      <c r="AK88">
+        <v>40</v>
+      </c>
+      <c r="AL88">
+        <v>55</v>
+      </c>
+      <c r="AM88">
+        <v>110</v>
+      </c>
+      <c r="AN88">
+        <v>36</v>
+      </c>
+      <c r="AO88">
+        <v>27</v>
+      </c>
+      <c r="AP88">
+        <v>11</v>
+      </c>
+      <c r="AQ88">
+        <v>9</v>
+      </c>
+      <c r="AR88">
+        <v>14.5</v>
+      </c>
+      <c r="AS88">
+        <v>32</v>
+      </c>
+      <c r="AT88">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU88">
+        <v>6.8</v>
+      </c>
+      <c r="AV88">
+        <v>10.5</v>
+      </c>
+      <c r="AW88">
+        <v>24</v>
+      </c>
+      <c r="AX88">
+        <v>17.5</v>
+      </c>
+      <c r="AY88">
+        <v>12</v>
+      </c>
+      <c r="AZ88">
+        <v>15.5</v>
+      </c>
+      <c r="BA88">
+        <v>36</v>
+      </c>
+      <c r="BB88">
+        <v>42</v>
+      </c>
+      <c r="BC88">
+        <v>30</v>
+      </c>
+      <c r="BD88">
+        <v>40</v>
+      </c>
+      <c r="BE88">
+        <v>80</v>
+      </c>
+      <c r="BF88">
+        <v>7.2</v>
+      </c>
+      <c r="BG88">
+        <v>19</v>
+      </c>
+      <c r="BH88">
+        <v>1000</v>
+      </c>
+      <c r="BI88">
+        <v>1.01</v>
+      </c>
+      <c r="BJ88">
+        <v>1000</v>
+      </c>
+      <c r="BK88">
+        <v>1.01</v>
+      </c>
+      <c r="BL88">
+        <v>1000</v>
+      </c>
+      <c r="BM88">
+        <v>1.01</v>
+      </c>
+      <c r="BN88">
+        <v>1000</v>
+      </c>
+      <c r="BO88">
+        <v>1.01</v>
+      </c>
+      <c r="BP88">
+        <v>1000</v>
+      </c>
+      <c r="BQ88">
+        <v>1.01</v>
+      </c>
+      <c r="BR88">
+        <v>1000</v>
+      </c>
+      <c r="BS88">
+        <v>1.01</v>
+      </c>
+      <c r="BT88">
+        <v>1000</v>
+      </c>
+      <c r="BU88">
+        <v>1.01</v>
+      </c>
+      <c r="BV88">
+        <v>1000</v>
+      </c>
+      <c r="BW88">
+        <v>1.01</v>
+      </c>
+      <c r="BX88">
+        <v>1000</v>
+      </c>
+      <c r="BY88">
+        <v>1.01</v>
+      </c>
+      <c r="BZ88">
+        <v>0</v>
+      </c>
+      <c r="CA88">
+        <v>0</v>
+      </c>
+      <c r="CB88" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:80">
+      <c r="A89" t="s">
+        <v>123</v>
+      </c>
+      <c r="B89" t="s">
+        <v>124</v>
+      </c>
+      <c r="C89" t="s">
+        <v>145</v>
+      </c>
+      <c r="D89" t="s">
+        <v>233</v>
+      </c>
+      <c r="E89" t="s">
+        <v>321</v>
+      </c>
+      <c r="F89">
         <v>1.04</v>
       </c>
-      <c r="G88">
+      <c r="G89">
         <v>990</v>
       </c>
-      <c r="H88">
+      <c r="H89">
         <v>1.04</v>
       </c>
-      <c r="I88">
-        <v>990</v>
-      </c>
-      <c r="J88">
-        <v>1.02</v>
-      </c>
-      <c r="K88">
-        <v>500</v>
-      </c>
-      <c r="L88">
-        <v>1.01</v>
-      </c>
-      <c r="M88">
-        <v>1.01</v>
-      </c>
-      <c r="N88">
-        <v>1.24</v>
-      </c>
-      <c r="O88">
+      <c r="I89">
+        <v>60</v>
+      </c>
+      <c r="J89">
+        <v>1.04</v>
+      </c>
+      <c r="K89">
+        <v>950</v>
+      </c>
+      <c r="L89">
+        <v>1.01</v>
+      </c>
+      <c r="M89">
+        <v>1.01</v>
+      </c>
+      <c r="N89">
+        <v>1.26</v>
+      </c>
+      <c r="O89">
         <v>1.41</v>
       </c>
-      <c r="P88">
-        <v>1.24</v>
-      </c>
-      <c r="Q88">
+      <c r="P89">
+        <v>1.25</v>
+      </c>
+      <c r="Q89">
         <v>1.41</v>
       </c>
-      <c r="R88">
+      <c r="R89">
         <v>1.18</v>
       </c>
-      <c r="S88">
+      <c r="S89">
         <v>1.4</v>
       </c>
-      <c r="T88">
+      <c r="T89">
         <v>1.11</v>
       </c>
-      <c r="U88">
+      <c r="U89">
         <v>1.11</v>
       </c>
-      <c r="V88">
-        <v>1.01</v>
-      </c>
-      <c r="W88">
-        <v>1.01</v>
-      </c>
-      <c r="X88">
-        <v>1000</v>
-      </c>
-      <c r="Y88">
-        <v>1000</v>
-      </c>
-      <c r="Z88">
-        <v>1000</v>
-      </c>
-      <c r="AA88">
-        <v>1000</v>
-      </c>
-      <c r="AB88">
-        <v>1000</v>
-      </c>
-      <c r="AC88">
-        <v>1000</v>
-      </c>
-      <c r="AD88">
-        <v>1000</v>
-      </c>
-      <c r="AE88">
-        <v>1000</v>
-      </c>
-      <c r="AF88">
-        <v>1000</v>
-      </c>
-      <c r="AG88">
-        <v>1000</v>
-      </c>
-      <c r="AH88">
-        <v>1000</v>
-      </c>
-      <c r="AI88">
-        <v>1000</v>
-      </c>
-      <c r="AJ88">
-        <v>1000</v>
-      </c>
-      <c r="AK88">
-        <v>1000</v>
-      </c>
-      <c r="AL88">
-        <v>1000</v>
-      </c>
-      <c r="AM88">
-        <v>1000</v>
-      </c>
-      <c r="AN88">
-        <v>1000</v>
-      </c>
-      <c r="AO88">
-        <v>1000</v>
-      </c>
-      <c r="AP88">
-        <v>1.01</v>
-      </c>
-      <c r="AQ88">
-        <v>1.01</v>
-      </c>
-      <c r="AR88">
-        <v>1.01</v>
-      </c>
-      <c r="AS88">
-        <v>1.01</v>
-      </c>
-      <c r="AT88">
-        <v>1.01</v>
-      </c>
-      <c r="AU88">
-        <v>1.01</v>
-      </c>
-      <c r="AV88">
-        <v>1.01</v>
-      </c>
-      <c r="AW88">
-        <v>1.01</v>
-      </c>
-      <c r="AX88">
-        <v>1.01</v>
-      </c>
-      <c r="AY88">
-        <v>1.01</v>
-      </c>
-      <c r="AZ88">
-        <v>1.01</v>
-      </c>
-      <c r="BA88">
-        <v>1.01</v>
-      </c>
-      <c r="BB88">
-        <v>1.01</v>
-      </c>
-      <c r="BC88">
-        <v>1.01</v>
-      </c>
-      <c r="BD88">
-        <v>1.01</v>
-      </c>
-      <c r="BE88">
-        <v>1.01</v>
-      </c>
-      <c r="BF88">
-        <v>1.01</v>
-      </c>
-      <c r="BG88">
-        <v>1.01</v>
-      </c>
-      <c r="BH88">
-        <v>1000</v>
-      </c>
-      <c r="BI88">
+      <c r="V89">
+        <v>1.01</v>
+      </c>
+      <c r="W89">
+        <v>1.01</v>
+      </c>
+      <c r="X89">
+        <v>1000</v>
+      </c>
+      <c r="Y89">
+        <v>1000</v>
+      </c>
+      <c r="Z89">
+        <v>1000</v>
+      </c>
+      <c r="AA89">
+        <v>1000</v>
+      </c>
+      <c r="AB89">
+        <v>1000</v>
+      </c>
+      <c r="AC89">
+        <v>1000</v>
+      </c>
+      <c r="AD89">
+        <v>1000</v>
+      </c>
+      <c r="AE89">
+        <v>1000</v>
+      </c>
+      <c r="AF89">
+        <v>1000</v>
+      </c>
+      <c r="AG89">
+        <v>1000</v>
+      </c>
+      <c r="AH89">
+        <v>1000</v>
+      </c>
+      <c r="AI89">
+        <v>1000</v>
+      </c>
+      <c r="AJ89">
+        <v>1000</v>
+      </c>
+      <c r="AK89">
+        <v>1000</v>
+      </c>
+      <c r="AL89">
+        <v>1000</v>
+      </c>
+      <c r="AM89">
+        <v>1000</v>
+      </c>
+      <c r="AN89">
+        <v>1000</v>
+      </c>
+      <c r="AO89">
+        <v>1000</v>
+      </c>
+      <c r="AP89">
+        <v>1.03</v>
+      </c>
+      <c r="AQ89">
+        <v>1.03</v>
+      </c>
+      <c r="AR89">
+        <v>1.03</v>
+      </c>
+      <c r="AS89">
+        <v>1.03</v>
+      </c>
+      <c r="AT89">
+        <v>1.03</v>
+      </c>
+      <c r="AU89">
+        <v>1.03</v>
+      </c>
+      <c r="AV89">
+        <v>1.03</v>
+      </c>
+      <c r="AW89">
+        <v>1.03</v>
+      </c>
+      <c r="AX89">
+        <v>1.03</v>
+      </c>
+      <c r="AY89">
+        <v>1.03</v>
+      </c>
+      <c r="AZ89">
+        <v>1.03</v>
+      </c>
+      <c r="BA89">
+        <v>1.03</v>
+      </c>
+      <c r="BB89">
+        <v>1.03</v>
+      </c>
+      <c r="BC89">
+        <v>1.03</v>
+      </c>
+      <c r="BD89">
+        <v>1.03</v>
+      </c>
+      <c r="BE89">
+        <v>1.03</v>
+      </c>
+      <c r="BF89">
+        <v>1.01</v>
+      </c>
+      <c r="BG89">
+        <v>1.01</v>
+      </c>
+      <c r="BH89">
+        <v>1000</v>
+      </c>
+      <c r="BI89">
         <v>1.04</v>
       </c>
-      <c r="BJ88">
-        <v>1000</v>
-      </c>
-      <c r="BK88">
+      <c r="BJ89">
+        <v>1000</v>
+      </c>
+      <c r="BK89">
         <v>1.04</v>
       </c>
-      <c r="BL88">
-        <v>1000</v>
-      </c>
-      <c r="BM88">
+      <c r="BL89">
+        <v>1000</v>
+      </c>
+      <c r="BM89">
         <v>1.04</v>
       </c>
-      <c r="BN88">
-        <v>1000</v>
-      </c>
-      <c r="BO88">
+      <c r="BN89">
+        <v>1000</v>
+      </c>
+      <c r="BO89">
         <v>1.04</v>
       </c>
-      <c r="BP88">
-        <v>1000</v>
-      </c>
-      <c r="BQ88">
+      <c r="BP89">
+        <v>1000</v>
+      </c>
+      <c r="BQ89">
         <v>1.04</v>
       </c>
-      <c r="BR88">
-        <v>1000</v>
-      </c>
-      <c r="BS88">
+      <c r="BR89">
+        <v>1000</v>
+      </c>
+      <c r="BS89">
         <v>1.04</v>
       </c>
-      <c r="BT88">
-        <v>1000</v>
-      </c>
-      <c r="BU88">
+      <c r="BT89">
+        <v>1000</v>
+      </c>
+      <c r="BU89">
         <v>1.04</v>
       </c>
-      <c r="BV88">
-        <v>1000</v>
-      </c>
-      <c r="BW88">
+      <c r="BV89">
+        <v>1000</v>
+      </c>
+      <c r="BW89">
         <v>1.04</v>
       </c>
-      <c r="BX88">
-        <v>1000</v>
-      </c>
-      <c r="BY88">
+      <c r="BX89">
+        <v>1000</v>
+      </c>
+      <c r="BY89">
         <v>1.04</v>
       </c>
-      <c r="BZ88">
-        <v>1000</v>
-      </c>
-      <c r="CA88">
+      <c r="BZ89">
+        <v>1000</v>
+      </c>
+      <c r="CA89">
         <v>1.04</v>
       </c>
-      <c r="CB88" t="s">
-        <v>320</v>
+      <c r="CB89" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
